--- a/file/temp/ExcelTableToMarkDownSample.xlsx
+++ b/file/temp/ExcelTableToMarkDownSample.xlsx
@@ -8,18 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\D_SSD2TB\R.DAPC\file\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5053FB6-8D5B-4459-B422-BBFD9341C2DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A61A59-E5FD-4EA3-A716-E5F4733968C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="2" xr2:uid="{D94F812B-BC61-4A22-9692-634766FE0D40}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="3" xr2:uid="{D94F812B-BC61-4A22-9692-634766FE0D40}"/>
   </bookViews>
   <sheets>
     <sheet name="Sample" sheetId="1" r:id="rId1"/>
     <sheet name="LayerL1" sheetId="6" r:id="rId2"/>
     <sheet name="LayerL2" sheetId="7" r:id="rId3"/>
+    <sheet name="LayerL2 (2)" sheetId="8" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_Toc107986980" localSheetId="1">LayerL1!$B$9</definedName>
     <definedName name="_Toc107986980" localSheetId="2">LayerL2!$B$9</definedName>
+    <definedName name="_Toc107986980" localSheetId="3">'LayerL2 (2)'!$B$9</definedName>
     <definedName name="_Toc107986980" localSheetId="0">Sample!$B$9</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="150">
   <si>
     <t>Creación de tablas en formato .md</t>
   </si>
@@ -354,6 +356,144 @@
   </si>
   <si>
     <t>Contratista / Planos de taller</t>
+  </si>
+  <si>
+    <t>AD</t>
+  </si>
+  <si>
+    <t>Architectural Demolition</t>
+  </si>
+  <si>
+    <t>AE</t>
+  </si>
+  <si>
+    <t>Architectural Elements</t>
+  </si>
+  <si>
+    <t>AF</t>
+  </si>
+  <si>
+    <t>Architectural Finishes</t>
+  </si>
+  <si>
+    <t>AG</t>
+  </si>
+  <si>
+    <t>Architectural Graphics</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>Architectural Interiors</t>
+  </si>
+  <si>
+    <t>AJ</t>
+  </si>
+  <si>
+    <t>User Defined</t>
+  </si>
+  <si>
+    <t>AK</t>
+  </si>
+  <si>
+    <t>AS</t>
+  </si>
+  <si>
+    <t>Architectural Site</t>
+  </si>
+  <si>
+    <t>Designador</t>
+  </si>
+  <si>
+    <t>Demolición arquitectónica</t>
+  </si>
+  <si>
+    <t>Elementos arquitectónicos</t>
+  </si>
+  <si>
+    <t>Acabados arquitectónicos</t>
+  </si>
+  <si>
+    <t>Gráficos arquitectónicos</t>
+  </si>
+  <si>
+    <t>Interiores arquitectónicos</t>
+  </si>
+  <si>
+    <t>Definido por el usuario</t>
+  </si>
+  <si>
+    <t>Sitio arquitectónico</t>
+  </si>
+  <si>
+    <t>Descripción (en)</t>
+  </si>
+  <si>
+    <t>Descripción (es)</t>
+  </si>
+  <si>
+    <t>Abandoned</t>
+  </si>
+  <si>
+    <t>Abandonado</t>
+  </si>
+  <si>
+    <t>Existing to demolish</t>
+  </si>
+  <si>
+    <t>Existente para demoler</t>
+  </si>
+  <si>
+    <t>Existing to remain</t>
+  </si>
+  <si>
+    <t>Existente para conservar</t>
+  </si>
+  <si>
+    <t>Future work</t>
+  </si>
+  <si>
+    <t>Trabajo futuro</t>
+  </si>
+  <si>
+    <t>Items to be moved</t>
+  </si>
+  <si>
+    <t>Artículos a trasladar</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>New work</t>
+  </si>
+  <si>
+    <t>Trabajo nuevo</t>
+  </si>
+  <si>
+    <t>Temporary work</t>
+  </si>
+  <si>
+    <t>Trabajo temporal</t>
+  </si>
+  <si>
+    <t>Not in contract</t>
+  </si>
+  <si>
+    <t>Sin contrato</t>
+  </si>
+  <si>
+    <t>1a9</t>
+  </si>
+  <si>
+    <t>Phase numbers</t>
+  </si>
+  <si>
+    <t>Número de fases</t>
+  </si>
+  <si>
+    <t>ß</t>
   </si>
 </sst>
 </file>
@@ -7806,7 +7946,7 @@
         <v>|  |  |  |</v>
       </c>
       <c r="R70" s="5" t="str">
-        <f t="shared" ref="R70:R105" si="11">_xlfn.CONCAT("| ",B70," | ",C70," | ",D70," | ",E70," |")</f>
+        <f t="shared" ref="R70:R103" si="11">_xlfn.CONCAT("| ",B70," | ",C70," | ",D70," | ",E70," |")</f>
         <v>|  |  |  |  |</v>
       </c>
       <c r="S70" s="5" t="str">
@@ -9282,13 +9422,13 @@
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="4" t="s">
-        <v>44</v>
+        <v>119</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>45</v>
+        <v>127</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>11</v>
@@ -9311,31 +9451,31 @@
       <c r="O3" s="4"/>
       <c r="P3" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B3," | ",C3," |")</f>
-        <v>| Prefijo | Disciplina (en) |</v>
+        <v>| Designador | Descripción (en) |</v>
       </c>
       <c r="Q3" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," |")</f>
-        <v>| Prefijo | Disciplina (en) | Disciplina (es) |</v>
+        <v>| Designador | Descripción (en) | Descripción (es) |</v>
       </c>
       <c r="R3" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," |")</f>
-        <v>| Prefijo | Disciplina (en) | Disciplina (es) | A |</v>
+        <v>| Designador | Descripción (en) | Descripción (es) | A |</v>
       </c>
       <c r="S3" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," |",F3," |")</f>
-        <v>| Prefijo | Disciplina (en) | Disciplina (es) | A |B |</v>
+        <v>| Designador | Descripción (en) | Descripción (es) | A |B |</v>
       </c>
       <c r="T3" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," |",F3," |",G3," |")</f>
-        <v>| Prefijo | Disciplina (en) | Disciplina (es) | A |B |C |</v>
+        <v>| Designador | Descripción (en) | Descripción (es) | A |B |C |</v>
       </c>
       <c r="U3" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," | ",F3," | ",G3," | ",H3," |")</f>
-        <v>| Prefijo | Disciplina (en) | Disciplina (es) | A | B | C | D |</v>
+        <v>| Designador | Descripción (en) | Descripción (es) | A | B | C | D |</v>
       </c>
       <c r="V3" s="5" t="str">
         <f t="shared" ref="V3:V14" si="0">_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," |",F3," |",G3," |",H3," |",I3," |",J3," |",K3," |",L3," |",M3," |",N3," |")</f>
-        <v>| Prefijo | Disciplina (en) | Disciplina (es) | A |B |C |D | | | | | | |</v>
+        <v>| Designador | Descripción (en) | Descripción (es) | A |B |C |D | | | | | | |</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.55000000000000004">
@@ -9464,13 +9604,13 @@
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="5" t="s">
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>49</v>
+        <v>105</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>6</v>
@@ -9489,42 +9629,42 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5" t="str">
         <f t="shared" ref="P6:P14" si="4">_xlfn.CONCAT("| ",B6," | ",C6," |")</f>
-        <v>| B | Geotechnical |</v>
+        <v>| AD | Architectural Demolition |</v>
       </c>
       <c r="Q6" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| B | Geotechnical | Geotecnia |</v>
+        <v>| AD | Architectural Demolition | Demolición arquitectónica |</v>
       </c>
       <c r="R6" s="5" t="str">
         <f t="shared" ref="R6:R69" si="5">_xlfn.CONCAT("| ",B6," | ",C6," | ",D6," | ",E6," |")</f>
-        <v>| B | Geotechnical | Geotecnia | ✓ |</v>
+        <v>| AD | Architectural Demolition | Demolición arquitectónica | ✓ |</v>
       </c>
       <c r="S6" s="5" t="str">
         <f t="shared" ref="S6:S69" si="6">_xlfn.CONCAT("| ",B6," | ",C6," | ",D6," | ",E6," |",F6," |")</f>
-        <v>| B | Geotechnical | Geotecnia | ✓ |✕ |</v>
+        <v>| AD | Architectural Demolition | Demolición arquitectónica | ✓ |✕ |</v>
       </c>
       <c r="T6" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| B | Geotechnical | Geotecnia | ✓ |✕ | |</v>
+        <v>| AD | Architectural Demolition | Demolición arquitectónica | ✓ |✕ | |</v>
       </c>
       <c r="U6" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| B | Geotechnical | Geotecnia | ✓ | ✕ |  |  |</v>
+        <v>| AD | Architectural Demolition | Demolición arquitectónica | ✓ | ✕ |  |  |</v>
       </c>
       <c r="V6" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| B | Geotechnical | Geotecnia | ✓ |✕ | | | | | | | | |</v>
+        <v>| AD | Architectural Demolition | Demolición arquitectónica | ✓ |✕ | | | | | | | | |</v>
       </c>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="5" t="s">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>51</v>
+        <v>107</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>51</v>
+        <v>121</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>6</v>
@@ -9543,42 +9683,42 @@
       <c r="O7" s="5"/>
       <c r="P7" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| C | Civil |</v>
+        <v>| AE | Architectural Elements |</v>
       </c>
       <c r="Q7" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| C | Civil | Civil |</v>
+        <v>| AE | Architectural Elements | Elementos arquitectónicos |</v>
       </c>
       <c r="R7" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| C | Civil | Civil | ✓ |</v>
+        <v>| AE | Architectural Elements | Elementos arquitectónicos | ✓ |</v>
       </c>
       <c r="S7" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| C | Civil | Civil | ✓ |✓ |</v>
+        <v>| AE | Architectural Elements | Elementos arquitectónicos | ✓ |✓ |</v>
       </c>
       <c r="T7" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| C | Civil | Civil | ✓ |✓ | |</v>
+        <v>| AE | Architectural Elements | Elementos arquitectónicos | ✓ |✓ | |</v>
       </c>
       <c r="U7" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| C | Civil | Civil | ✓ | ✓ |  |  |</v>
+        <v>| AE | Architectural Elements | Elementos arquitectónicos | ✓ | ✓ |  |  |</v>
       </c>
       <c r="V7" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| C | Civil | Civil | ✓ |✓ | | | | | | | | |</v>
+        <v>| AE | Architectural Elements | Elementos arquitectónicos | ✓ |✓ | | | | | | | | |</v>
       </c>
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="5" t="s">
-        <v>14</v>
+        <v>108</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>53</v>
+        <v>122</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>6</v>
@@ -9597,42 +9737,42 @@
       <c r="O8" s="5"/>
       <c r="P8" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| D | Process |</v>
+        <v>| AF | Architectural Finishes |</v>
       </c>
       <c r="Q8" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| D | Process | Procesos |</v>
+        <v>| AF | Architectural Finishes | Acabados arquitectónicos |</v>
       </c>
       <c r="R8" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| D | Process | Procesos | ✓ |</v>
+        <v>| AF | Architectural Finishes | Acabados arquitectónicos | ✓ |</v>
       </c>
       <c r="S8" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| D | Process | Procesos | ✓ |✕ |</v>
+        <v>| AF | Architectural Finishes | Acabados arquitectónicos | ✓ |✕ |</v>
       </c>
       <c r="T8" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| D | Process | Procesos | ✓ |✕ | |</v>
+        <v>| AF | Architectural Finishes | Acabados arquitectónicos | ✓ |✕ | |</v>
       </c>
       <c r="U8" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| D | Process | Procesos | ✓ | ✕ |  |  |</v>
+        <v>| AF | Architectural Finishes | Acabados arquitectónicos | ✓ | ✕ |  |  |</v>
       </c>
       <c r="V8" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| D | Process | Procesos | ✓ |✕ | | | | | | | | |</v>
+        <v>| AF | Architectural Finishes | Acabados arquitectónicos | ✓ |✕ | | | | | | | | |</v>
       </c>
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="5" t="s">
-        <v>54</v>
+        <v>110</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>56</v>
+        <v>123</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>6</v>
@@ -9651,42 +9791,42 @@
       <c r="O9" s="5"/>
       <c r="P9" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| E | Electrical |</v>
+        <v>| AG | Architectural Graphics |</v>
       </c>
       <c r="Q9" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| E | Electrical | Electricidad |</v>
+        <v>| AG | Architectural Graphics | Gráficos arquitectónicos |</v>
       </c>
       <c r="R9" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| E | Electrical | Electricidad | ✓ |</v>
+        <v>| AG | Architectural Graphics | Gráficos arquitectónicos | ✓ |</v>
       </c>
       <c r="S9" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| E | Electrical | Electricidad | ✓ |✕ |</v>
+        <v>| AG | Architectural Graphics | Gráficos arquitectónicos | ✓ |✕ |</v>
       </c>
       <c r="T9" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| E | Electrical | Electricidad | ✓ |✕ | |</v>
+        <v>| AG | Architectural Graphics | Gráficos arquitectónicos | ✓ |✕ | |</v>
       </c>
       <c r="U9" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| E | Electrical | Electricidad | ✓ | ✕ |  |  |</v>
+        <v>| AG | Architectural Graphics | Gráficos arquitectónicos | ✓ | ✕ |  |  |</v>
       </c>
       <c r="V9" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| E | Electrical | Electricidad | ✓ |✕ | | | | | | | | |</v>
+        <v>| AG | Architectural Graphics | Gráficos arquitectónicos | ✓ |✕ | | | | | | | | |</v>
       </c>
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="5" t="s">
-        <v>57</v>
+        <v>112</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>58</v>
+        <v>113</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>59</v>
+        <v>124</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>6</v>
@@ -9705,42 +9845,42 @@
       <c r="O10" s="5"/>
       <c r="P10" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| F | Fire Protection |</v>
+        <v>| AI | Architectural Interiors |</v>
       </c>
       <c r="Q10" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| F | Fire Protection | Protección contra incendios |</v>
+        <v>| AI | Architectural Interiors | Interiores arquitectónicos |</v>
       </c>
       <c r="R10" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| F | Fire Protection | Protección contra incendios | ✓ |</v>
+        <v>| AI | Architectural Interiors | Interiores arquitectónicos | ✓ |</v>
       </c>
       <c r="S10" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| F | Fire Protection | Protección contra incendios | ✓ |✕ |</v>
+        <v>| AI | Architectural Interiors | Interiores arquitectónicos | ✓ |✕ |</v>
       </c>
       <c r="T10" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| F | Fire Protection | Protección contra incendios | ✓ |✕ | |</v>
+        <v>| AI | Architectural Interiors | Interiores arquitectónicos | ✓ |✕ | |</v>
       </c>
       <c r="U10" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| F | Fire Protection | Protección contra incendios | ✓ | ✕ |  |  |</v>
+        <v>| AI | Architectural Interiors | Interiores arquitectónicos | ✓ | ✕ |  |  |</v>
       </c>
       <c r="V10" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| F | Fire Protection | Protección contra incendios | ✓ |✕ | | | | | | | | |</v>
+        <v>| AI | Architectural Interiors | Interiores arquitectónicos | ✓ |✕ | | | | | | | | |</v>
       </c>
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="5" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>61</v>
+        <v>115</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>61</v>
+        <v>125</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>6</v>
@@ -9759,42 +9899,42 @@
       <c r="O11" s="5"/>
       <c r="P11" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| G | General |</v>
+        <v>| AJ | User Defined |</v>
       </c>
       <c r="Q11" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| G | General | General |</v>
+        <v>| AJ | User Defined | Definido por el usuario |</v>
       </c>
       <c r="R11" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| G | General | General | ✓ |</v>
+        <v>| AJ | User Defined | Definido por el usuario | ✓ |</v>
       </c>
       <c r="S11" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| G | General | General | ✓ |✓ |</v>
+        <v>| AJ | User Defined | Definido por el usuario | ✓ |✓ |</v>
       </c>
       <c r="T11" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| G | General | General | ✓ |✓ | |</v>
+        <v>| AJ | User Defined | Definido por el usuario | ✓ |✓ | |</v>
       </c>
       <c r="U11" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>| G | General | General | ✓ | ✓ |  |  |</v>
+        <v>| AJ | User Defined | Definido por el usuario | ✓ | ✓ |  |  |</v>
       </c>
       <c r="V11" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| G | General | General | ✓ |✓ | | | | | | | | |</v>
+        <v>| AJ | User Defined | Definido por el usuario | ✓ |✓ | | | | | | | | |</v>
       </c>
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="5" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>64</v>
+        <v>125</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
@@ -9809,39 +9949,39 @@
       <c r="O12" s="5"/>
       <c r="P12" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| H | Hazardous Materials |</v>
+        <v>| AK | User Defined |</v>
       </c>
       <c r="Q12" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| H | Hazardous Materials | Materiales peligrosos |</v>
+        <v>| AK | User Defined | Definido por el usuario |</v>
       </c>
       <c r="R12" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| H | Hazardous Materials | Materiales peligrosos |  |</v>
+        <v>| AK | User Defined | Definido por el usuario |  |</v>
       </c>
       <c r="S12" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| H | Hazardous Materials | Materiales peligrosos |  | |</v>
+        <v>| AK | User Defined | Definido por el usuario |  | |</v>
       </c>
       <c r="T12" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| H | Hazardous Materials | Materiales peligrosos |  | | |</v>
+        <v>| AK | User Defined | Definido por el usuario |  | | |</v>
       </c>
       <c r="U12" s="5"/>
       <c r="V12" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| H | Hazardous Materials | Materiales peligrosos |  | | | | | | | | | |</v>
+        <v>| AK | User Defined | Definido por el usuario |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="5" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>67</v>
+        <v>126</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
@@ -9856,40 +9996,34 @@
       <c r="O13" s="5"/>
       <c r="P13" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| I | Interiors |</v>
+        <v>| AS | Architectural Site |</v>
       </c>
       <c r="Q13" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| I | Interiors | Interiores |</v>
+        <v>| AS | Architectural Site | Sitio arquitectónico |</v>
       </c>
       <c r="R13" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| I | Interiors | Interiores |  |</v>
+        <v>| AS | Architectural Site | Sitio arquitectónico |  |</v>
       </c>
       <c r="S13" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| I | Interiors | Interiores |  | |</v>
+        <v>| AS | Architectural Site | Sitio arquitectónico |  | |</v>
       </c>
       <c r="T13" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| I | Interiors | Interiores |  | | |</v>
+        <v>| AS | Architectural Site | Sitio arquitectónico |  | | |</v>
       </c>
       <c r="U13" s="5"/>
       <c r="V13" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| I | Interiors | Interiores |  | | | | | | | | | |</v>
+        <v>| AS | Architectural Site | Sitio arquitectónico |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>70</v>
-      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
@@ -9903,40 +10037,34 @@
       <c r="O14" s="5"/>
       <c r="P14" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>| L | Landscape |</v>
+        <v>|  |  |</v>
       </c>
       <c r="Q14" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| L | Landscape | Paisajismo |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R14" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>| L | Landscape | Paisajismo |  |</v>
+        <v>|  |  |  |  |</v>
       </c>
       <c r="S14" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>| L | Landscape | Paisajismo |  | |</v>
+        <v>|  |  |  |  | |</v>
       </c>
       <c r="T14" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>| L | Landscape | Paisajismo |  | | |</v>
+        <v>|  |  |  |  | | |</v>
       </c>
       <c r="U14" s="5"/>
       <c r="V14" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>| L | Landscape | Paisajismo |  | | | | | | | | | |</v>
+        <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>73</v>
-      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
@@ -9951,7 +10079,7 @@
       <c r="P15" s="5"/>
       <c r="Q15" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| M | Mechanical | Mecánica |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R15" s="5"/>
       <c r="S15" s="5"/>
@@ -9960,15 +10088,9 @@
       <c r="V15" s="5"/>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>76</v>
-      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
@@ -9983,7 +10105,7 @@
       <c r="P16" s="5"/>
       <c r="Q16" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| O | Operations | Operaciones |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R16" s="5"/>
       <c r="S16" s="5"/>
@@ -9992,15 +10114,9 @@
       <c r="V16" s="5"/>
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>79</v>
-      </c>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -10015,7 +10131,7 @@
       <c r="P17" s="5"/>
       <c r="Q17" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| P | Plumbing | Fontanería |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R17" s="5"/>
       <c r="S17" s="5"/>
@@ -10024,15 +10140,9 @@
       <c r="V17" s="5"/>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>82</v>
-      </c>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
@@ -10047,7 +10157,7 @@
       <c r="P18" s="5"/>
       <c r="Q18" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| Q | Equipment | Equipos |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R18" s="5"/>
       <c r="S18" s="5"/>
@@ -10056,15 +10166,9 @@
       <c r="V18" s="5"/>
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>85</v>
-      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
@@ -10079,7 +10183,7 @@
       <c r="P19" s="5"/>
       <c r="Q19" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| R | Resource | Recursos |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R19" s="5"/>
       <c r="S19" s="5"/>
@@ -10088,15 +10192,9 @@
       <c r="V19" s="5"/>
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>88</v>
-      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
@@ -10111,7 +10209,7 @@
       <c r="P20" s="5"/>
       <c r="Q20" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| S | Structural | Estructura |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R20" s="5"/>
       <c r="S20" s="5"/>
@@ -10120,15 +10218,9 @@
       <c r="V20" s="5"/>
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>91</v>
-      </c>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
@@ -10143,7 +10235,7 @@
       <c r="P21" s="5"/>
       <c r="Q21" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| T | Telecommunications | Telecomunicaciones |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R21" s="5"/>
       <c r="S21" s="5"/>
@@ -10152,15 +10244,9 @@
       <c r="V21" s="5"/>
     </row>
     <row r="22" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>94</v>
-      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
@@ -10175,7 +10261,7 @@
       <c r="P22" s="5"/>
       <c r="Q22" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| V | Survey / Mapping | Topografía / Cartografía |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R22" s="5"/>
       <c r="S22" s="5"/>
@@ -10184,15 +10270,9 @@
       <c r="V22" s="5"/>
     </row>
     <row r="23" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B23" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>97</v>
-      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
@@ -10207,7 +10287,7 @@
       <c r="P23" s="5"/>
       <c r="Q23" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| W | Distributed Energy | Energía distribuida |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R23" s="5"/>
       <c r="S23" s="5"/>
@@ -10216,15 +10296,9 @@
       <c r="V23" s="5"/>
     </row>
     <row r="24" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B24" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>100</v>
-      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
@@ -10239,7 +10313,7 @@
       <c r="P24" s="5"/>
       <c r="Q24" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| X | Other Disciplines | Otras disciplinas |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R24" s="5"/>
       <c r="S24" s="5"/>
@@ -10248,15 +10322,9 @@
       <c r="V24" s="5"/>
     </row>
     <row r="25" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B25" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>103</v>
-      </c>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
@@ -10271,7 +10339,7 @@
       <c r="P25" s="5"/>
       <c r="Q25" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>| Z | Contractor / Shop Drawings | Contratista / Planos de taller |</v>
+        <v>|  |  |  |</v>
       </c>
       <c r="R25" s="5"/>
       <c r="S25" s="5"/>
@@ -11804,7 +11872,7 @@
         <v>|  |  |  |</v>
       </c>
       <c r="R70" s="5" t="str">
-        <f t="shared" ref="R70:R105" si="11">_xlfn.CONCAT("| ",B70," | ",C70," | ",D70," | ",E70," |")</f>
+        <f t="shared" ref="R70:R103" si="11">_xlfn.CONCAT("| ",B70," | ",C70," | ",D70," | ",E70," |")</f>
         <v>|  |  |  |  |</v>
       </c>
       <c r="S70" s="5" t="str">
@@ -13178,4 +13246,3931 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{435D73F0-A81A-4218-A9EB-3B3DC641466C}">
+  <dimension ref="B1:V103"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="2.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="26.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="46.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="29.28515625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="6.640625" style="1" customWidth="1"/>
+    <col min="7" max="8" width="7.140625" style="1" customWidth="1"/>
+    <col min="9" max="14" width="4.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="2.7109375" style="1" customWidth="1"/>
+    <col min="16" max="20" width="74.140625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="56" style="1" customWidth="1"/>
+    <col min="22" max="22" width="74.140625" style="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B1" s="1">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B3" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="5" t="str">
+        <f>_xlfn.CONCAT("| ",B3," | ",C3," |")</f>
+        <v>| Designador | Descripción (en) |</v>
+      </c>
+      <c r="Q3" s="5" t="str">
+        <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," |")</f>
+        <v>| Designador | Descripción (en) | Descripción (es) |</v>
+      </c>
+      <c r="R3" s="5" t="str">
+        <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," |")</f>
+        <v>| Designador | Descripción (en) | Descripción (es) | A |</v>
+      </c>
+      <c r="S3" s="5" t="str">
+        <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," |",F3," |")</f>
+        <v>| Designador | Descripción (en) | Descripción (es) | A |B |</v>
+      </c>
+      <c r="T3" s="5" t="str">
+        <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," |",F3," |",G3," |")</f>
+        <v>| Designador | Descripción (en) | Descripción (es) | A |B |C |</v>
+      </c>
+      <c r="U3" s="5" t="str">
+        <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," | ",F3," | ",G3," | ",H3," |")</f>
+        <v>| Designador | Descripción (en) | Descripción (es) | A | B | C | D |</v>
+      </c>
+      <c r="V3" s="5" t="str">
+        <f t="shared" ref="V3:V14" si="0">_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," |",F3," |",G3," |",H3," |",I3," |",J3," |",K3," |",L3," |",M3," |",N3," |")</f>
+        <v>| Designador | Descripción (en) | Descripción (es) | A |B |C |D | | | | | | |</v>
+      </c>
+    </row>
+    <row r="4" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="O4" s="7"/>
+      <c r="P4" s="8" t="str">
+        <f>_xlfn.CONCAT("|",B4,"|",C4,"|")</f>
+        <v>|---|---|</v>
+      </c>
+      <c r="Q4" s="8" t="str">
+        <f>_xlfn.CONCAT("|",B4,"|",C4,"|",D4,"|")</f>
+        <v>|---|---|---|</v>
+      </c>
+      <c r="R4" s="8" t="str">
+        <f>_xlfn.CONCAT("|",B4,"|",C4,"|",D4,"|",E4,"|")</f>
+        <v>|---|---|---|---|</v>
+      </c>
+      <c r="S4" s="8" t="str">
+        <f>_xlfn.CONCAT("|",B4,"|",C4,"|",D4,"|",E4,"|",F4,"|")</f>
+        <v>|---|---|---|---|---|</v>
+      </c>
+      <c r="T4" s="5" t="str">
+        <f t="shared" ref="T4:T67" si="1">_xlfn.CONCAT("| ",B4," | ",C4," | ",D4," | ",E4," |",F4," |",G4," |")</f>
+        <v>| --- | --- | --- | --- |--- |--- |</v>
+      </c>
+      <c r="U4" s="5" t="str">
+        <f t="shared" ref="U4:U11" si="2">_xlfn.CONCAT("| ",B4," | ",C4," | ",D4," | ",E4," | ",F4," | ",G4," | ",H4," |")</f>
+        <v>| --- | --- | --- | --- | --- | --- | --- |</v>
+      </c>
+      <c r="V4" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>| --- | --- | --- | --- |--- |--- |--- |--- |--- |--- |--- |--- |--- |</v>
+      </c>
+    </row>
+    <row r="5" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5" t="str">
+        <f>_xlfn.CONCAT("| ",B5," | ",C5," |")</f>
+        <v>| A | Abandoned |</v>
+      </c>
+      <c r="Q5" s="5" t="str">
+        <f t="shared" ref="Q5:Q38" si="3">_xlfn.CONCAT("| ",B5," | ",C5," | ",D5," |")</f>
+        <v>| A | Abandoned | Abandonado |</v>
+      </c>
+      <c r="R5" s="5" t="str">
+        <f>_xlfn.CONCAT("| ",B5," | ",C5," | ",D5," | ",E5," |")</f>
+        <v>| A | Abandoned | Abandonado | ✓ |</v>
+      </c>
+      <c r="S5" s="5" t="str">
+        <f>_xlfn.CONCAT("| ",B5," | ",C5," | ",D5," | ",E5," |",F5," |")</f>
+        <v>| A | Abandoned | Abandonado | ✓ |✓ |</v>
+      </c>
+      <c r="T5" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| A | Abandoned | Abandonado | ✓ |✓ | |</v>
+      </c>
+      <c r="U5" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>| A | Abandoned | Abandonado | ✓ | ✓ |  |  |</v>
+      </c>
+      <c r="V5" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>| A | Abandoned | Abandonado | ✓ |✓ | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="6" spans="2:22" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5" t="str">
+        <f t="shared" ref="P6:P14" si="4">_xlfn.CONCAT("| ",B6," | ",C6," |")</f>
+        <v>| D | Existing to demolish |</v>
+      </c>
+      <c r="Q6" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| D | Existing to demolish | Existente para demoler |</v>
+      </c>
+      <c r="R6" s="5" t="str">
+        <f t="shared" ref="R6:R69" si="5">_xlfn.CONCAT("| ",B6," | ",C6," | ",D6," | ",E6," |")</f>
+        <v>| D | Existing to demolish | Existente para demoler | ✓ |</v>
+      </c>
+      <c r="S6" s="5" t="str">
+        <f t="shared" ref="S6:S69" si="6">_xlfn.CONCAT("| ",B6," | ",C6," | ",D6," | ",E6," |",F6," |")</f>
+        <v>| D | Existing to demolish | Existente para demoler | ✓ |✕ |</v>
+      </c>
+      <c r="T6" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| D | Existing to demolish | Existente para demoler | ✓ |✕ | |</v>
+      </c>
+      <c r="U6" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>| D | Existing to demolish | Existente para demoler | ✓ | ✕ |  |  |</v>
+      </c>
+      <c r="V6" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>| D | Existing to demolish | Existente para demoler | ✓ |✕ | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="7" spans="2:22" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>| E | Existing to remain |</v>
+      </c>
+      <c r="Q7" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| E | Existing to remain | Existente para conservar |</v>
+      </c>
+      <c r="R7" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| E | Existing to remain | Existente para conservar | ✓ |</v>
+      </c>
+      <c r="S7" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| E | Existing to remain | Existente para conservar | ✓ |✓ |</v>
+      </c>
+      <c r="T7" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| E | Existing to remain | Existente para conservar | ✓ |✓ | |</v>
+      </c>
+      <c r="U7" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>| E | Existing to remain | Existente para conservar | ✓ | ✓ |  |  |</v>
+      </c>
+      <c r="V7" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>| E | Existing to remain | Existente para conservar | ✓ |✓ | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="8" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>| ß | Future work |</v>
+      </c>
+      <c r="Q8" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| ß | Future work | Trabajo futuro |</v>
+      </c>
+      <c r="R8" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| ß | Future work | Trabajo futuro | ✓ |</v>
+      </c>
+      <c r="S8" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| ß | Future work | Trabajo futuro | ✓ |✕ |</v>
+      </c>
+      <c r="T8" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| ß | Future work | Trabajo futuro | ✓ |✕ | |</v>
+      </c>
+      <c r="U8" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>| ß | Future work | Trabajo futuro | ✓ | ✕ |  |  |</v>
+      </c>
+      <c r="V8" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>| ß | Future work | Trabajo futuro | ✓ |✕ | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="9" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>| M | Items to be moved |</v>
+      </c>
+      <c r="Q9" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| M | Items to be moved | Artículos a trasladar |</v>
+      </c>
+      <c r="R9" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| M | Items to be moved | Artículos a trasladar | ✓ |</v>
+      </c>
+      <c r="S9" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| M | Items to be moved | Artículos a trasladar | ✓ |✕ |</v>
+      </c>
+      <c r="T9" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| M | Items to be moved | Artículos a trasladar | ✓ |✕ | |</v>
+      </c>
+      <c r="U9" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>| M | Items to be moved | Artículos a trasladar | ✓ | ✕ |  |  |</v>
+      </c>
+      <c r="V9" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>| M | Items to be moved | Artículos a trasladar | ✓ |✕ | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="10" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>| N | New work |</v>
+      </c>
+      <c r="Q10" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| N | New work | Trabajo nuevo |</v>
+      </c>
+      <c r="R10" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| N | New work | Trabajo nuevo | ✓ |</v>
+      </c>
+      <c r="S10" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| N | New work | Trabajo nuevo | ✓ |✕ |</v>
+      </c>
+      <c r="T10" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| N | New work | Trabajo nuevo | ✓ |✕ | |</v>
+      </c>
+      <c r="U10" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>| N | New work | Trabajo nuevo | ✓ | ✕ |  |  |</v>
+      </c>
+      <c r="V10" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>| N | New work | Trabajo nuevo | ✓ |✕ | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="11" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>| T | Temporary work |</v>
+      </c>
+      <c r="Q11" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| T | Temporary work | Trabajo temporal |</v>
+      </c>
+      <c r="R11" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| T | Temporary work | Trabajo temporal | ✓ |</v>
+      </c>
+      <c r="S11" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| T | Temporary work | Trabajo temporal | ✓ |✓ |</v>
+      </c>
+      <c r="T11" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| T | Temporary work | Trabajo temporal | ✓ |✓ | |</v>
+      </c>
+      <c r="U11" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>| T | Temporary work | Trabajo temporal | ✓ | ✓ |  |  |</v>
+      </c>
+      <c r="V11" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>| T | Temporary work | Trabajo temporal | ✓ |✓ | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="12" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>| X | Not in contract |</v>
+      </c>
+      <c r="Q12" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| X | Not in contract | Sin contrato |</v>
+      </c>
+      <c r="R12" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| X | Not in contract | Sin contrato |  |</v>
+      </c>
+      <c r="S12" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| X | Not in contract | Sin contrato |  | |</v>
+      </c>
+      <c r="T12" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| X | Not in contract | Sin contrato |  | | |</v>
+      </c>
+      <c r="U12" s="5"/>
+      <c r="V12" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>| X | Not in contract | Sin contrato |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="13" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>| 1a9 | Phase numbers |</v>
+      </c>
+      <c r="Q13" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| 1a9 | Phase numbers | Número de fases |</v>
+      </c>
+      <c r="R13" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| 1a9 | Phase numbers | Número de fases |  |</v>
+      </c>
+      <c r="S13" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| 1a9 | Phase numbers | Número de fases |  | |</v>
+      </c>
+      <c r="T13" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| 1a9 | Phase numbers | Número de fases |  | | |</v>
+      </c>
+      <c r="U13" s="5"/>
+      <c r="V13" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>| 1a9 | Phase numbers | Número de fases |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="14" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q14" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R14" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S14" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T14" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U14" s="5"/>
+      <c r="V14" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="15" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R15" s="5"/>
+      <c r="S15" s="5"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="5"/>
+      <c r="V15" s="5"/>
+    </row>
+    <row r="16" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R16" s="5"/>
+      <c r="S16" s="5"/>
+      <c r="T16" s="5"/>
+      <c r="U16" s="5"/>
+      <c r="V16" s="5"/>
+    </row>
+    <row r="17" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R17" s="5"/>
+      <c r="S17" s="5"/>
+      <c r="T17" s="5"/>
+      <c r="U17" s="5"/>
+      <c r="V17" s="5"/>
+    </row>
+    <row r="18" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R18" s="5"/>
+      <c r="S18" s="5"/>
+      <c r="T18" s="5"/>
+      <c r="U18" s="5"/>
+      <c r="V18" s="5"/>
+    </row>
+    <row r="19" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R19" s="5"/>
+      <c r="S19" s="5"/>
+      <c r="T19" s="5"/>
+      <c r="U19" s="5"/>
+      <c r="V19" s="5"/>
+    </row>
+    <row r="20" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R20" s="5"/>
+      <c r="S20" s="5"/>
+      <c r="T20" s="5"/>
+      <c r="U20" s="5"/>
+      <c r="V20" s="5"/>
+    </row>
+    <row r="21" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R21" s="5"/>
+      <c r="S21" s="5"/>
+      <c r="T21" s="5"/>
+      <c r="U21" s="5"/>
+      <c r="V21" s="5"/>
+    </row>
+    <row r="22" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R22" s="5"/>
+      <c r="S22" s="5"/>
+      <c r="T22" s="5"/>
+      <c r="U22" s="5"/>
+      <c r="V22" s="5"/>
+    </row>
+    <row r="23" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R23" s="5"/>
+      <c r="S23" s="5"/>
+      <c r="T23" s="5"/>
+      <c r="U23" s="5"/>
+      <c r="V23" s="5"/>
+    </row>
+    <row r="24" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R24" s="5"/>
+      <c r="S24" s="5"/>
+      <c r="T24" s="5"/>
+      <c r="U24" s="5"/>
+      <c r="V24" s="5"/>
+    </row>
+    <row r="25" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R25" s="5"/>
+      <c r="S25" s="5"/>
+      <c r="T25" s="5"/>
+      <c r="U25" s="5"/>
+      <c r="V25" s="5"/>
+    </row>
+    <row r="26" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="4"/>
+      <c r="N26" s="4"/>
+      <c r="O26" s="4"/>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R26" s="5"/>
+      <c r="S26" s="5"/>
+      <c r="T26" s="5"/>
+      <c r="U26" s="5"/>
+      <c r="V26" s="5"/>
+    </row>
+    <row r="27" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="4"/>
+      <c r="N27" s="4"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R27" s="5"/>
+      <c r="S27" s="5"/>
+      <c r="T27" s="5"/>
+      <c r="U27" s="5"/>
+      <c r="V27" s="5"/>
+    </row>
+    <row r="28" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="4"/>
+      <c r="N28" s="4"/>
+      <c r="O28" s="4"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R28" s="5"/>
+      <c r="S28" s="5"/>
+      <c r="T28" s="5"/>
+      <c r="U28" s="5"/>
+      <c r="V28" s="5"/>
+    </row>
+    <row r="29" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="4"/>
+      <c r="N29" s="4"/>
+      <c r="O29" s="4"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R29" s="5"/>
+      <c r="S29" s="5"/>
+      <c r="T29" s="5"/>
+      <c r="U29" s="5"/>
+      <c r="V29" s="5"/>
+    </row>
+    <row r="30" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="4"/>
+      <c r="O30" s="4"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R30" s="5"/>
+      <c r="S30" s="5"/>
+      <c r="T30" s="5"/>
+      <c r="U30" s="5"/>
+      <c r="V30" s="5"/>
+    </row>
+    <row r="31" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="4"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R31" s="5"/>
+      <c r="S31" s="5"/>
+      <c r="T31" s="5"/>
+      <c r="U31" s="5"/>
+      <c r="V31" s="5"/>
+    </row>
+    <row r="32" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B32" s="5"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="4"/>
+      <c r="O32" s="4"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R32" s="5"/>
+      <c r="S32" s="5"/>
+      <c r="T32" s="5"/>
+      <c r="U32" s="5"/>
+      <c r="V32" s="5"/>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B33" s="5"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="4"/>
+      <c r="O33" s="4"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R33" s="5"/>
+      <c r="S33" s="5"/>
+      <c r="T33" s="5"/>
+      <c r="U33" s="5"/>
+      <c r="V33" s="5"/>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="4"/>
+      <c r="P34" s="5"/>
+      <c r="Q34" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R34" s="5"/>
+      <c r="S34" s="5"/>
+      <c r="T34" s="5"/>
+      <c r="U34" s="5"/>
+      <c r="V34" s="5"/>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="4"/>
+      <c r="O35" s="4"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R35" s="5"/>
+      <c r="S35" s="5"/>
+      <c r="T35" s="5"/>
+      <c r="U35" s="5"/>
+      <c r="V35" s="5"/>
+    </row>
+    <row r="36" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="4"/>
+      <c r="O36" s="4"/>
+      <c r="P36" s="5"/>
+      <c r="Q36" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R36" s="5"/>
+      <c r="S36" s="5"/>
+      <c r="T36" s="5"/>
+      <c r="U36" s="5"/>
+      <c r="V36" s="5"/>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B37" s="5"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="4"/>
+      <c r="O37" s="4"/>
+      <c r="P37" s="5"/>
+      <c r="Q37" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R37" s="5"/>
+      <c r="S37" s="5"/>
+      <c r="T37" s="5"/>
+      <c r="U37" s="5"/>
+      <c r="V37" s="5"/>
+    </row>
+    <row r="38" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="4"/>
+      <c r="P38" s="5"/>
+      <c r="Q38" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R38" s="5"/>
+      <c r="S38" s="5"/>
+      <c r="T38" s="5"/>
+      <c r="U38" s="5"/>
+      <c r="V38" s="5"/>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="4"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="5"/>
+      <c r="R39" s="5"/>
+      <c r="S39" s="5"/>
+      <c r="T39" s="5"/>
+      <c r="U39" s="5"/>
+      <c r="V39" s="5"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="4"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="4"/>
+      <c r="P40" s="5"/>
+      <c r="Q40" s="5"/>
+      <c r="R40" s="5"/>
+      <c r="S40" s="5"/>
+      <c r="T40" s="5"/>
+      <c r="U40" s="5"/>
+      <c r="V40" s="5"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="4"/>
+      <c r="P41" s="5"/>
+      <c r="Q41" s="5"/>
+      <c r="R41" s="5"/>
+      <c r="S41" s="5"/>
+      <c r="T41" s="5"/>
+      <c r="U41" s="5"/>
+      <c r="V41" s="5"/>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="4"/>
+      <c r="N42" s="4"/>
+      <c r="O42" s="4"/>
+      <c r="P42" s="5"/>
+      <c r="Q42" s="5"/>
+      <c r="R42" s="5"/>
+      <c r="S42" s="5"/>
+      <c r="T42" s="5"/>
+      <c r="U42" s="5"/>
+      <c r="V42" s="5"/>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="4"/>
+      <c r="N43" s="4"/>
+      <c r="O43" s="4"/>
+      <c r="P43" s="5"/>
+      <c r="Q43" s="5"/>
+      <c r="R43" s="5"/>
+      <c r="S43" s="5"/>
+      <c r="T43" s="5"/>
+      <c r="U43" s="5"/>
+      <c r="V43" s="5"/>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="4"/>
+      <c r="N44" s="4"/>
+      <c r="O44" s="4"/>
+      <c r="P44" s="5"/>
+      <c r="Q44" s="5"/>
+      <c r="R44" s="5"/>
+      <c r="S44" s="5"/>
+      <c r="T44" s="5"/>
+      <c r="U44" s="5"/>
+      <c r="V44" s="5"/>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="4"/>
+      <c r="N45" s="4"/>
+      <c r="O45" s="4"/>
+      <c r="P45" s="5" t="str">
+        <f t="shared" ref="P45:P103" si="7">_xlfn.CONCAT("| ",B45," | ",C45," |")</f>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q45" s="5" t="str">
+        <f t="shared" ref="Q45:Q103" si="8">_xlfn.CONCAT("| ",B45," | ",C45," | ",D45," |")</f>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R45" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S45" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T45" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U45" s="5"/>
+      <c r="V45" s="5" t="str">
+        <f t="shared" ref="V45:V103" si="9">_xlfn.CONCAT("| ",B45," | ",C45," | ",D45," | ",E45," |",F45," |",G45," |",H45," |",I45," |",J45," |",K45," |",L45," |",M45," |",N45," |")</f>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
+      <c r="M46" s="4"/>
+      <c r="N46" s="4"/>
+      <c r="O46" s="4"/>
+      <c r="P46" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q46" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R46" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S46" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T46" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U46" s="5"/>
+      <c r="V46" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="4"/>
+      <c r="N47" s="4"/>
+      <c r="O47" s="4"/>
+      <c r="P47" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q47" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R47" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S47" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T47" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U47" s="5"/>
+      <c r="V47" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="4"/>
+      <c r="N48" s="4"/>
+      <c r="O48" s="4"/>
+      <c r="P48" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q48" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R48" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S48" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T48" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U48" s="5"/>
+      <c r="V48" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="49" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="4"/>
+      <c r="N49" s="4"/>
+      <c r="O49" s="4"/>
+      <c r="P49" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q49" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R49" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S49" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T49" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U49" s="5"/>
+      <c r="V49" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="50" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="4"/>
+      <c r="N50" s="4"/>
+      <c r="O50" s="4"/>
+      <c r="P50" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q50" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R50" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S50" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T50" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U50" s="5"/>
+      <c r="V50" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="51" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="4"/>
+      <c r="N51" s="4"/>
+      <c r="O51" s="4"/>
+      <c r="P51" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q51" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R51" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S51" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T51" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U51" s="5"/>
+      <c r="V51" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="52" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="4"/>
+      <c r="L52" s="4"/>
+      <c r="M52" s="4"/>
+      <c r="N52" s="4"/>
+      <c r="O52" s="4"/>
+      <c r="P52" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q52" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R52" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S52" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T52" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U52" s="5"/>
+      <c r="V52" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="53" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="4"/>
+      <c r="N53" s="4"/>
+      <c r="O53" s="4"/>
+      <c r="P53" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q53" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R53" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S53" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T53" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U53" s="5"/>
+      <c r="V53" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="54" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
+      <c r="K54" s="4"/>
+      <c r="L54" s="4"/>
+      <c r="M54" s="4"/>
+      <c r="N54" s="4"/>
+      <c r="O54" s="4"/>
+      <c r="P54" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q54" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R54" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S54" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T54" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U54" s="5"/>
+      <c r="V54" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="55" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="4"/>
+      <c r="L55" s="4"/>
+      <c r="M55" s="4"/>
+      <c r="N55" s="4"/>
+      <c r="O55" s="4"/>
+      <c r="P55" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q55" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R55" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S55" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T55" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U55" s="5"/>
+      <c r="V55" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="56" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
+      <c r="L56" s="4"/>
+      <c r="M56" s="4"/>
+      <c r="N56" s="4"/>
+      <c r="O56" s="4"/>
+      <c r="P56" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q56" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R56" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S56" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T56" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U56" s="5"/>
+      <c r="V56" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="57" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4"/>
+      <c r="L57" s="4"/>
+      <c r="M57" s="4"/>
+      <c r="N57" s="4"/>
+      <c r="O57" s="4"/>
+      <c r="P57" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q57" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R57" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S57" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T57" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U57" s="5"/>
+      <c r="V57" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="58" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="4"/>
+      <c r="L58" s="4"/>
+      <c r="M58" s="4"/>
+      <c r="N58" s="4"/>
+      <c r="O58" s="4"/>
+      <c r="P58" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q58" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R58" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S58" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T58" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U58" s="5"/>
+      <c r="V58" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="59" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B59" s="4"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
+      <c r="K59" s="4"/>
+      <c r="L59" s="4"/>
+      <c r="M59" s="4"/>
+      <c r="N59" s="4"/>
+      <c r="O59" s="4"/>
+      <c r="P59" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q59" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R59" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S59" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T59" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U59" s="5"/>
+      <c r="V59" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="60" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="4"/>
+      <c r="L60" s="4"/>
+      <c r="M60" s="4"/>
+      <c r="N60" s="4"/>
+      <c r="O60" s="4"/>
+      <c r="P60" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q60" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R60" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S60" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T60" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U60" s="5"/>
+      <c r="V60" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="61" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="4"/>
+      <c r="L61" s="4"/>
+      <c r="M61" s="4"/>
+      <c r="N61" s="4"/>
+      <c r="O61" s="4"/>
+      <c r="P61" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q61" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R61" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S61" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T61" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U61" s="5"/>
+      <c r="V61" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="62" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4"/>
+      <c r="L62" s="4"/>
+      <c r="M62" s="4"/>
+      <c r="N62" s="4"/>
+      <c r="O62" s="4"/>
+      <c r="P62" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q62" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R62" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S62" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T62" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U62" s="5"/>
+      <c r="V62" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="63" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="4"/>
+      <c r="L63" s="4"/>
+      <c r="M63" s="4"/>
+      <c r="N63" s="4"/>
+      <c r="O63" s="4"/>
+      <c r="P63" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q63" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R63" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S63" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T63" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U63" s="5"/>
+      <c r="V63" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="64" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="4"/>
+      <c r="L64" s="4"/>
+      <c r="M64" s="4"/>
+      <c r="N64" s="4"/>
+      <c r="O64" s="4"/>
+      <c r="P64" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q64" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R64" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S64" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T64" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U64" s="5"/>
+      <c r="V64" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="4"/>
+      <c r="L65" s="4"/>
+      <c r="M65" s="4"/>
+      <c r="N65" s="4"/>
+      <c r="O65" s="4"/>
+      <c r="P65" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q65" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R65" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S65" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T65" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U65" s="5"/>
+      <c r="V65" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="4"/>
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="4"/>
+      <c r="L66" s="4"/>
+      <c r="M66" s="4"/>
+      <c r="N66" s="4"/>
+      <c r="O66" s="4"/>
+      <c r="P66" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q66" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R66" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S66" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T66" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U66" s="5"/>
+      <c r="V66" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="4"/>
+      <c r="L67" s="4"/>
+      <c r="M67" s="4"/>
+      <c r="N67" s="4"/>
+      <c r="O67" s="4"/>
+      <c r="P67" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q67" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R67" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S67" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T67" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U67" s="5"/>
+      <c r="V67" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="4"/>
+      <c r="L68" s="4"/>
+      <c r="M68" s="4"/>
+      <c r="N68" s="4"/>
+      <c r="O68" s="4"/>
+      <c r="P68" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q68" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R68" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S68" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T68" s="5" t="str">
+        <f t="shared" ref="T68:T103" si="10">_xlfn.CONCAT("| ",B68," | ",C68," | ",D68," | ",E68," |",F68," |",G68," |")</f>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U68" s="5"/>
+      <c r="V68" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="4"/>
+      <c r="L69" s="4"/>
+      <c r="M69" s="4"/>
+      <c r="N69" s="4"/>
+      <c r="O69" s="4"/>
+      <c r="P69" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q69" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R69" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S69" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T69" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U69" s="5"/>
+      <c r="V69" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
+      <c r="J70" s="4"/>
+      <c r="K70" s="4"/>
+      <c r="L70" s="4"/>
+      <c r="M70" s="4"/>
+      <c r="N70" s="4"/>
+      <c r="O70" s="4"/>
+      <c r="P70" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q70" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R70" s="5" t="str">
+        <f t="shared" ref="R70:R103" si="11">_xlfn.CONCAT("| ",B70," | ",C70," | ",D70," | ",E70," |")</f>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S70" s="5" t="str">
+        <f t="shared" ref="S70:S103" si="12">_xlfn.CONCAT("| ",B70," | ",C70," | ",D70," | ",E70," |",F70," |")</f>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T70" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U70" s="5"/>
+      <c r="V70" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B71" s="4"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="4"/>
+      <c r="L71" s="4"/>
+      <c r="M71" s="4"/>
+      <c r="N71" s="4"/>
+      <c r="O71" s="4"/>
+      <c r="P71" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q71" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R71" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S71" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T71" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U71" s="5"/>
+      <c r="V71" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="4"/>
+      <c r="M72" s="4"/>
+      <c r="N72" s="4"/>
+      <c r="O72" s="4"/>
+      <c r="P72" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q72" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R72" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S72" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T72" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U72" s="5"/>
+      <c r="V72" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B73" s="4"/>
+      <c r="C73" s="4"/>
+      <c r="D73" s="4"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+      <c r="G73" s="4"/>
+      <c r="H73" s="4"/>
+      <c r="I73" s="4"/>
+      <c r="J73" s="4"/>
+      <c r="K73" s="4"/>
+      <c r="L73" s="4"/>
+      <c r="M73" s="4"/>
+      <c r="N73" s="4"/>
+      <c r="O73" s="4"/>
+      <c r="P73" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q73" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R73" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S73" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T73" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U73" s="5"/>
+      <c r="V73" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4"/>
+      <c r="M74" s="4"/>
+      <c r="N74" s="4"/>
+      <c r="O74" s="4"/>
+      <c r="P74" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q74" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R74" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S74" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T74" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U74" s="5"/>
+      <c r="V74" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="4"/>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+      <c r="G75" s="4"/>
+      <c r="H75" s="4"/>
+      <c r="I75" s="4"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="4"/>
+      <c r="L75" s="4"/>
+      <c r="M75" s="4"/>
+      <c r="N75" s="4"/>
+      <c r="O75" s="4"/>
+      <c r="P75" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q75" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R75" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S75" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T75" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U75" s="5"/>
+      <c r="V75" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B76" s="4"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+      <c r="G76" s="4"/>
+      <c r="H76" s="4"/>
+      <c r="I76" s="4"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="4"/>
+      <c r="L76" s="4"/>
+      <c r="M76" s="4"/>
+      <c r="N76" s="4"/>
+      <c r="O76" s="4"/>
+      <c r="P76" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q76" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R76" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S76" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T76" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U76" s="5"/>
+      <c r="V76" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="4"/>
+      <c r="I77" s="4"/>
+      <c r="J77" s="4"/>
+      <c r="K77" s="4"/>
+      <c r="L77" s="4"/>
+      <c r="M77" s="4"/>
+      <c r="N77" s="4"/>
+      <c r="O77" s="4"/>
+      <c r="P77" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q77" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R77" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S77" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T77" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U77" s="5"/>
+      <c r="V77" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="78" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B78" s="4"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="4"/>
+      <c r="I78" s="4"/>
+      <c r="J78" s="4"/>
+      <c r="K78" s="4"/>
+      <c r="L78" s="4"/>
+      <c r="M78" s="4"/>
+      <c r="N78" s="4"/>
+      <c r="O78" s="4"/>
+      <c r="P78" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q78" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R78" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S78" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T78" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U78" s="5"/>
+      <c r="V78" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B79" s="4"/>
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+      <c r="I79" s="4"/>
+      <c r="J79" s="4"/>
+      <c r="K79" s="4"/>
+      <c r="L79" s="4"/>
+      <c r="M79" s="4"/>
+      <c r="N79" s="4"/>
+      <c r="O79" s="4"/>
+      <c r="P79" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q79" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R79" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S79" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T79" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U79" s="5"/>
+      <c r="V79" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="80" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B80" s="4"/>
+      <c r="C80" s="4"/>
+      <c r="D80" s="4"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+      <c r="G80" s="4"/>
+      <c r="H80" s="4"/>
+      <c r="I80" s="4"/>
+      <c r="J80" s="4"/>
+      <c r="K80" s="4"/>
+      <c r="L80" s="4"/>
+      <c r="M80" s="4"/>
+      <c r="N80" s="4"/>
+      <c r="O80" s="4"/>
+      <c r="P80" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q80" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R80" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S80" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T80" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U80" s="5"/>
+      <c r="V80" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="81" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B81" s="4"/>
+      <c r="C81" s="4"/>
+      <c r="D81" s="4"/>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
+      <c r="G81" s="4"/>
+      <c r="H81" s="4"/>
+      <c r="I81" s="4"/>
+      <c r="J81" s="4"/>
+      <c r="K81" s="4"/>
+      <c r="L81" s="4"/>
+      <c r="M81" s="4"/>
+      <c r="N81" s="4"/>
+      <c r="O81" s="4"/>
+      <c r="P81" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q81" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R81" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S81" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T81" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U81" s="5"/>
+      <c r="V81" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="82" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B82" s="4"/>
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4"/>
+      <c r="I82" s="4"/>
+      <c r="J82" s="4"/>
+      <c r="K82" s="4"/>
+      <c r="L82" s="4"/>
+      <c r="M82" s="4"/>
+      <c r="N82" s="4"/>
+      <c r="O82" s="4"/>
+      <c r="P82" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q82" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R82" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S82" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T82" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U82" s="5"/>
+      <c r="V82" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="83" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B83" s="4"/>
+      <c r="C83" s="4"/>
+      <c r="D83" s="4"/>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+      <c r="G83" s="4"/>
+      <c r="H83" s="4"/>
+      <c r="I83" s="4"/>
+      <c r="J83" s="4"/>
+      <c r="K83" s="4"/>
+      <c r="L83" s="4"/>
+      <c r="M83" s="4"/>
+      <c r="N83" s="4"/>
+      <c r="O83" s="4"/>
+      <c r="P83" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q83" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R83" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S83" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T83" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U83" s="5"/>
+      <c r="V83" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="84" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B84" s="4"/>
+      <c r="C84" s="4"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="4"/>
+      <c r="H84" s="4"/>
+      <c r="I84" s="4"/>
+      <c r="J84" s="4"/>
+      <c r="K84" s="4"/>
+      <c r="L84" s="4"/>
+      <c r="M84" s="4"/>
+      <c r="N84" s="4"/>
+      <c r="O84" s="4"/>
+      <c r="P84" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q84" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R84" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S84" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T84" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U84" s="5"/>
+      <c r="V84" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="85" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B85" s="4"/>
+      <c r="C85" s="4"/>
+      <c r="D85" s="4"/>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+      <c r="G85" s="4"/>
+      <c r="H85" s="4"/>
+      <c r="I85" s="4"/>
+      <c r="J85" s="4"/>
+      <c r="K85" s="4"/>
+      <c r="L85" s="4"/>
+      <c r="M85" s="4"/>
+      <c r="N85" s="4"/>
+      <c r="O85" s="4"/>
+      <c r="P85" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q85" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R85" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S85" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T85" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U85" s="5"/>
+      <c r="V85" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="86" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B86" s="4"/>
+      <c r="C86" s="4"/>
+      <c r="D86" s="4"/>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+      <c r="G86" s="4"/>
+      <c r="H86" s="4"/>
+      <c r="I86" s="4"/>
+      <c r="J86" s="4"/>
+      <c r="K86" s="4"/>
+      <c r="L86" s="4"/>
+      <c r="M86" s="4"/>
+      <c r="N86" s="4"/>
+      <c r="O86" s="4"/>
+      <c r="P86" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q86" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R86" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S86" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T86" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U86" s="5"/>
+      <c r="V86" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="87" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B87" s="4"/>
+      <c r="C87" s="4"/>
+      <c r="D87" s="4"/>
+      <c r="E87" s="4"/>
+      <c r="F87" s="4"/>
+      <c r="G87" s="4"/>
+      <c r="H87" s="4"/>
+      <c r="I87" s="4"/>
+      <c r="J87" s="4"/>
+      <c r="K87" s="4"/>
+      <c r="L87" s="4"/>
+      <c r="M87" s="4"/>
+      <c r="N87" s="4"/>
+      <c r="O87" s="4"/>
+      <c r="P87" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q87" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R87" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S87" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T87" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U87" s="5"/>
+      <c r="V87" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="88" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B88" s="4"/>
+      <c r="C88" s="4"/>
+      <c r="D88" s="4"/>
+      <c r="E88" s="4"/>
+      <c r="F88" s="4"/>
+      <c r="G88" s="4"/>
+      <c r="H88" s="4"/>
+      <c r="I88" s="4"/>
+      <c r="J88" s="4"/>
+      <c r="K88" s="4"/>
+      <c r="L88" s="4"/>
+      <c r="M88" s="4"/>
+      <c r="N88" s="4"/>
+      <c r="O88" s="4"/>
+      <c r="P88" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q88" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R88" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S88" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T88" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U88" s="5"/>
+      <c r="V88" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="89" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B89" s="4"/>
+      <c r="C89" s="4"/>
+      <c r="D89" s="4"/>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4"/>
+      <c r="G89" s="4"/>
+      <c r="H89" s="4"/>
+      <c r="I89" s="4"/>
+      <c r="J89" s="4"/>
+      <c r="K89" s="4"/>
+      <c r="L89" s="4"/>
+      <c r="M89" s="4"/>
+      <c r="N89" s="4"/>
+      <c r="O89" s="4"/>
+      <c r="P89" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q89" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R89" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S89" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T89" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U89" s="5"/>
+      <c r="V89" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="90" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B90" s="4"/>
+      <c r="C90" s="4"/>
+      <c r="D90" s="4"/>
+      <c r="E90" s="4"/>
+      <c r="F90" s="4"/>
+      <c r="G90" s="4"/>
+      <c r="H90" s="4"/>
+      <c r="I90" s="4"/>
+      <c r="J90" s="4"/>
+      <c r="K90" s="4"/>
+      <c r="L90" s="4"/>
+      <c r="M90" s="4"/>
+      <c r="N90" s="4"/>
+      <c r="O90" s="4"/>
+      <c r="P90" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q90" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R90" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S90" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T90" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U90" s="5"/>
+      <c r="V90" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="91" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B91" s="4"/>
+      <c r="C91" s="4"/>
+      <c r="D91" s="4"/>
+      <c r="E91" s="4"/>
+      <c r="F91" s="4"/>
+      <c r="G91" s="4"/>
+      <c r="H91" s="4"/>
+      <c r="I91" s="4"/>
+      <c r="J91" s="4"/>
+      <c r="K91" s="4"/>
+      <c r="L91" s="4"/>
+      <c r="M91" s="4"/>
+      <c r="N91" s="4"/>
+      <c r="O91" s="4"/>
+      <c r="P91" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q91" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R91" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S91" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T91" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U91" s="5"/>
+      <c r="V91" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="92" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B92" s="4"/>
+      <c r="C92" s="4"/>
+      <c r="D92" s="4"/>
+      <c r="E92" s="4"/>
+      <c r="F92" s="4"/>
+      <c r="G92" s="4"/>
+      <c r="H92" s="4"/>
+      <c r="I92" s="4"/>
+      <c r="J92" s="4"/>
+      <c r="K92" s="4"/>
+      <c r="L92" s="4"/>
+      <c r="M92" s="4"/>
+      <c r="N92" s="4"/>
+      <c r="O92" s="4"/>
+      <c r="P92" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q92" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R92" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S92" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T92" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U92" s="5"/>
+      <c r="V92" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="93" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B93" s="4"/>
+      <c r="C93" s="4"/>
+      <c r="D93" s="4"/>
+      <c r="E93" s="4"/>
+      <c r="F93" s="4"/>
+      <c r="G93" s="4"/>
+      <c r="H93" s="4"/>
+      <c r="I93" s="4"/>
+      <c r="J93" s="4"/>
+      <c r="K93" s="4"/>
+      <c r="L93" s="4"/>
+      <c r="M93" s="4"/>
+      <c r="N93" s="4"/>
+      <c r="O93" s="4"/>
+      <c r="P93" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q93" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R93" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S93" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T93" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U93" s="5"/>
+      <c r="V93" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="94" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B94" s="4"/>
+      <c r="C94" s="4"/>
+      <c r="D94" s="4"/>
+      <c r="E94" s="4"/>
+      <c r="F94" s="4"/>
+      <c r="G94" s="4"/>
+      <c r="H94" s="4"/>
+      <c r="I94" s="4"/>
+      <c r="J94" s="4"/>
+      <c r="K94" s="4"/>
+      <c r="L94" s="4"/>
+      <c r="M94" s="4"/>
+      <c r="N94" s="4"/>
+      <c r="O94" s="4"/>
+      <c r="P94" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q94" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R94" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S94" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T94" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U94" s="5"/>
+      <c r="V94" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="95" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B95" s="4"/>
+      <c r="C95" s="4"/>
+      <c r="D95" s="4"/>
+      <c r="E95" s="4"/>
+      <c r="F95" s="4"/>
+      <c r="G95" s="4"/>
+      <c r="H95" s="4"/>
+      <c r="I95" s="4"/>
+      <c r="J95" s="4"/>
+      <c r="K95" s="4"/>
+      <c r="L95" s="4"/>
+      <c r="M95" s="4"/>
+      <c r="N95" s="4"/>
+      <c r="O95" s="4"/>
+      <c r="P95" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q95" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R95" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S95" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T95" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U95" s="5"/>
+      <c r="V95" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="96" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B96" s="4"/>
+      <c r="C96" s="4"/>
+      <c r="D96" s="4"/>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4"/>
+      <c r="G96" s="4"/>
+      <c r="H96" s="4"/>
+      <c r="I96" s="4"/>
+      <c r="J96" s="4"/>
+      <c r="K96" s="4"/>
+      <c r="L96" s="4"/>
+      <c r="M96" s="4"/>
+      <c r="N96" s="4"/>
+      <c r="O96" s="4"/>
+      <c r="P96" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q96" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R96" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S96" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T96" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U96" s="5"/>
+      <c r="V96" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="97" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B97" s="4"/>
+      <c r="C97" s="4"/>
+      <c r="D97" s="4"/>
+      <c r="E97" s="4"/>
+      <c r="F97" s="4"/>
+      <c r="G97" s="4"/>
+      <c r="H97" s="4"/>
+      <c r="I97" s="4"/>
+      <c r="J97" s="4"/>
+      <c r="K97" s="4"/>
+      <c r="L97" s="4"/>
+      <c r="M97" s="4"/>
+      <c r="N97" s="4"/>
+      <c r="O97" s="4"/>
+      <c r="P97" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q97" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R97" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S97" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T97" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U97" s="5"/>
+      <c r="V97" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="98" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B98" s="4"/>
+      <c r="C98" s="4"/>
+      <c r="D98" s="4"/>
+      <c r="E98" s="4"/>
+      <c r="F98" s="4"/>
+      <c r="G98" s="4"/>
+      <c r="H98" s="4"/>
+      <c r="I98" s="4"/>
+      <c r="J98" s="4"/>
+      <c r="K98" s="4"/>
+      <c r="L98" s="4"/>
+      <c r="M98" s="4"/>
+      <c r="N98" s="4"/>
+      <c r="O98" s="4"/>
+      <c r="P98" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q98" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R98" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S98" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T98" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U98" s="5"/>
+      <c r="V98" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="99" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B99" s="4"/>
+      <c r="C99" s="4"/>
+      <c r="D99" s="4"/>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4"/>
+      <c r="G99" s="4"/>
+      <c r="H99" s="4"/>
+      <c r="I99" s="4"/>
+      <c r="J99" s="4"/>
+      <c r="K99" s="4"/>
+      <c r="L99" s="4"/>
+      <c r="M99" s="4"/>
+      <c r="N99" s="4"/>
+      <c r="O99" s="4"/>
+      <c r="P99" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q99" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R99" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S99" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T99" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U99" s="5"/>
+      <c r="V99" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="100" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B100" s="4"/>
+      <c r="C100" s="4"/>
+      <c r="D100" s="4"/>
+      <c r="E100" s="4"/>
+      <c r="F100" s="4"/>
+      <c r="G100" s="4"/>
+      <c r="H100" s="4"/>
+      <c r="I100" s="4"/>
+      <c r="J100" s="4"/>
+      <c r="K100" s="4"/>
+      <c r="L100" s="4"/>
+      <c r="M100" s="4"/>
+      <c r="N100" s="4"/>
+      <c r="O100" s="4"/>
+      <c r="P100" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q100" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R100" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S100" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T100" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U100" s="5"/>
+      <c r="V100" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="101" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B101" s="4"/>
+      <c r="C101" s="4"/>
+      <c r="D101" s="4"/>
+      <c r="E101" s="4"/>
+      <c r="F101" s="4"/>
+      <c r="G101" s="4"/>
+      <c r="H101" s="4"/>
+      <c r="I101" s="4"/>
+      <c r="J101" s="4"/>
+      <c r="K101" s="4"/>
+      <c r="L101" s="4"/>
+      <c r="M101" s="4"/>
+      <c r="N101" s="4"/>
+      <c r="O101" s="4"/>
+      <c r="P101" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q101" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R101" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S101" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T101" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U101" s="5"/>
+      <c r="V101" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="102" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B102" s="4"/>
+      <c r="C102" s="4"/>
+      <c r="D102" s="4"/>
+      <c r="E102" s="4"/>
+      <c r="F102" s="4"/>
+      <c r="G102" s="4"/>
+      <c r="H102" s="4"/>
+      <c r="I102" s="4"/>
+      <c r="J102" s="4"/>
+      <c r="K102" s="4"/>
+      <c r="L102" s="4"/>
+      <c r="M102" s="4"/>
+      <c r="N102" s="4"/>
+      <c r="O102" s="4"/>
+      <c r="P102" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q102" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R102" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S102" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T102" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U102" s="5"/>
+      <c r="V102" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="103" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B103" s="4"/>
+      <c r="C103" s="4"/>
+      <c r="D103" s="4"/>
+      <c r="E103" s="4"/>
+      <c r="F103" s="4"/>
+      <c r="G103" s="4"/>
+      <c r="H103" s="4"/>
+      <c r="I103" s="4"/>
+      <c r="J103" s="4"/>
+      <c r="K103" s="4"/>
+      <c r="L103" s="4"/>
+      <c r="M103" s="4"/>
+      <c r="N103" s="4"/>
+      <c r="O103" s="4"/>
+      <c r="P103" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>|  |  |</v>
+      </c>
+      <c r="Q103" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>|  |  |  |</v>
+      </c>
+      <c r="R103" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>|  |  |  |  |</v>
+      </c>
+      <c r="S103" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>|  |  |  |  | |</v>
+      </c>
+      <c r="T103" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>|  |  |  |  | | |</v>
+      </c>
+      <c r="U103" s="5"/>
+      <c r="V103" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>|  |  |  |  | | | | | | | | | |</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/file/temp/ExcelTableToMarkDownSample.xlsx
+++ b/file/temp/ExcelTableToMarkDownSample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\D_SSD2TB\R.DAPC\file\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A61A59-E5FD-4EA3-A716-E5F4733968C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8204DCFC-3FA7-4729-BA42-346F1217FD5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="3" xr2:uid="{D94F812B-BC61-4A22-9692-634766FE0D40}"/>
   </bookViews>
@@ -16,12 +16,14 @@
     <sheet name="Sample" sheetId="1" r:id="rId1"/>
     <sheet name="LayerL1" sheetId="6" r:id="rId2"/>
     <sheet name="LayerL2" sheetId="7" r:id="rId3"/>
-    <sheet name="LayerL2 (2)" sheetId="8" r:id="rId4"/>
+    <sheet name="Group" sheetId="9" r:id="rId4"/>
+    <sheet name="Estado" sheetId="8" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_Toc107986980" localSheetId="4">Estado!$B$9</definedName>
+    <definedName name="_Toc107986980" localSheetId="3">Group!$B$9</definedName>
     <definedName name="_Toc107986980" localSheetId="1">LayerL1!$B$9</definedName>
     <definedName name="_Toc107986980" localSheetId="2">LayerL2!$B$9</definedName>
-    <definedName name="_Toc107986980" localSheetId="3">'LayerL2 (2)'!$B$9</definedName>
     <definedName name="_Toc107986980" localSheetId="0">Sample!$B$9</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -44,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="991" uniqueCount="766">
   <si>
     <t>Creación de tablas en formato .md</t>
   </si>
@@ -494,6 +496,1854 @@
   </si>
   <si>
     <t>ß</t>
+  </si>
+  <si>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>ED</t>
+  </si>
+  <si>
+    <t>Electrical Demolition</t>
+  </si>
+  <si>
+    <t>Demolición eléctrica</t>
+  </si>
+  <si>
+    <t>EI</t>
+  </si>
+  <si>
+    <t>Electrical Instrumentation</t>
+  </si>
+  <si>
+    <t>Instrumentación eléctrica</t>
+  </si>
+  <si>
+    <t>EJ</t>
+  </si>
+  <si>
+    <t>EK</t>
+  </si>
+  <si>
+    <t>EL</t>
+  </si>
+  <si>
+    <t>Electrical Lighting</t>
+  </si>
+  <si>
+    <t>Iluminación eléctrica</t>
+  </si>
+  <si>
+    <t>EP</t>
+  </si>
+  <si>
+    <t>Electrical Power</t>
+  </si>
+  <si>
+    <t>Energía eléctrica</t>
+  </si>
+  <si>
+    <t>ES</t>
+  </si>
+  <si>
+    <t>Electrical Site</t>
+  </si>
+  <si>
+    <t>Sitio eléctrico</t>
+  </si>
+  <si>
+    <t>ET</t>
+  </si>
+  <si>
+    <t>Electrical Telecommunications</t>
+  </si>
+  <si>
+    <t>Telecomunicaciones eléctricas</t>
+  </si>
+  <si>
+    <t>EY</t>
+  </si>
+  <si>
+    <t>Electrical Auxiliary Systems</t>
+  </si>
+  <si>
+    <t>Sistemas auxiliares eléctricos</t>
+  </si>
+  <si>
+    <t>CD</t>
+  </si>
+  <si>
+    <t>Civil Demolition</t>
+  </si>
+  <si>
+    <t>Demolición Civil</t>
+  </si>
+  <si>
+    <t>CG</t>
+  </si>
+  <si>
+    <t>Civil Grading</t>
+  </si>
+  <si>
+    <t>Nivelación Civil</t>
+  </si>
+  <si>
+    <t>CI</t>
+  </si>
+  <si>
+    <t>Civil Improvements</t>
+  </si>
+  <si>
+    <t>Mejoras Civiles</t>
+  </si>
+  <si>
+    <t>CJ</t>
+  </si>
+  <si>
+    <t>Definido por el Usuario</t>
+  </si>
+  <si>
+    <t>CK</t>
+  </si>
+  <si>
+    <t>CN</t>
+  </si>
+  <si>
+    <t>Civil Nodes</t>
+  </si>
+  <si>
+    <t>Nudos Civiles</t>
+  </si>
+  <si>
+    <t>CP</t>
+  </si>
+  <si>
+    <t>Civil Paving</t>
+  </si>
+  <si>
+    <t>Pavimentación Civil</t>
+  </si>
+  <si>
+    <t>CS</t>
+  </si>
+  <si>
+    <t>Civil Site</t>
+  </si>
+  <si>
+    <t>Sitio Civil</t>
+  </si>
+  <si>
+    <t>CT</t>
+  </si>
+  <si>
+    <t>Civil Transportation</t>
+  </si>
+  <si>
+    <t>Transporte Civil</t>
+  </si>
+  <si>
+    <t>CU</t>
+  </si>
+  <si>
+    <t>Civil Utilities</t>
+  </si>
+  <si>
+    <t>Servicios Civiles</t>
+  </si>
+  <si>
+    <t>ACCS</t>
+  </si>
+  <si>
+    <t>Access</t>
+  </si>
+  <si>
+    <t>Acceso</t>
+  </si>
+  <si>
+    <t>ACID</t>
+  </si>
+  <si>
+    <t>Acid waste systems</t>
+  </si>
+  <si>
+    <t>Sistemas de residuos ácidos</t>
+  </si>
+  <si>
+    <t>AERI</t>
+  </si>
+  <si>
+    <t>Aerial Survey</t>
+  </si>
+  <si>
+    <t>Levantamiento aéreo</t>
+  </si>
+  <si>
+    <t>AFFF</t>
+  </si>
+  <si>
+    <t>Aqueous film-forming foam system</t>
+  </si>
+  <si>
+    <t>Sistema de espuma formadora de película acuosa</t>
+  </si>
+  <si>
+    <t>AFLD</t>
+  </si>
+  <si>
+    <t>Airfields</t>
+  </si>
+  <si>
+    <t>Aeródromos</t>
+  </si>
+  <si>
+    <t>AIR~</t>
+  </si>
+  <si>
+    <t>Air</t>
+  </si>
+  <si>
+    <t>Aire</t>
+  </si>
+  <si>
+    <t>ALGN</t>
+  </si>
+  <si>
+    <t>Alignment</t>
+  </si>
+  <si>
+    <t>Alineación</t>
+  </si>
+  <si>
+    <t>ALRM</t>
+  </si>
+  <si>
+    <t>Alarm system</t>
+  </si>
+  <si>
+    <t>Sistema de alarma</t>
+  </si>
+  <si>
+    <t>ANNO</t>
+  </si>
+  <si>
+    <t>Annotation</t>
+  </si>
+  <si>
+    <t>Anotación</t>
+  </si>
+  <si>
+    <t>AREA</t>
+  </si>
+  <si>
+    <t>Area</t>
+  </si>
+  <si>
+    <t>Área</t>
+  </si>
+  <si>
+    <t>AUXL</t>
+  </si>
+  <si>
+    <t>Auxiliary systems</t>
+  </si>
+  <si>
+    <t>Sistemas auxiliares</t>
+  </si>
+  <si>
+    <t>BARR</t>
+  </si>
+  <si>
+    <t>Barrier</t>
+  </si>
+  <si>
+    <t>Barrera</t>
+  </si>
+  <si>
+    <t>BCST</t>
+  </si>
+  <si>
+    <t>Broadcast related system (radio or TV)</t>
+  </si>
+  <si>
+    <t>Sistema de radiodifusión (radio o TV)</t>
+  </si>
+  <si>
+    <t>BEAM</t>
+  </si>
+  <si>
+    <t>Beams</t>
+  </si>
+  <si>
+    <t>Vigas</t>
+  </si>
+  <si>
+    <t>BELL</t>
+  </si>
+  <si>
+    <t>Bell system</t>
+  </si>
+  <si>
+    <t>Sistema de timbres</t>
+  </si>
+  <si>
+    <t>BLDG</t>
+  </si>
+  <si>
+    <t>Buildings and primary structures</t>
+  </si>
+  <si>
+    <t>Edificios y estructuras primarias</t>
+  </si>
+  <si>
+    <t>BLIN</t>
+  </si>
+  <si>
+    <t>Baseline</t>
+  </si>
+  <si>
+    <t>Línea base</t>
+  </si>
+  <si>
+    <t>BNDY</t>
+  </si>
+  <si>
+    <t>Political boundaries</t>
+  </si>
+  <si>
+    <t>Límites políticos</t>
+  </si>
+  <si>
+    <t>BORE</t>
+  </si>
+  <si>
+    <t>Borings</t>
+  </si>
+  <si>
+    <t>Perforaciones</t>
+  </si>
+  <si>
+    <t>BRCG</t>
+  </si>
+  <si>
+    <t>Bracing</t>
+  </si>
+  <si>
+    <t>Arriostramiento</t>
+  </si>
+  <si>
+    <t>BRDG</t>
+  </si>
+  <si>
+    <t>Bridge</t>
+  </si>
+  <si>
+    <t>Puente</t>
+  </si>
+  <si>
+    <t>BRIN</t>
+  </si>
+  <si>
+    <t>Brine systems</t>
+  </si>
+  <si>
+    <t>Sistemas de salmuera</t>
+  </si>
+  <si>
+    <t>BRKL</t>
+  </si>
+  <si>
+    <t>Break / fault lines</t>
+  </si>
+  <si>
+    <t>Líneas de rotura/falla</t>
+  </si>
+  <si>
+    <t>BRLN</t>
+  </si>
+  <si>
+    <t>Building restriction line</t>
+  </si>
+  <si>
+    <t>Línea de restricción de edificaciones</t>
+  </si>
+  <si>
+    <t>BZNA</t>
+  </si>
+  <si>
+    <t>Buffer zone area</t>
+  </si>
+  <si>
+    <t>Zona de amortiguamiento</t>
+  </si>
+  <si>
+    <t>CABL</t>
+  </si>
+  <si>
+    <t>Cable systems</t>
+  </si>
+  <si>
+    <t>Sistemas de cable</t>
+  </si>
+  <si>
+    <t>CATH</t>
+  </si>
+  <si>
+    <t>Cathodic Protection System</t>
+  </si>
+  <si>
+    <t>Sistema de protección catódica</t>
+  </si>
+  <si>
+    <t>CATV</t>
+  </si>
+  <si>
+    <t>Cable television system</t>
+  </si>
+  <si>
+    <t>Sistema de televisión por cable</t>
+  </si>
+  <si>
+    <t>CCTV</t>
+  </si>
+  <si>
+    <t>Closed-circuit television system</t>
+  </si>
+  <si>
+    <t>Sistema de circuito cerrado de televisión</t>
+  </si>
+  <si>
+    <t>CEME</t>
+  </si>
+  <si>
+    <t>Cemetery</t>
+  </si>
+  <si>
+    <t>Cementerio</t>
+  </si>
+  <si>
+    <t>CHAN</t>
+  </si>
+  <si>
+    <t>Navigable channels</t>
+  </si>
+  <si>
+    <t>Canales navegables</t>
+  </si>
+  <si>
+    <t>CHEM</t>
+  </si>
+  <si>
+    <t>Chemical</t>
+  </si>
+  <si>
+    <t>Productos químicos</t>
+  </si>
+  <si>
+    <t>CHIM</t>
+  </si>
+  <si>
+    <t>Chimneys and stacks</t>
+  </si>
+  <si>
+    <t>Chimeneas y conductos</t>
+  </si>
+  <si>
+    <t>CLNG</t>
+  </si>
+  <si>
+    <t>Ceiling</t>
+  </si>
+  <si>
+    <t>Techo</t>
+  </si>
+  <si>
+    <t>CLOK</t>
+  </si>
+  <si>
+    <t>Clock system</t>
+  </si>
+  <si>
+    <t>Sistema de relojería</t>
+  </si>
+  <si>
+    <t>CMPA</t>
+  </si>
+  <si>
+    <t>Compressed / processed air systems</t>
+  </si>
+  <si>
+    <t>Sistemas de aire comprimido/procesado</t>
+  </si>
+  <si>
+    <t>CMPR</t>
+  </si>
+  <si>
+    <t>Computer</t>
+  </si>
+  <si>
+    <t>Ordenador</t>
+  </si>
+  <si>
+    <t>CNDW</t>
+  </si>
+  <si>
+    <t>Condenser water systems</t>
+  </si>
+  <si>
+    <t>Sistemas de agua del condensador</t>
+  </si>
+  <si>
+    <t>CO2S</t>
+  </si>
+  <si>
+    <t>CO2 system</t>
+  </si>
+  <si>
+    <t>Sistema de CO2</t>
+  </si>
+  <si>
+    <t>CODE</t>
+  </si>
+  <si>
+    <t>Code compliance plan</t>
+  </si>
+  <si>
+    <t>Plan de cumplimiento normativo</t>
+  </si>
+  <si>
+    <t>COLS</t>
+  </si>
+  <si>
+    <t>Columns</t>
+  </si>
+  <si>
+    <t>Columnas</t>
+  </si>
+  <si>
+    <t>COMM</t>
+  </si>
+  <si>
+    <t>Communications</t>
+  </si>
+  <si>
+    <t>Comunicaciones</t>
+  </si>
+  <si>
+    <t>CONT</t>
+  </si>
+  <si>
+    <t>Controls and instrumentation</t>
+  </si>
+  <si>
+    <t>Controles e instrumentación</t>
+  </si>
+  <si>
+    <t>CONV</t>
+  </si>
+  <si>
+    <t>Conveying systems</t>
+  </si>
+  <si>
+    <t>Sistemas de transporte</t>
+  </si>
+  <si>
+    <t>CRPT</t>
+  </si>
+  <si>
+    <t>Carpet / carpet tiles</t>
+  </si>
+  <si>
+    <t>Alfombra/losetas de moqueta</t>
+  </si>
+  <si>
+    <t>CSWK</t>
+  </si>
+  <si>
+    <t>Casework</t>
+  </si>
+  <si>
+    <t>Carpintería</t>
+  </si>
+  <si>
+    <t>CTRL</t>
+  </si>
+  <si>
+    <t>Control points</t>
+  </si>
+  <si>
+    <t>Puntos de control</t>
+  </si>
+  <si>
+    <t>CWTR</t>
+  </si>
+  <si>
+    <t>Chilled water systems</t>
+  </si>
+  <si>
+    <t>Sistemas de agua refrigerada</t>
+  </si>
+  <si>
+    <t>DATA</t>
+  </si>
+  <si>
+    <t>Data / LAN system</t>
+  </si>
+  <si>
+    <t>Datos/LAN Sistema</t>
+  </si>
+  <si>
+    <t>DECK</t>
+  </si>
+  <si>
+    <t>Deck</t>
+  </si>
+  <si>
+    <t>Cubierta</t>
+  </si>
+  <si>
+    <t>DETL</t>
+  </si>
+  <si>
+    <t>Detail</t>
+  </si>
+  <si>
+    <t>Detalle</t>
+  </si>
+  <si>
+    <t>DFLD</t>
+  </si>
+  <si>
+    <t>Drain fields</t>
+  </si>
+  <si>
+    <t>Campos de drenaje</t>
+  </si>
+  <si>
+    <t>DIAG</t>
+  </si>
+  <si>
+    <t>Diagrams</t>
+  </si>
+  <si>
+    <t>Diagramas</t>
+  </si>
+  <si>
+    <t>DICT</t>
+  </si>
+  <si>
+    <t>Dictation system</t>
+  </si>
+  <si>
+    <t>Sistema de dictado</t>
+  </si>
+  <si>
+    <t>DOMW</t>
+  </si>
+  <si>
+    <t>Domestic water systems</t>
+  </si>
+  <si>
+    <t>Sistemas de agua potable</t>
+  </si>
+  <si>
+    <t>DOOR</t>
+  </si>
+  <si>
+    <t>Doors</t>
+  </si>
+  <si>
+    <t>Puertas</t>
+  </si>
+  <si>
+    <t>DRAN</t>
+  </si>
+  <si>
+    <t>Drains</t>
+  </si>
+  <si>
+    <t>Desagües</t>
+  </si>
+  <si>
+    <t>DRIV</t>
+  </si>
+  <si>
+    <t>Driveways</t>
+  </si>
+  <si>
+    <t>Entradas de vehículos</t>
+  </si>
+  <si>
+    <t>DTCH</t>
+  </si>
+  <si>
+    <t>Ditches or washes</t>
+  </si>
+  <si>
+    <t>Cunetas o lavaderos</t>
+  </si>
+  <si>
+    <t>DUAL</t>
+  </si>
+  <si>
+    <t>Dual temperature systems</t>
+  </si>
+  <si>
+    <t>Sistemas de doble temperatura</t>
+  </si>
+  <si>
+    <t>DUST</t>
+  </si>
+  <si>
+    <t>Dust and fume collection systems</t>
+  </si>
+  <si>
+    <t>Sistemas de recolección de polvo y humos</t>
+  </si>
+  <si>
+    <t>ELEC</t>
+  </si>
+  <si>
+    <t>Electrical system, telecom plan</t>
+  </si>
+  <si>
+    <t>Sistema eléctrico, plano de telecomunicaciones</t>
+  </si>
+  <si>
+    <t>ELEV</t>
+  </si>
+  <si>
+    <t>Elevation</t>
+  </si>
+  <si>
+    <t>Elevación</t>
+  </si>
+  <si>
+    <t>ELHT</t>
+  </si>
+  <si>
+    <t>Electric heat</t>
+  </si>
+  <si>
+    <t>Calefacción eléctrica</t>
+  </si>
+  <si>
+    <t>EMCS</t>
+  </si>
+  <si>
+    <t>Energy monitoring control system</t>
+  </si>
+  <si>
+    <t>Sistema de control de monitoreo de energía</t>
+  </si>
+  <si>
+    <t>ENER</t>
+  </si>
+  <si>
+    <t>Energy management systems</t>
+  </si>
+  <si>
+    <t>Sistemas de gestión de energía</t>
+  </si>
+  <si>
+    <t>EQPM</t>
+  </si>
+  <si>
+    <t>Equipo</t>
+  </si>
+  <si>
+    <t>EROS</t>
+  </si>
+  <si>
+    <t>Erosion and sediment control</t>
+  </si>
+  <si>
+    <t>Control de erosión y sedimentos</t>
+  </si>
+  <si>
+    <t>ESMT</t>
+  </si>
+  <si>
+    <t>Easements</t>
+  </si>
+  <si>
+    <t>Servidumbres</t>
+  </si>
+  <si>
+    <t>EVAC</t>
+  </si>
+  <si>
+    <t>Evacuation plan</t>
+  </si>
+  <si>
+    <t>Plan de evacuación</t>
+  </si>
+  <si>
+    <t>EXHS</t>
+  </si>
+  <si>
+    <t>Exhaust system</t>
+  </si>
+  <si>
+    <t>Sistema de extracción</t>
+  </si>
+  <si>
+    <t>FENC</t>
+  </si>
+  <si>
+    <t>Fences</t>
+  </si>
+  <si>
+    <t>Cercas</t>
+  </si>
+  <si>
+    <t>FIRE</t>
+  </si>
+  <si>
+    <t>Fire protection</t>
+  </si>
+  <si>
+    <t>FLHA</t>
+  </si>
+  <si>
+    <t>Flood hazard area</t>
+  </si>
+  <si>
+    <t>Zona con riesgo de inundación</t>
+  </si>
+  <si>
+    <t>FLOR</t>
+  </si>
+  <si>
+    <t>Floor</t>
+  </si>
+  <si>
+    <t>Piso</t>
+  </si>
+  <si>
+    <t>FNDN</t>
+  </si>
+  <si>
+    <t>Foundation</t>
+  </si>
+  <si>
+    <t>Cimentación</t>
+  </si>
+  <si>
+    <t>FNSH</t>
+  </si>
+  <si>
+    <t>Finishes</t>
+  </si>
+  <si>
+    <t>Acabados</t>
+  </si>
+  <si>
+    <t>FRAM</t>
+  </si>
+  <si>
+    <t>Braced frame or moment frame</t>
+  </si>
+  <si>
+    <t>Marco arriostrado o marco de momento</t>
+  </si>
+  <si>
+    <t>FSTN</t>
+  </si>
+  <si>
+    <t>Fasteners and connections</t>
+  </si>
+  <si>
+    <t>Sujeciones y conexiones</t>
+  </si>
+  <si>
+    <t>FUEL</t>
+  </si>
+  <si>
+    <t>Fuel systems</t>
+  </si>
+  <si>
+    <t>Sistemas de combustible</t>
+  </si>
+  <si>
+    <t>FUME</t>
+  </si>
+  <si>
+    <t>Fume hood</t>
+  </si>
+  <si>
+    <t>Campana de extracción de gases</t>
+  </si>
+  <si>
+    <t>FURN</t>
+  </si>
+  <si>
+    <t>Furnishings</t>
+  </si>
+  <si>
+    <t>Mobiliario</t>
+  </si>
+  <si>
+    <t>GAS~</t>
+  </si>
+  <si>
+    <t>Gas</t>
+  </si>
+  <si>
+    <t>GATE</t>
+  </si>
+  <si>
+    <t>Gate</t>
+  </si>
+  <si>
+    <t>Portón</t>
+  </si>
+  <si>
+    <t>GLAZ</t>
+  </si>
+  <si>
+    <t>Glazing</t>
+  </si>
+  <si>
+    <t>Acristalamiento</t>
+  </si>
+  <si>
+    <t>GLYC</t>
+  </si>
+  <si>
+    <t>Glycol systems</t>
+  </si>
+  <si>
+    <t>Sistemas de glicol</t>
+  </si>
+  <si>
+    <t>GRID</t>
+  </si>
+  <si>
+    <t>Grids</t>
+  </si>
+  <si>
+    <t>Rejillas</t>
+  </si>
+  <si>
+    <t>GRLN</t>
+  </si>
+  <si>
+    <t>Grade line</t>
+  </si>
+  <si>
+    <t>Línea de rasante</t>
+  </si>
+  <si>
+    <t>GRND</t>
+  </si>
+  <si>
+    <t>Ground system</t>
+  </si>
+  <si>
+    <t>Sistema de puesta a tierra</t>
+  </si>
+  <si>
+    <t>HALN</t>
+  </si>
+  <si>
+    <t>Halon</t>
+  </si>
+  <si>
+    <t>Halón</t>
+  </si>
+  <si>
+    <t>HVAC</t>
+  </si>
+  <si>
+    <t>HVAC systems</t>
+  </si>
+  <si>
+    <t>Sistemas de climatización (HVAC)</t>
+  </si>
+  <si>
+    <t>HWTR</t>
+  </si>
+  <si>
+    <t>Hot water heating system</t>
+  </si>
+  <si>
+    <t>Sistema de calentamiento de agua caliente</t>
+  </si>
+  <si>
+    <t>HYDR</t>
+  </si>
+  <si>
+    <t>Hydraulic structure</t>
+  </si>
+  <si>
+    <t>Estructura hidráulica</t>
+  </si>
+  <si>
+    <t>IGAS</t>
+  </si>
+  <si>
+    <t>Inert gas</t>
+  </si>
+  <si>
+    <t>Gas inerte</t>
+  </si>
+  <si>
+    <t>INGR</t>
+  </si>
+  <si>
+    <t>Ingrants</t>
+  </si>
+  <si>
+    <t>Concesiones</t>
+  </si>
+  <si>
+    <t>INST</t>
+  </si>
+  <si>
+    <t>Instrumentation system</t>
+  </si>
+  <si>
+    <t>Sistema de instrumentación</t>
+  </si>
+  <si>
+    <t>INTC</t>
+  </si>
+  <si>
+    <t>Intercom / PA systems</t>
+  </si>
+  <si>
+    <t>Intercomunicador/PA Sistemas</t>
+  </si>
+  <si>
+    <t>IRRG</t>
+  </si>
+  <si>
+    <t>Irrigation</t>
+  </si>
+  <si>
+    <t>Riego</t>
+  </si>
+  <si>
+    <t>JNTS</t>
+  </si>
+  <si>
+    <t>Joints</t>
+  </si>
+  <si>
+    <t>Juntas</t>
+  </si>
+  <si>
+    <t>JOIS</t>
+  </si>
+  <si>
+    <t>Joists</t>
+  </si>
+  <si>
+    <t>Viguetas</t>
+  </si>
+  <si>
+    <t>LAND</t>
+  </si>
+  <si>
+    <t>Land</t>
+  </si>
+  <si>
+    <t>Terreno</t>
+  </si>
+  <si>
+    <t>LEGN</t>
+  </si>
+  <si>
+    <t>Legend, symbols keys</t>
+  </si>
+  <si>
+    <t>Leyenda, símbolos y claves</t>
+  </si>
+  <si>
+    <t>LEVE</t>
+  </si>
+  <si>
+    <t>Levee</t>
+  </si>
+  <si>
+    <t>Dique</t>
+  </si>
+  <si>
+    <t>LGAS</t>
+  </si>
+  <si>
+    <t>Laboratory gas systems</t>
+  </si>
+  <si>
+    <t>Sistemas de gases de laboratorio</t>
+  </si>
+  <si>
+    <t>LIQD</t>
+  </si>
+  <si>
+    <t>Liquid</t>
+  </si>
+  <si>
+    <t>Líquido</t>
+  </si>
+  <si>
+    <t>LITE</t>
+  </si>
+  <si>
+    <t>Lighting</t>
+  </si>
+  <si>
+    <t>Iluminación</t>
+  </si>
+  <si>
+    <t>LNTL</t>
+  </si>
+  <si>
+    <t>Lintels</t>
+  </si>
+  <si>
+    <t>Dinteles</t>
+  </si>
+  <si>
+    <t>LOCN</t>
+  </si>
+  <si>
+    <t>Limits of construction</t>
+  </si>
+  <si>
+    <t>Límites de construcción</t>
+  </si>
+  <si>
+    <t>LTNG</t>
+  </si>
+  <si>
+    <t>Lightning protection system</t>
+  </si>
+  <si>
+    <t>Sistema de protección contra rayos</t>
+  </si>
+  <si>
+    <t>MACH</t>
+  </si>
+  <si>
+    <t>Machine shop</t>
+  </si>
+  <si>
+    <t>Taller de maquinaria</t>
+  </si>
+  <si>
+    <t>MAJQ</t>
+  </si>
+  <si>
+    <t>Major equipment</t>
+  </si>
+  <si>
+    <t>Equipo principal</t>
+  </si>
+  <si>
+    <t>MDGS</t>
+  </si>
+  <si>
+    <t>Medical gas systems</t>
+  </si>
+  <si>
+    <t>Sistemas de gases medicinales</t>
+  </si>
+  <si>
+    <t>MILL</t>
+  </si>
+  <si>
+    <t>Millwork</t>
+  </si>
+  <si>
+    <t>MINQ</t>
+  </si>
+  <si>
+    <t>Minor equipment</t>
+  </si>
+  <si>
+    <t>Equipo menor</t>
+  </si>
+  <si>
+    <t>MKUP</t>
+  </si>
+  <si>
+    <t>Make-up air systems</t>
+  </si>
+  <si>
+    <t>Sistemas de aire de reposición</t>
+  </si>
+  <si>
+    <t>MNTG</t>
+  </si>
+  <si>
+    <t>Mounting system</t>
+  </si>
+  <si>
+    <t>Sistema de montaje</t>
+  </si>
+  <si>
+    <t>MPIP</t>
+  </si>
+  <si>
+    <t>Miscellaneous piping systems</t>
+  </si>
+  <si>
+    <t>Sistemas de tuberías misceláneos</t>
+  </si>
+  <si>
+    <t>NGAS</t>
+  </si>
+  <si>
+    <t>Natural gas systems</t>
+  </si>
+  <si>
+    <t>Sistemas de gas natural</t>
+  </si>
+  <si>
+    <t>NODE</t>
+  </si>
+  <si>
+    <t>Node</t>
+  </si>
+  <si>
+    <t>Nodo</t>
+  </si>
+  <si>
+    <t>NURS</t>
+  </si>
+  <si>
+    <t>Nurse call system</t>
+  </si>
+  <si>
+    <t>Sistema de llamada a enfermeras</t>
+  </si>
+  <si>
+    <t>OBST</t>
+  </si>
+  <si>
+    <t>Obstructions</t>
+  </si>
+  <si>
+    <t>Obstrucciones</t>
+  </si>
+  <si>
+    <t>OIL~</t>
+  </si>
+  <si>
+    <t>Oil</t>
+  </si>
+  <si>
+    <t>Petróleo</t>
+  </si>
+  <si>
+    <t>OTGR</t>
+  </si>
+  <si>
+    <t>Outgrants</t>
+  </si>
+  <si>
+    <t>Conducciones de salida</t>
+  </si>
+  <si>
+    <t>PADS</t>
+  </si>
+  <si>
+    <t>Pads</t>
+  </si>
+  <si>
+    <t>Almohadillas</t>
+  </si>
+  <si>
+    <t>PERC</t>
+  </si>
+  <si>
+    <t>Perc testing</t>
+  </si>
+  <si>
+    <t>Prueba de percolación</t>
+  </si>
+  <si>
+    <t>PGNG</t>
+  </si>
+  <si>
+    <t>Paging system</t>
+  </si>
+  <si>
+    <t>Sistema de buscapersonas</t>
+  </si>
+  <si>
+    <t>PHON</t>
+  </si>
+  <si>
+    <t>Telephone system</t>
+  </si>
+  <si>
+    <t>Sistema telefónico</t>
+  </si>
+  <si>
+    <t>PIPE</t>
+  </si>
+  <si>
+    <t>Piping</t>
+  </si>
+  <si>
+    <t>Tuberías</t>
+  </si>
+  <si>
+    <t>PLAN</t>
+  </si>
+  <si>
+    <t>Key Plan (Floor Plan)</t>
+  </si>
+  <si>
+    <t>Plano clave (Plano de planta)</t>
+  </si>
+  <si>
+    <t>PLAT</t>
+  </si>
+  <si>
+    <t>Platform</t>
+  </si>
+  <si>
+    <t>Andén</t>
+  </si>
+  <si>
+    <t>PLNT</t>
+  </si>
+  <si>
+    <t>Plant and landscape material</t>
+  </si>
+  <si>
+    <t>Planta y material de jardinería</t>
+  </si>
+  <si>
+    <t>POND</t>
+  </si>
+  <si>
+    <t>Ponds</t>
+  </si>
+  <si>
+    <t>Estanques</t>
+  </si>
+  <si>
+    <t>POWR</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>Energía</t>
+  </si>
+  <si>
+    <t>PRKG</t>
+  </si>
+  <si>
+    <t>Parking lots</t>
+  </si>
+  <si>
+    <t>Estacionamientos</t>
+  </si>
+  <si>
+    <t>PROC</t>
+  </si>
+  <si>
+    <t>Process systems</t>
+  </si>
+  <si>
+    <t>Sistemas de proceso</t>
+  </si>
+  <si>
+    <t>PROJ</t>
+  </si>
+  <si>
+    <t>Projector system</t>
+  </si>
+  <si>
+    <t>Sistema de proyectores</t>
+  </si>
+  <si>
+    <t>PROP</t>
+  </si>
+  <si>
+    <t>Property</t>
+  </si>
+  <si>
+    <t>Propiedad</t>
+  </si>
+  <si>
+    <t>PROT</t>
+  </si>
+  <si>
+    <t>Fire protection system</t>
+  </si>
+  <si>
+    <t>Sistema de protección contra incendios</t>
+  </si>
+  <si>
+    <t>PRTN</t>
+  </si>
+  <si>
+    <t>Partitions</t>
+  </si>
+  <si>
+    <t>Tabiques</t>
+  </si>
+  <si>
+    <t>PVMD</t>
+  </si>
+  <si>
+    <t>Photovoltaic modules</t>
+  </si>
+  <si>
+    <t>Módulos fotovoltaicos</t>
+  </si>
+  <si>
+    <t>PVMT</t>
+  </si>
+  <si>
+    <t>Pavement</t>
+  </si>
+  <si>
+    <t>Pavimento</t>
+  </si>
+  <si>
+    <t>RAIL</t>
+  </si>
+  <si>
+    <t>Railroad</t>
+  </si>
+  <si>
+    <t>Ferrocarril</t>
+  </si>
+  <si>
+    <t>RAIR</t>
+  </si>
+  <si>
+    <t>Relief air systems</t>
+  </si>
+  <si>
+    <t>Sistemas de aire de alivio</t>
+  </si>
+  <si>
+    <t>RCOV</t>
+  </si>
+  <si>
+    <t>Energy recovery systems</t>
+  </si>
+  <si>
+    <t>Sistemas de recuperación de energía</t>
+  </si>
+  <si>
+    <t>REFG</t>
+  </si>
+  <si>
+    <t>Refrigeration systems</t>
+  </si>
+  <si>
+    <t>Sistemas de refrigeración</t>
+  </si>
+  <si>
+    <t>RIGG</t>
+  </si>
+  <si>
+    <t>Rigging / automation systems</t>
+  </si>
+  <si>
+    <t>Aparejos/automatización Sistemas</t>
+  </si>
+  <si>
+    <t>RIVR</t>
+  </si>
+  <si>
+    <t>River</t>
+  </si>
+  <si>
+    <t>Río</t>
+  </si>
+  <si>
+    <t>ROAD</t>
+  </si>
+  <si>
+    <t>Roadways</t>
+  </si>
+  <si>
+    <t>Carreteras</t>
+  </si>
+  <si>
+    <t>ROOF</t>
+  </si>
+  <si>
+    <t>Roof</t>
+  </si>
+  <si>
+    <t>RRAP</t>
+  </si>
+  <si>
+    <t>Riprap</t>
+  </si>
+  <si>
+    <t>Escalones</t>
+  </si>
+  <si>
+    <t>RUNW</t>
+  </si>
+  <si>
+    <t>Runway</t>
+  </si>
+  <si>
+    <t>Pista</t>
+  </si>
+  <si>
+    <t>RWAY</t>
+  </si>
+  <si>
+    <t>Right-of-way</t>
+  </si>
+  <si>
+    <t>Derecho de paso</t>
+  </si>
+  <si>
+    <t>SECT</t>
+  </si>
+  <si>
+    <t>Section</t>
+  </si>
+  <si>
+    <t>Sección</t>
+  </si>
+  <si>
+    <t>SERT</t>
+  </si>
+  <si>
+    <t>Security system</t>
+  </si>
+  <si>
+    <t>Sistema de seguridad</t>
+  </si>
+  <si>
+    <t>SGHT</t>
+  </si>
+  <si>
+    <t>Sight distance</t>
+  </si>
+  <si>
+    <t>Distancia visual</t>
+  </si>
+  <si>
+    <t>SIGN</t>
+  </si>
+  <si>
+    <t>Sign</t>
+  </si>
+  <si>
+    <t>Señal</t>
+  </si>
+  <si>
+    <t>SITE</t>
+  </si>
+  <si>
+    <t>Site features</t>
+  </si>
+  <si>
+    <t>Características del sitio</t>
+  </si>
+  <si>
+    <t>SLAB</t>
+  </si>
+  <si>
+    <t>Slab</t>
+  </si>
+  <si>
+    <t>Losa</t>
+  </si>
+  <si>
+    <t>SLUR</t>
+  </si>
+  <si>
+    <t>Slurry</t>
+  </si>
+  <si>
+    <t>Lodo</t>
+  </si>
+  <si>
+    <t>SMOK</t>
+  </si>
+  <si>
+    <t>Smoke extraction systems</t>
+  </si>
+  <si>
+    <t>Sistemas de extracción de humos</t>
+  </si>
+  <si>
+    <t>SOIL</t>
+  </si>
+  <si>
+    <t>Soils</t>
+  </si>
+  <si>
+    <t>Suelos</t>
+  </si>
+  <si>
+    <t>SOUN</t>
+  </si>
+  <si>
+    <t>Sound system</t>
+  </si>
+  <si>
+    <t>Sistema de sonido</t>
+  </si>
+  <si>
+    <t>SPCL</t>
+  </si>
+  <si>
+    <t>Special systems</t>
+  </si>
+  <si>
+    <t>Sistemas especiales</t>
+  </si>
+  <si>
+    <t>SPFX</t>
+  </si>
+  <si>
+    <t>Entertainment special effects system</t>
+  </si>
+  <si>
+    <t>Sistema de efectos especiales para entretenimiento</t>
+  </si>
+  <si>
+    <t>SPKL</t>
+  </si>
+  <si>
+    <t>Sprinkler</t>
+  </si>
+  <si>
+    <t>Rociadores</t>
+  </si>
+  <si>
+    <t>SSWR</t>
+  </si>
+  <si>
+    <t>Sanitary sewer</t>
+  </si>
+  <si>
+    <t>Alcantarillado sanitario</t>
+  </si>
+  <si>
+    <t>STEM</t>
+  </si>
+  <si>
+    <t>Steam system</t>
+  </si>
+  <si>
+    <t>Sistema de vapor</t>
+  </si>
+  <si>
+    <t>STIF</t>
+  </si>
+  <si>
+    <t>Stiffener</t>
+  </si>
+  <si>
+    <t>Refuerzo</t>
+  </si>
+  <si>
+    <t>STRM</t>
+  </si>
+  <si>
+    <t>Storm sewer</t>
+  </si>
+  <si>
+    <t>Alcantarillado pluvial</t>
+  </si>
+  <si>
+    <t>STRS</t>
+  </si>
+  <si>
+    <t>Stairs</t>
+  </si>
+  <si>
+    <t>Escaleras</t>
+  </si>
+  <si>
+    <t>SURV</t>
+  </si>
+  <si>
+    <t>Survey</t>
+  </si>
+  <si>
+    <t>Topografía</t>
+  </si>
+  <si>
+    <t>SWLK</t>
+  </si>
+  <si>
+    <t>Sidewalks</t>
+  </si>
+  <si>
+    <t>Aceras</t>
+  </si>
+  <si>
+    <t>TEST</t>
+  </si>
+  <si>
+    <t>Test equipment</t>
+  </si>
+  <si>
+    <t>Equipo de prueba</t>
+  </si>
+  <si>
+    <t>TILE</t>
+  </si>
+  <si>
+    <t>Tile</t>
+  </si>
+  <si>
+    <t>Tejas</t>
+  </si>
+  <si>
+    <t>TINN</t>
+  </si>
+  <si>
+    <t>Triangulated irregular network</t>
+  </si>
+  <si>
+    <t>Red irregular triangular</t>
+  </si>
+  <si>
+    <t>TOPO</t>
+  </si>
+  <si>
+    <t>Topographic feature</t>
+  </si>
+  <si>
+    <t>Característica topográfica</t>
+  </si>
+  <si>
+    <t>TRAL</t>
+  </si>
+  <si>
+    <t>Trails or paths</t>
+  </si>
+  <si>
+    <t>Senderos o caminos</t>
+  </si>
+  <si>
+    <t>TRAN</t>
+  </si>
+  <si>
+    <t>Transmission system</t>
+  </si>
+  <si>
+    <t>Sistema de transmisión</t>
+  </si>
+  <si>
+    <t>TRUS</t>
+  </si>
+  <si>
+    <t>Trusses</t>
+  </si>
+  <si>
+    <t>Cerchas</t>
+  </si>
+  <si>
+    <t>TVAN</t>
+  </si>
+  <si>
+    <t>Television antenna system</t>
+  </si>
+  <si>
+    <t>Sistema de antena de televisión</t>
+  </si>
+  <si>
+    <t>TVVS</t>
+  </si>
+  <si>
+    <t>Television and video system</t>
+  </si>
+  <si>
+    <t>Sistema de televisión y video</t>
+  </si>
+  <si>
+    <t>UNID</t>
+  </si>
+  <si>
+    <t>Unidentified site objects</t>
+  </si>
+  <si>
+    <t>Objetos no identificados del sitio</t>
+  </si>
+  <si>
+    <t>UTIL</t>
+  </si>
+  <si>
+    <t>Utilities</t>
+  </si>
+  <si>
+    <t>Servicios públicos</t>
+  </si>
+  <si>
+    <t>VACU</t>
+  </si>
+  <si>
+    <t>Vacuum</t>
+  </si>
+  <si>
+    <t>Aspiradora</t>
+  </si>
+  <si>
+    <t>VIDO</t>
+  </si>
+  <si>
+    <t>Entertainment projection systems</t>
+  </si>
+  <si>
+    <t>Sistemas de proyección de entretenimiento</t>
+  </si>
+  <si>
+    <t>WALL</t>
+  </si>
+  <si>
+    <t>Walls</t>
+  </si>
+  <si>
+    <t>Muros</t>
+  </si>
+  <si>
+    <t>WATR</t>
+  </si>
+  <si>
+    <t>Water supply</t>
+  </si>
+  <si>
+    <t>Suministro de agua</t>
+  </si>
+  <si>
+    <t>WETL</t>
+  </si>
+  <si>
+    <t>Wetlands</t>
+  </si>
+  <si>
+    <t>Humedales</t>
+  </si>
+  <si>
+    <t>WIND</t>
+  </si>
+  <si>
+    <t>Wind powered</t>
+  </si>
+  <si>
+    <t>Energía eólica</t>
+  </si>
+  <si>
+    <t>WWAY</t>
+  </si>
+  <si>
+    <t>Waterway</t>
+  </si>
+  <si>
+    <t>Vía fluvial</t>
   </si>
 </sst>
 </file>
@@ -9602,7 +11452,7 @@
         <v>| A | Architectural | Arquitectura | ✓ |✓ | | | | | | | | |</v>
       </c>
     </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="2:22" ht="30.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="5" t="s">
         <v>104</v>
       </c>
@@ -9656,7 +11506,7 @@
         <v>| AD | Architectural Demolition | Demolición arquitectónica | ✓ |✕ | | | | | | | | |</v>
       </c>
     </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="2:22" ht="30.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="5" t="s">
         <v>106</v>
       </c>
@@ -10021,9 +11871,15 @@
       </c>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+      <c r="B14" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>56</v>
+      </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
@@ -10037,34 +11893,40 @@
       <c r="O14" s="5"/>
       <c r="P14" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>|  |  |</v>
+        <v>| E | Electrical |</v>
       </c>
       <c r="Q14" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>|  |  |  |</v>
+        <v>| E | Electrical | Electricidad |</v>
       </c>
       <c r="R14" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>|  |  |  |  |</v>
+        <v>| E | Electrical | Electricidad |  |</v>
       </c>
       <c r="S14" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>|  |  |  |  | |</v>
+        <v>| E | Electrical | Electricidad |  | |</v>
       </c>
       <c r="T14" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>|  |  |  |  | | |</v>
+        <v>| E | Electrical | Electricidad |  | | |</v>
       </c>
       <c r="U14" s="5"/>
       <c r="V14" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>|  |  |  |  | | | | | | | | | |</v>
+        <v>| E | Electrical | Electricidad |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
+      <c r="B15" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>153</v>
+      </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
@@ -10079,7 +11941,7 @@
       <c r="P15" s="5"/>
       <c r="Q15" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>|  |  |  |</v>
+        <v>| ED | Electrical Demolition | Demolición eléctrica |</v>
       </c>
       <c r="R15" s="5"/>
       <c r="S15" s="5"/>
@@ -10088,9 +11950,15 @@
       <c r="V15" s="5"/>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
+      <c r="B16" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>156</v>
+      </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
@@ -10105,7 +11973,7 @@
       <c r="P16" s="5"/>
       <c r="Q16" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>|  |  |  |</v>
+        <v>| EI | Electrical Instrumentation | Instrumentación eléctrica |</v>
       </c>
       <c r="R16" s="5"/>
       <c r="S16" s="5"/>
@@ -10114,9 +11982,15 @@
       <c r="V16" s="5"/>
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
+      <c r="B17" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>125</v>
+      </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -10131,7 +12005,7 @@
       <c r="P17" s="5"/>
       <c r="Q17" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>|  |  |  |</v>
+        <v>| EJ | User Defined | Definido por el usuario |</v>
       </c>
       <c r="R17" s="5"/>
       <c r="S17" s="5"/>
@@ -10140,9 +12014,15 @@
       <c r="V17" s="5"/>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
+      <c r="B18" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>125</v>
+      </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
@@ -10157,7 +12037,7 @@
       <c r="P18" s="5"/>
       <c r="Q18" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>|  |  |  |</v>
+        <v>| EK | User Defined | Definido por el usuario |</v>
       </c>
       <c r="R18" s="5"/>
       <c r="S18" s="5"/>
@@ -10166,9 +12046,15 @@
       <c r="V18" s="5"/>
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
+      <c r="B19" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>161</v>
+      </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
@@ -10183,7 +12069,7 @@
       <c r="P19" s="5"/>
       <c r="Q19" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>|  |  |  |</v>
+        <v>| EL | Electrical Lighting | Iluminación eléctrica |</v>
       </c>
       <c r="R19" s="5"/>
       <c r="S19" s="5"/>
@@ -10192,9 +12078,15 @@
       <c r="V19" s="5"/>
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
+      <c r="B20" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>164</v>
+      </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
@@ -10209,7 +12101,7 @@
       <c r="P20" s="5"/>
       <c r="Q20" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>|  |  |  |</v>
+        <v>| EP | Electrical Power | Energía eléctrica |</v>
       </c>
       <c r="R20" s="5"/>
       <c r="S20" s="5"/>
@@ -10218,9 +12110,15 @@
       <c r="V20" s="5"/>
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
+      <c r="B21" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>167</v>
+      </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
@@ -10235,7 +12133,7 @@
       <c r="P21" s="5"/>
       <c r="Q21" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>|  |  |  |</v>
+        <v>| ES | Electrical Site | Sitio eléctrico |</v>
       </c>
       <c r="R21" s="5"/>
       <c r="S21" s="5"/>
@@ -10244,9 +12142,15 @@
       <c r="V21" s="5"/>
     </row>
     <row r="22" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
+      <c r="B22" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>170</v>
+      </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
@@ -10261,7 +12165,7 @@
       <c r="P22" s="5"/>
       <c r="Q22" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>|  |  |  |</v>
+        <v>| ET | Electrical Telecommunications | Telecomunicaciones eléctricas |</v>
       </c>
       <c r="R22" s="5"/>
       <c r="S22" s="5"/>
@@ -10270,9 +12174,15 @@
       <c r="V22" s="5"/>
     </row>
     <row r="23" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
+      <c r="B23" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>173</v>
+      </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
@@ -10287,7 +12197,7 @@
       <c r="P23" s="5"/>
       <c r="Q23" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>|  |  |  |</v>
+        <v>| EY | Electrical Auxiliary Systems | Sistemas auxiliares eléctricos |</v>
       </c>
       <c r="R23" s="5"/>
       <c r="S23" s="5"/>
@@ -10296,9 +12206,15 @@
       <c r="V23" s="5"/>
     </row>
     <row r="24" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
+      <c r="B24" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>51</v>
+      </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
@@ -10313,7 +12229,7 @@
       <c r="P24" s="5"/>
       <c r="Q24" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>|  |  |  |</v>
+        <v>| C | Civil | Civil |</v>
       </c>
       <c r="R24" s="5"/>
       <c r="S24" s="5"/>
@@ -10322,9 +12238,15 @@
       <c r="V24" s="5"/>
     </row>
     <row r="25" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
+      <c r="B25" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>176</v>
+      </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
@@ -10339,7 +12261,7 @@
       <c r="P25" s="5"/>
       <c r="Q25" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>|  |  |  |</v>
+        <v>| CD | Civil Demolition | Demolición Civil |</v>
       </c>
       <c r="R25" s="5"/>
       <c r="S25" s="5"/>
@@ -10348,9 +12270,15 @@
       <c r="V25" s="5"/>
     </row>
     <row r="26" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
+      <c r="B26" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>179</v>
+      </c>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
@@ -10365,7 +12293,7 @@
       <c r="P26" s="5"/>
       <c r="Q26" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>|  |  |  |</v>
+        <v>| CG | Civil Grading | Nivelación Civil |</v>
       </c>
       <c r="R26" s="5"/>
       <c r="S26" s="5"/>
@@ -10374,9 +12302,15 @@
       <c r="V26" s="5"/>
     </row>
     <row r="27" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
+      <c r="B27" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>182</v>
+      </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
@@ -10391,7 +12325,7 @@
       <c r="P27" s="5"/>
       <c r="Q27" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>|  |  |  |</v>
+        <v>| CI | Civil Improvements | Mejoras Civiles |</v>
       </c>
       <c r="R27" s="5"/>
       <c r="S27" s="5"/>
@@ -10400,9 +12334,15 @@
       <c r="V27" s="5"/>
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
+      <c r="B28" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>184</v>
+      </c>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
@@ -10417,7 +12357,7 @@
       <c r="P28" s="5"/>
       <c r="Q28" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>|  |  |  |</v>
+        <v>| CJ | User Defined | Definido por el Usuario |</v>
       </c>
       <c r="R28" s="5"/>
       <c r="S28" s="5"/>
@@ -10426,9 +12366,15 @@
       <c r="V28" s="5"/>
     </row>
     <row r="29" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
+      <c r="B29" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>184</v>
+      </c>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
@@ -10443,7 +12389,7 @@
       <c r="P29" s="5"/>
       <c r="Q29" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>|  |  |  |</v>
+        <v>| CK | User Defined | Definido por el Usuario |</v>
       </c>
       <c r="R29" s="5"/>
       <c r="S29" s="5"/>
@@ -10452,9 +12398,15 @@
       <c r="V29" s="5"/>
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
+      <c r="B30" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>188</v>
+      </c>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
@@ -10469,7 +12421,7 @@
       <c r="P30" s="5"/>
       <c r="Q30" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>|  |  |  |</v>
+        <v>| CN | Civil Nodes | Nudos Civiles |</v>
       </c>
       <c r="R30" s="5"/>
       <c r="S30" s="5"/>
@@ -10478,9 +12430,15 @@
       <c r="V30" s="5"/>
     </row>
     <row r="31" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
+      <c r="B31" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>191</v>
+      </c>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
@@ -10495,7 +12453,7 @@
       <c r="P31" s="5"/>
       <c r="Q31" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>|  |  |  |</v>
+        <v>| CP | Civil Paving | Pavimentación Civil |</v>
       </c>
       <c r="R31" s="5"/>
       <c r="S31" s="5"/>
@@ -10504,9 +12462,15 @@
       <c r="V31" s="5"/>
     </row>
     <row r="32" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="5"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
+      <c r="B32" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>194</v>
+      </c>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
@@ -10521,7 +12485,7 @@
       <c r="P32" s="5"/>
       <c r="Q32" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>|  |  |  |</v>
+        <v>| CS | Civil Site | Sitio Civil |</v>
       </c>
       <c r="R32" s="5"/>
       <c r="S32" s="5"/>
@@ -10530,9 +12494,15 @@
       <c r="V32" s="5"/>
     </row>
     <row r="33" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B33" s="5"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
+      <c r="B33" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>197</v>
+      </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
@@ -10547,7 +12517,7 @@
       <c r="P33" s="5"/>
       <c r="Q33" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>|  |  |  |</v>
+        <v>| CT | Civil Transportation | Transporte Civil |</v>
       </c>
       <c r="R33" s="5"/>
       <c r="S33" s="5"/>
@@ -10556,9 +12526,15 @@
       <c r="V33" s="5"/>
     </row>
     <row r="34" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
+      <c r="B34" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>200</v>
+      </c>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
@@ -10573,7 +12549,7 @@
       <c r="P34" s="5"/>
       <c r="Q34" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>|  |  |  |</v>
+        <v>| CU | Civil Utilities | Servicios Civiles |</v>
       </c>
       <c r="R34" s="5"/>
       <c r="S34" s="5"/>
@@ -13249,6 +15225,5473 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B53ECC1-3B1D-4C8A-92C3-A53ACBB569A1}">
+  <dimension ref="B1:V194"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="2.7109375" style="1" customWidth="1"/>
+    <col min="2" max="3" width="46.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="29.28515625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="6.640625" style="1" customWidth="1"/>
+    <col min="7" max="8" width="7.140625" style="1" customWidth="1"/>
+    <col min="9" max="14" width="4.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="2.7109375" style="1" customWidth="1"/>
+    <col min="16" max="20" width="74.140625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="56" style="1" customWidth="1"/>
+    <col min="22" max="22" width="74.140625" style="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B1" s="1">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B3" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="5" t="str">
+        <f>_xlfn.CONCAT("| ",B3," | ",C3," |")</f>
+        <v>| Designador | Descripción (en) |</v>
+      </c>
+      <c r="Q3" s="5" t="str">
+        <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," |")</f>
+        <v>| Designador | Descripción (en) | Descripción (es) |</v>
+      </c>
+      <c r="R3" s="5" t="str">
+        <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," |")</f>
+        <v>| Designador | Descripción (en) | Descripción (es) | A |</v>
+      </c>
+      <c r="S3" s="5" t="str">
+        <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," |",F3," |")</f>
+        <v>| Designador | Descripción (en) | Descripción (es) | A |B |</v>
+      </c>
+      <c r="T3" s="5" t="str">
+        <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," |",F3," |",G3," |")</f>
+        <v>| Designador | Descripción (en) | Descripción (es) | A |B |C |</v>
+      </c>
+      <c r="U3" s="5" t="str">
+        <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," | ",F3," | ",G3," | ",H3," |")</f>
+        <v>| Designador | Descripción (en) | Descripción (es) | A | B | C | D |</v>
+      </c>
+      <c r="V3" s="5" t="str">
+        <f t="shared" ref="V3:V14" si="0">_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," |",F3," |",G3," |",H3," |",I3," |",J3," |",K3," |",L3," |",M3," |",N3," |")</f>
+        <v>| Designador | Descripción (en) | Descripción (es) | A |B |C |D | | | | | | |</v>
+      </c>
+    </row>
+    <row r="4" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="O4" s="7"/>
+      <c r="P4" s="8" t="str">
+        <f>_xlfn.CONCAT("|",B4,"|",C4,"|")</f>
+        <v>|---|---|</v>
+      </c>
+      <c r="Q4" s="8" t="str">
+        <f>_xlfn.CONCAT("|",B4,"|",C4,"|",D4,"|")</f>
+        <v>|---|---|---|</v>
+      </c>
+      <c r="R4" s="8" t="str">
+        <f>_xlfn.CONCAT("|",B4,"|",C4,"|",D4,"|",E4,"|")</f>
+        <v>|---|---|---|---|</v>
+      </c>
+      <c r="S4" s="8" t="str">
+        <f>_xlfn.CONCAT("|",B4,"|",C4,"|",D4,"|",E4,"|",F4,"|")</f>
+        <v>|---|---|---|---|---|</v>
+      </c>
+      <c r="T4" s="5" t="str">
+        <f t="shared" ref="T4:T67" si="1">_xlfn.CONCAT("| ",B4," | ",C4," | ",D4," | ",E4," |",F4," |",G4," |")</f>
+        <v>| --- | --- | --- | --- |--- |--- |</v>
+      </c>
+      <c r="U4" s="5" t="str">
+        <f t="shared" ref="U4:U11" si="2">_xlfn.CONCAT("| ",B4," | ",C4," | ",D4," | ",E4," | ",F4," | ",G4," | ",H4," |")</f>
+        <v>| --- | --- | --- | --- | --- | --- | --- |</v>
+      </c>
+      <c r="V4" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>| --- | --- | --- | --- |--- |--- |--- |--- |--- |--- |--- |--- |--- |</v>
+      </c>
+    </row>
+    <row r="5" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5" t="str">
+        <f>_xlfn.CONCAT("| ",B5," | ",C5," |")</f>
+        <v>| ACCS | Access |</v>
+      </c>
+      <c r="Q5" s="5" t="str">
+        <f t="shared" ref="Q5:Q38" si="3">_xlfn.CONCAT("| ",B5," | ",C5," | ",D5," |")</f>
+        <v>| ACCS | Access | Acceso |</v>
+      </c>
+      <c r="R5" s="5" t="str">
+        <f>_xlfn.CONCAT("| ",B5," | ",C5," | ",D5," | ",E5," |")</f>
+        <v>| ACCS | Access | Acceso | ✓ |</v>
+      </c>
+      <c r="S5" s="5" t="str">
+        <f>_xlfn.CONCAT("| ",B5," | ",C5," | ",D5," | ",E5," |",F5," |")</f>
+        <v>| ACCS | Access | Acceso | ✓ |✓ |</v>
+      </c>
+      <c r="T5" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| ACCS | Access | Acceso | ✓ |✓ | |</v>
+      </c>
+      <c r="U5" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>| ACCS | Access | Acceso | ✓ | ✓ |  |  |</v>
+      </c>
+      <c r="V5" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>| ACCS | Access | Acceso | ✓ |✓ | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="6" spans="2:22" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5" t="str">
+        <f t="shared" ref="P6:P14" si="4">_xlfn.CONCAT("| ",B6," | ",C6," |")</f>
+        <v>| ACID | Acid waste systems |</v>
+      </c>
+      <c r="Q6" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| ACID | Acid waste systems | Sistemas de residuos ácidos |</v>
+      </c>
+      <c r="R6" s="5" t="str">
+        <f t="shared" ref="R6:R69" si="5">_xlfn.CONCAT("| ",B6," | ",C6," | ",D6," | ",E6," |")</f>
+        <v>| ACID | Acid waste systems | Sistemas de residuos ácidos | ✓ |</v>
+      </c>
+      <c r="S6" s="5" t="str">
+        <f t="shared" ref="S6:S69" si="6">_xlfn.CONCAT("| ",B6," | ",C6," | ",D6," | ",E6," |",F6," |")</f>
+        <v>| ACID | Acid waste systems | Sistemas de residuos ácidos | ✓ |✕ |</v>
+      </c>
+      <c r="T6" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| ACID | Acid waste systems | Sistemas de residuos ácidos | ✓ |✕ | |</v>
+      </c>
+      <c r="U6" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>| ACID | Acid waste systems | Sistemas de residuos ácidos | ✓ | ✕ |  |  |</v>
+      </c>
+      <c r="V6" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>| ACID | Acid waste systems | Sistemas de residuos ácidos | ✓ |✕ | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="7" spans="2:22" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>| AERI | Aerial Survey |</v>
+      </c>
+      <c r="Q7" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| AERI | Aerial Survey | Levantamiento aéreo |</v>
+      </c>
+      <c r="R7" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| AERI | Aerial Survey | Levantamiento aéreo | ✓ |</v>
+      </c>
+      <c r="S7" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| AERI | Aerial Survey | Levantamiento aéreo | ✓ |✓ |</v>
+      </c>
+      <c r="T7" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| AERI | Aerial Survey | Levantamiento aéreo | ✓ |✓ | |</v>
+      </c>
+      <c r="U7" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>| AERI | Aerial Survey | Levantamiento aéreo | ✓ | ✓ |  |  |</v>
+      </c>
+      <c r="V7" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>| AERI | Aerial Survey | Levantamiento aéreo | ✓ |✓ | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="8" spans="2:22" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>| AFFF | Aqueous film-forming foam system |</v>
+      </c>
+      <c r="Q8" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| AFFF | Aqueous film-forming foam system | Sistema de espuma formadora de película acuosa |</v>
+      </c>
+      <c r="R8" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| AFFF | Aqueous film-forming foam system | Sistema de espuma formadora de película acuosa | ✓ |</v>
+      </c>
+      <c r="S8" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| AFFF | Aqueous film-forming foam system | Sistema de espuma formadora de película acuosa | ✓ |✕ |</v>
+      </c>
+      <c r="T8" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| AFFF | Aqueous film-forming foam system | Sistema de espuma formadora de película acuosa | ✓ |✕ | |</v>
+      </c>
+      <c r="U8" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>| AFFF | Aqueous film-forming foam system | Sistema de espuma formadora de película acuosa | ✓ | ✕ |  |  |</v>
+      </c>
+      <c r="V8" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>| AFFF | Aqueous film-forming foam system | Sistema de espuma formadora de película acuosa | ✓ |✕ | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="9" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>| AFLD | Airfields |</v>
+      </c>
+      <c r="Q9" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| AFLD | Airfields | Aeródromos |</v>
+      </c>
+      <c r="R9" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| AFLD | Airfields | Aeródromos | ✓ |</v>
+      </c>
+      <c r="S9" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| AFLD | Airfields | Aeródromos | ✓ |✕ |</v>
+      </c>
+      <c r="T9" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| AFLD | Airfields | Aeródromos | ✓ |✕ | |</v>
+      </c>
+      <c r="U9" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>| AFLD | Airfields | Aeródromos | ✓ | ✕ |  |  |</v>
+      </c>
+      <c r="V9" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>| AFLD | Airfields | Aeródromos | ✓ |✕ | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="10" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>| AIR~ | Air |</v>
+      </c>
+      <c r="Q10" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| AIR~ | Air | Aire |</v>
+      </c>
+      <c r="R10" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| AIR~ | Air | Aire | ✓ |</v>
+      </c>
+      <c r="S10" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| AIR~ | Air | Aire | ✓ |✕ |</v>
+      </c>
+      <c r="T10" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| AIR~ | Air | Aire | ✓ |✕ | |</v>
+      </c>
+      <c r="U10" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>| AIR~ | Air | Aire | ✓ | ✕ |  |  |</v>
+      </c>
+      <c r="V10" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>| AIR~ | Air | Aire | ✓ |✕ | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="11" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>| ALGN | Alignment |</v>
+      </c>
+      <c r="Q11" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| ALGN | Alignment | Alineación |</v>
+      </c>
+      <c r="R11" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| ALGN | Alignment | Alineación | ✓ |</v>
+      </c>
+      <c r="S11" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| ALGN | Alignment | Alineación | ✓ |✓ |</v>
+      </c>
+      <c r="T11" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| ALGN | Alignment | Alineación | ✓ |✓ | |</v>
+      </c>
+      <c r="U11" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>| ALGN | Alignment | Alineación | ✓ | ✓ |  |  |</v>
+      </c>
+      <c r="V11" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>| ALGN | Alignment | Alineación | ✓ |✓ | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="12" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>| ALRM | Alarm system |</v>
+      </c>
+      <c r="Q12" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| ALRM | Alarm system | Sistema de alarma |</v>
+      </c>
+      <c r="R12" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| ALRM | Alarm system | Sistema de alarma |  |</v>
+      </c>
+      <c r="S12" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| ALRM | Alarm system | Sistema de alarma |  | |</v>
+      </c>
+      <c r="T12" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| ALRM | Alarm system | Sistema de alarma |  | | |</v>
+      </c>
+      <c r="U12" s="5"/>
+      <c r="V12" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>| ALRM | Alarm system | Sistema de alarma |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="13" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>| ANNO | Annotation |</v>
+      </c>
+      <c r="Q13" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| ANNO | Annotation | Anotación |</v>
+      </c>
+      <c r="R13" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| ANNO | Annotation | Anotación |  |</v>
+      </c>
+      <c r="S13" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| ANNO | Annotation | Anotación |  | |</v>
+      </c>
+      <c r="T13" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| ANNO | Annotation | Anotación |  | | |</v>
+      </c>
+      <c r="U13" s="5"/>
+      <c r="V13" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>| ANNO | Annotation | Anotación |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="14" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>| AREA | Area |</v>
+      </c>
+      <c r="Q14" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| AREA | Area | Área |</v>
+      </c>
+      <c r="R14" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| AREA | Area | Área |  |</v>
+      </c>
+      <c r="S14" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| AREA | Area | Área |  | |</v>
+      </c>
+      <c r="T14" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| AREA | Area | Área |  | | |</v>
+      </c>
+      <c r="U14" s="5"/>
+      <c r="V14" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>| AREA | Area | Área |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="15" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B15" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| AUXL | Auxiliary systems | Sistemas auxiliares |</v>
+      </c>
+      <c r="R15" s="5"/>
+      <c r="S15" s="5"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="5"/>
+      <c r="V15" s="5"/>
+    </row>
+    <row r="16" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| BARR | Barrier | Barrera |</v>
+      </c>
+      <c r="R16" s="5"/>
+      <c r="S16" s="5"/>
+      <c r="T16" s="5"/>
+      <c r="U16" s="5"/>
+      <c r="V16" s="5"/>
+    </row>
+    <row r="17" spans="2:22" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| BCST | Broadcast related system (radio or TV) | Sistema de radiodifusión (radio o TV) |</v>
+      </c>
+      <c r="R17" s="5"/>
+      <c r="S17" s="5"/>
+      <c r="T17" s="5"/>
+      <c r="U17" s="5"/>
+      <c r="V17" s="5"/>
+    </row>
+    <row r="18" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B18" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| BEAM | Beams | Vigas |</v>
+      </c>
+      <c r="R18" s="5"/>
+      <c r="S18" s="5"/>
+      <c r="T18" s="5"/>
+      <c r="U18" s="5"/>
+      <c r="V18" s="5"/>
+    </row>
+    <row r="19" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| BELL | Bell system | Sistema de timbres |</v>
+      </c>
+      <c r="R19" s="5"/>
+      <c r="S19" s="5"/>
+      <c r="T19" s="5"/>
+      <c r="U19" s="5"/>
+      <c r="V19" s="5"/>
+    </row>
+    <row r="20" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| BLDG | Buildings and primary structures | Edificios y estructuras primarias |</v>
+      </c>
+      <c r="R20" s="5"/>
+      <c r="S20" s="5"/>
+      <c r="T20" s="5"/>
+      <c r="U20" s="5"/>
+      <c r="V20" s="5"/>
+    </row>
+    <row r="21" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| BLIN | Baseline | Línea base |</v>
+      </c>
+      <c r="R21" s="5"/>
+      <c r="S21" s="5"/>
+      <c r="T21" s="5"/>
+      <c r="U21" s="5"/>
+      <c r="V21" s="5"/>
+    </row>
+    <row r="22" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| BNDY | Political boundaries | Límites políticos |</v>
+      </c>
+      <c r="R22" s="5"/>
+      <c r="S22" s="5"/>
+      <c r="T22" s="5"/>
+      <c r="U22" s="5"/>
+      <c r="V22" s="5"/>
+    </row>
+    <row r="23" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| BORE | Borings | Perforaciones |</v>
+      </c>
+      <c r="R23" s="5"/>
+      <c r="S23" s="5"/>
+      <c r="T23" s="5"/>
+      <c r="U23" s="5"/>
+      <c r="V23" s="5"/>
+    </row>
+    <row r="24" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B24" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| BRCG | Bracing | Arriostramiento |</v>
+      </c>
+      <c r="R24" s="5"/>
+      <c r="S24" s="5"/>
+      <c r="T24" s="5"/>
+      <c r="U24" s="5"/>
+      <c r="V24" s="5"/>
+    </row>
+    <row r="25" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B25" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| BRDG | Bridge | Puente |</v>
+      </c>
+      <c r="R25" s="5"/>
+      <c r="S25" s="5"/>
+      <c r="T25" s="5"/>
+      <c r="U25" s="5"/>
+      <c r="V25" s="5"/>
+    </row>
+    <row r="26" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B26" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="4"/>
+      <c r="N26" s="4"/>
+      <c r="O26" s="4"/>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| BRIN | Brine systems | Sistemas de salmuera |</v>
+      </c>
+      <c r="R26" s="5"/>
+      <c r="S26" s="5"/>
+      <c r="T26" s="5"/>
+      <c r="U26" s="5"/>
+      <c r="V26" s="5"/>
+    </row>
+    <row r="27" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B27" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="4"/>
+      <c r="N27" s="4"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| BRKL | Break / fault lines | Líneas de rotura/falla |</v>
+      </c>
+      <c r="R27" s="5"/>
+      <c r="S27" s="5"/>
+      <c r="T27" s="5"/>
+      <c r="U27" s="5"/>
+      <c r="V27" s="5"/>
+    </row>
+    <row r="28" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B28" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="4"/>
+      <c r="N28" s="4"/>
+      <c r="O28" s="4"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| BRLN | Building restriction line | Línea de restricción de edificaciones |</v>
+      </c>
+      <c r="R28" s="5"/>
+      <c r="S28" s="5"/>
+      <c r="T28" s="5"/>
+      <c r="U28" s="5"/>
+      <c r="V28" s="5"/>
+    </row>
+    <row r="29" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B29" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="4"/>
+      <c r="N29" s="4"/>
+      <c r="O29" s="4"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| BZNA | Buffer zone area | Zona de amortiguamiento |</v>
+      </c>
+      <c r="R29" s="5"/>
+      <c r="S29" s="5"/>
+      <c r="T29" s="5"/>
+      <c r="U29" s="5"/>
+      <c r="V29" s="5"/>
+    </row>
+    <row r="30" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B30" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="4"/>
+      <c r="O30" s="4"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| CABL | Cable systems | Sistemas de cable |</v>
+      </c>
+      <c r="R30" s="5"/>
+      <c r="S30" s="5"/>
+      <c r="T30" s="5"/>
+      <c r="U30" s="5"/>
+      <c r="V30" s="5"/>
+    </row>
+    <row r="31" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B31" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="4"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| CATH | Cathodic Protection System | Sistema de protección catódica |</v>
+      </c>
+      <c r="R31" s="5"/>
+      <c r="S31" s="5"/>
+      <c r="T31" s="5"/>
+      <c r="U31" s="5"/>
+      <c r="V31" s="5"/>
+    </row>
+    <row r="32" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B32" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="4"/>
+      <c r="O32" s="4"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| CATV | Cable television system | Sistema de televisión por cable |</v>
+      </c>
+      <c r="R32" s="5"/>
+      <c r="S32" s="5"/>
+      <c r="T32" s="5"/>
+      <c r="U32" s="5"/>
+      <c r="V32" s="5"/>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B33" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="4"/>
+      <c r="O33" s="4"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| CCTV | Closed-circuit television system | Sistema de circuito cerrado de televisión |</v>
+      </c>
+      <c r="R33" s="5"/>
+      <c r="S33" s="5"/>
+      <c r="T33" s="5"/>
+      <c r="U33" s="5"/>
+      <c r="V33" s="5"/>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B34" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="4"/>
+      <c r="P34" s="5"/>
+      <c r="Q34" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| CEME | Cemetery | Cementerio |</v>
+      </c>
+      <c r="R34" s="5"/>
+      <c r="S34" s="5"/>
+      <c r="T34" s="5"/>
+      <c r="U34" s="5"/>
+      <c r="V34" s="5"/>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B35" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="4"/>
+      <c r="O35" s="4"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| CHAN | Navigable channels | Canales navegables |</v>
+      </c>
+      <c r="R35" s="5"/>
+      <c r="S35" s="5"/>
+      <c r="T35" s="5"/>
+      <c r="U35" s="5"/>
+      <c r="V35" s="5"/>
+    </row>
+    <row r="36" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B36" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="4"/>
+      <c r="O36" s="4"/>
+      <c r="P36" s="5"/>
+      <c r="Q36" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| CHEM | Chemical | Productos químicos |</v>
+      </c>
+      <c r="R36" s="5"/>
+      <c r="S36" s="5"/>
+      <c r="T36" s="5"/>
+      <c r="U36" s="5"/>
+      <c r="V36" s="5"/>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B37" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="4"/>
+      <c r="O37" s="4"/>
+      <c r="P37" s="5"/>
+      <c r="Q37" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| CHIM | Chimneys and stacks | Chimeneas y conductos |</v>
+      </c>
+      <c r="R37" s="5"/>
+      <c r="S37" s="5"/>
+      <c r="T37" s="5"/>
+      <c r="U37" s="5"/>
+      <c r="V37" s="5"/>
+    </row>
+    <row r="38" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B38" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="E38" s="5"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="4"/>
+      <c r="P38" s="5"/>
+      <c r="Q38" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| CLNG | Ceiling | Techo |</v>
+      </c>
+      <c r="R38" s="5"/>
+      <c r="S38" s="5"/>
+      <c r="T38" s="5"/>
+      <c r="U38" s="5"/>
+      <c r="V38" s="5"/>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B39" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="4"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="5"/>
+      <c r="R39" s="5"/>
+      <c r="S39" s="5"/>
+      <c r="T39" s="5"/>
+      <c r="U39" s="5"/>
+      <c r="V39" s="5"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B40" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="4"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="4"/>
+      <c r="P40" s="5"/>
+      <c r="Q40" s="5"/>
+      <c r="R40" s="5"/>
+      <c r="S40" s="5"/>
+      <c r="T40" s="5"/>
+      <c r="U40" s="5"/>
+      <c r="V40" s="5"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B41" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="4"/>
+      <c r="P41" s="5"/>
+      <c r="Q41" s="5"/>
+      <c r="R41" s="5"/>
+      <c r="S41" s="5"/>
+      <c r="T41" s="5"/>
+      <c r="U41" s="5"/>
+      <c r="V41" s="5"/>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B42" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="4"/>
+      <c r="N42" s="4"/>
+      <c r="O42" s="4"/>
+      <c r="P42" s="5"/>
+      <c r="Q42" s="5"/>
+      <c r="R42" s="5"/>
+      <c r="S42" s="5"/>
+      <c r="T42" s="5"/>
+      <c r="U42" s="5"/>
+      <c r="V42" s="5"/>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B43" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="4"/>
+      <c r="N43" s="4"/>
+      <c r="O43" s="4"/>
+      <c r="P43" s="5"/>
+      <c r="Q43" s="5"/>
+      <c r="R43" s="5"/>
+      <c r="S43" s="5"/>
+      <c r="T43" s="5"/>
+      <c r="U43" s="5"/>
+      <c r="V43" s="5"/>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B44" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="4"/>
+      <c r="N44" s="4"/>
+      <c r="O44" s="4"/>
+      <c r="P44" s="5"/>
+      <c r="Q44" s="5"/>
+      <c r="R44" s="5"/>
+      <c r="S44" s="5"/>
+      <c r="T44" s="5"/>
+      <c r="U44" s="5"/>
+      <c r="V44" s="5"/>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B45" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="4"/>
+      <c r="N45" s="4"/>
+      <c r="O45" s="4"/>
+      <c r="P45" s="5" t="str">
+        <f t="shared" ref="P45:P103" si="7">_xlfn.CONCAT("| ",B45," | ",C45," |")</f>
+        <v>| COLS | Columns |</v>
+      </c>
+      <c r="Q45" s="5" t="str">
+        <f t="shared" ref="Q45:Q103" si="8">_xlfn.CONCAT("| ",B45," | ",C45," | ",D45," |")</f>
+        <v>| COLS | Columns | Columnas |</v>
+      </c>
+      <c r="R45" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| COLS | Columns | Columnas |  |</v>
+      </c>
+      <c r="S45" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| COLS | Columns | Columnas |  | |</v>
+      </c>
+      <c r="T45" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| COLS | Columns | Columnas |  | | |</v>
+      </c>
+      <c r="U45" s="5"/>
+      <c r="V45" s="5" t="str">
+        <f t="shared" ref="V45:V103" si="9">_xlfn.CONCAT("| ",B45," | ",C45," | ",D45," | ",E45," |",F45," |",G45," |",H45," |",I45," |",J45," |",K45," |",L45," |",M45," |",N45," |")</f>
+        <v>| COLS | Columns | Columnas |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B46" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
+      <c r="M46" s="4"/>
+      <c r="N46" s="4"/>
+      <c r="O46" s="4"/>
+      <c r="P46" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| COMM | Communications |</v>
+      </c>
+      <c r="Q46" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| COMM | Communications | Comunicaciones |</v>
+      </c>
+      <c r="R46" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| COMM | Communications | Comunicaciones |  |</v>
+      </c>
+      <c r="S46" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| COMM | Communications | Comunicaciones |  | |</v>
+      </c>
+      <c r="T46" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| COMM | Communications | Comunicaciones |  | | |</v>
+      </c>
+      <c r="U46" s="5"/>
+      <c r="V46" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| COMM | Communications | Comunicaciones |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B47" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="4"/>
+      <c r="N47" s="4"/>
+      <c r="O47" s="4"/>
+      <c r="P47" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| CONT | Controls and instrumentation |</v>
+      </c>
+      <c r="Q47" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| CONT | Controls and instrumentation | Controles e instrumentación |</v>
+      </c>
+      <c r="R47" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| CONT | Controls and instrumentation | Controles e instrumentación |  |</v>
+      </c>
+      <c r="S47" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| CONT | Controls and instrumentation | Controles e instrumentación |  | |</v>
+      </c>
+      <c r="T47" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| CONT | Controls and instrumentation | Controles e instrumentación |  | | |</v>
+      </c>
+      <c r="U47" s="5"/>
+      <c r="V47" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| CONT | Controls and instrumentation | Controles e instrumentación |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B48" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="4"/>
+      <c r="N48" s="4"/>
+      <c r="O48" s="4"/>
+      <c r="P48" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| CONV | Conveying systems |</v>
+      </c>
+      <c r="Q48" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| CONV | Conveying systems | Sistemas de transporte |</v>
+      </c>
+      <c r="R48" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| CONV | Conveying systems | Sistemas de transporte |  |</v>
+      </c>
+      <c r="S48" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| CONV | Conveying systems | Sistemas de transporte |  | |</v>
+      </c>
+      <c r="T48" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| CONV | Conveying systems | Sistemas de transporte |  | | |</v>
+      </c>
+      <c r="U48" s="5"/>
+      <c r="V48" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| CONV | Conveying systems | Sistemas de transporte |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="49" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B49" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="4"/>
+      <c r="N49" s="4"/>
+      <c r="O49" s="4"/>
+      <c r="P49" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| CRPT | Carpet / carpet tiles |</v>
+      </c>
+      <c r="Q49" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| CRPT | Carpet / carpet tiles | Alfombra/losetas de moqueta |</v>
+      </c>
+      <c r="R49" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| CRPT | Carpet / carpet tiles | Alfombra/losetas de moqueta |  |</v>
+      </c>
+      <c r="S49" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| CRPT | Carpet / carpet tiles | Alfombra/losetas de moqueta |  | |</v>
+      </c>
+      <c r="T49" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| CRPT | Carpet / carpet tiles | Alfombra/losetas de moqueta |  | | |</v>
+      </c>
+      <c r="U49" s="5"/>
+      <c r="V49" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| CRPT | Carpet / carpet tiles | Alfombra/losetas de moqueta |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="50" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B50" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="4"/>
+      <c r="N50" s="4"/>
+      <c r="O50" s="4"/>
+      <c r="P50" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| CSWK | Casework |</v>
+      </c>
+      <c r="Q50" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| CSWK | Casework | Carpintería |</v>
+      </c>
+      <c r="R50" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| CSWK | Casework | Carpintería |  |</v>
+      </c>
+      <c r="S50" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| CSWK | Casework | Carpintería |  | |</v>
+      </c>
+      <c r="T50" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| CSWK | Casework | Carpintería |  | | |</v>
+      </c>
+      <c r="U50" s="5"/>
+      <c r="V50" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| CSWK | Casework | Carpintería |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="51" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B51" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="4"/>
+      <c r="N51" s="4"/>
+      <c r="O51" s="4"/>
+      <c r="P51" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| CTRL | Control points |</v>
+      </c>
+      <c r="Q51" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| CTRL | Control points | Puntos de control |</v>
+      </c>
+      <c r="R51" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| CTRL | Control points | Puntos de control |  |</v>
+      </c>
+      <c r="S51" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| CTRL | Control points | Puntos de control |  | |</v>
+      </c>
+      <c r="T51" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| CTRL | Control points | Puntos de control |  | | |</v>
+      </c>
+      <c r="U51" s="5"/>
+      <c r="V51" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| CTRL | Control points | Puntos de control |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="52" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B52" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="4"/>
+      <c r="L52" s="4"/>
+      <c r="M52" s="4"/>
+      <c r="N52" s="4"/>
+      <c r="O52" s="4"/>
+      <c r="P52" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| CWTR | Chilled water systems |</v>
+      </c>
+      <c r="Q52" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| CWTR | Chilled water systems | Sistemas de agua refrigerada |</v>
+      </c>
+      <c r="R52" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| CWTR | Chilled water systems | Sistemas de agua refrigerada |  |</v>
+      </c>
+      <c r="S52" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| CWTR | Chilled water systems | Sistemas de agua refrigerada |  | |</v>
+      </c>
+      <c r="T52" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| CWTR | Chilled water systems | Sistemas de agua refrigerada |  | | |</v>
+      </c>
+      <c r="U52" s="5"/>
+      <c r="V52" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| CWTR | Chilled water systems | Sistemas de agua refrigerada |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="53" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B53" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="4"/>
+      <c r="N53" s="4"/>
+      <c r="O53" s="4"/>
+      <c r="P53" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| DATA | Data / LAN system |</v>
+      </c>
+      <c r="Q53" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| DATA | Data / LAN system | Datos/LAN Sistema |</v>
+      </c>
+      <c r="R53" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| DATA | Data / LAN system | Datos/LAN Sistema |  |</v>
+      </c>
+      <c r="S53" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| DATA | Data / LAN system | Datos/LAN Sistema |  | |</v>
+      </c>
+      <c r="T53" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| DATA | Data / LAN system | Datos/LAN Sistema |  | | |</v>
+      </c>
+      <c r="U53" s="5"/>
+      <c r="V53" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| DATA | Data / LAN system | Datos/LAN Sistema |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="54" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B54" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
+      <c r="K54" s="4"/>
+      <c r="L54" s="4"/>
+      <c r="M54" s="4"/>
+      <c r="N54" s="4"/>
+      <c r="O54" s="4"/>
+      <c r="P54" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| DECK | Deck |</v>
+      </c>
+      <c r="Q54" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| DECK | Deck | Cubierta |</v>
+      </c>
+      <c r="R54" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| DECK | Deck | Cubierta |  |</v>
+      </c>
+      <c r="S54" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| DECK | Deck | Cubierta |  | |</v>
+      </c>
+      <c r="T54" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| DECK | Deck | Cubierta |  | | |</v>
+      </c>
+      <c r="U54" s="5"/>
+      <c r="V54" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| DECK | Deck | Cubierta |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="55" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B55" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="4"/>
+      <c r="L55" s="4"/>
+      <c r="M55" s="4"/>
+      <c r="N55" s="4"/>
+      <c r="O55" s="4"/>
+      <c r="P55" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| DETL | Detail |</v>
+      </c>
+      <c r="Q55" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| DETL | Detail | Detalle |</v>
+      </c>
+      <c r="R55" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| DETL | Detail | Detalle |  |</v>
+      </c>
+      <c r="S55" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| DETL | Detail | Detalle |  | |</v>
+      </c>
+      <c r="T55" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| DETL | Detail | Detalle |  | | |</v>
+      </c>
+      <c r="U55" s="5"/>
+      <c r="V55" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| DETL | Detail | Detalle |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="56" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B56" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
+      <c r="L56" s="4"/>
+      <c r="M56" s="4"/>
+      <c r="N56" s="4"/>
+      <c r="O56" s="4"/>
+      <c r="P56" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| DFLD | Drain fields |</v>
+      </c>
+      <c r="Q56" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| DFLD | Drain fields | Campos de drenaje |</v>
+      </c>
+      <c r="R56" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| DFLD | Drain fields | Campos de drenaje |  |</v>
+      </c>
+      <c r="S56" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| DFLD | Drain fields | Campos de drenaje |  | |</v>
+      </c>
+      <c r="T56" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| DFLD | Drain fields | Campos de drenaje |  | | |</v>
+      </c>
+      <c r="U56" s="5"/>
+      <c r="V56" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| DFLD | Drain fields | Campos de drenaje |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="57" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B57" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4"/>
+      <c r="L57" s="4"/>
+      <c r="M57" s="4"/>
+      <c r="N57" s="4"/>
+      <c r="O57" s="4"/>
+      <c r="P57" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| DIAG | Diagrams |</v>
+      </c>
+      <c r="Q57" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| DIAG | Diagrams | Diagramas |</v>
+      </c>
+      <c r="R57" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| DIAG | Diagrams | Diagramas |  |</v>
+      </c>
+      <c r="S57" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| DIAG | Diagrams | Diagramas |  | |</v>
+      </c>
+      <c r="T57" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| DIAG | Diagrams | Diagramas |  | | |</v>
+      </c>
+      <c r="U57" s="5"/>
+      <c r="V57" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| DIAG | Diagrams | Diagramas |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="58" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B58" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="4"/>
+      <c r="L58" s="4"/>
+      <c r="M58" s="4"/>
+      <c r="N58" s="4"/>
+      <c r="O58" s="4"/>
+      <c r="P58" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| DICT | Dictation system |</v>
+      </c>
+      <c r="Q58" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| DICT | Dictation system | Sistema de dictado |</v>
+      </c>
+      <c r="R58" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| DICT | Dictation system | Sistema de dictado |  |</v>
+      </c>
+      <c r="S58" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| DICT | Dictation system | Sistema de dictado |  | |</v>
+      </c>
+      <c r="T58" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| DICT | Dictation system | Sistema de dictado |  | | |</v>
+      </c>
+      <c r="U58" s="5"/>
+      <c r="V58" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| DICT | Dictation system | Sistema de dictado |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="59" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B59" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
+      <c r="K59" s="4"/>
+      <c r="L59" s="4"/>
+      <c r="M59" s="4"/>
+      <c r="N59" s="4"/>
+      <c r="O59" s="4"/>
+      <c r="P59" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| DOMW | Domestic water systems |</v>
+      </c>
+      <c r="Q59" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| DOMW | Domestic water systems | Sistemas de agua potable |</v>
+      </c>
+      <c r="R59" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| DOMW | Domestic water systems | Sistemas de agua potable |  |</v>
+      </c>
+      <c r="S59" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| DOMW | Domestic water systems | Sistemas de agua potable |  | |</v>
+      </c>
+      <c r="T59" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| DOMW | Domestic water systems | Sistemas de agua potable |  | | |</v>
+      </c>
+      <c r="U59" s="5"/>
+      <c r="V59" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| DOMW | Domestic water systems | Sistemas de agua potable |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="60" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B60" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="4"/>
+      <c r="L60" s="4"/>
+      <c r="M60" s="4"/>
+      <c r="N60" s="4"/>
+      <c r="O60" s="4"/>
+      <c r="P60" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| DOOR | Doors |</v>
+      </c>
+      <c r="Q60" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| DOOR | Doors | Puertas |</v>
+      </c>
+      <c r="R60" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| DOOR | Doors | Puertas |  |</v>
+      </c>
+      <c r="S60" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| DOOR | Doors | Puertas |  | |</v>
+      </c>
+      <c r="T60" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| DOOR | Doors | Puertas |  | | |</v>
+      </c>
+      <c r="U60" s="5"/>
+      <c r="V60" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| DOOR | Doors | Puertas |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="61" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B61" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="4"/>
+      <c r="L61" s="4"/>
+      <c r="M61" s="4"/>
+      <c r="N61" s="4"/>
+      <c r="O61" s="4"/>
+      <c r="P61" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| DRAN | Drains |</v>
+      </c>
+      <c r="Q61" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| DRAN | Drains | Desagües |</v>
+      </c>
+      <c r="R61" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| DRAN | Drains | Desagües |  |</v>
+      </c>
+      <c r="S61" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| DRAN | Drains | Desagües |  | |</v>
+      </c>
+      <c r="T61" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| DRAN | Drains | Desagües |  | | |</v>
+      </c>
+      <c r="U61" s="5"/>
+      <c r="V61" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| DRAN | Drains | Desagües |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="62" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B62" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4"/>
+      <c r="L62" s="4"/>
+      <c r="M62" s="4"/>
+      <c r="N62" s="4"/>
+      <c r="O62" s="4"/>
+      <c r="P62" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| DRIV | Driveways |</v>
+      </c>
+      <c r="Q62" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| DRIV | Driveways | Entradas de vehículos |</v>
+      </c>
+      <c r="R62" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| DRIV | Driveways | Entradas de vehículos |  |</v>
+      </c>
+      <c r="S62" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| DRIV | Driveways | Entradas de vehículos |  | |</v>
+      </c>
+      <c r="T62" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| DRIV | Driveways | Entradas de vehículos |  | | |</v>
+      </c>
+      <c r="U62" s="5"/>
+      <c r="V62" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| DRIV | Driveways | Entradas de vehículos |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="63" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B63" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="4"/>
+      <c r="L63" s="4"/>
+      <c r="M63" s="4"/>
+      <c r="N63" s="4"/>
+      <c r="O63" s="4"/>
+      <c r="P63" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| DTCH | Ditches or washes |</v>
+      </c>
+      <c r="Q63" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| DTCH | Ditches or washes | Cunetas o lavaderos |</v>
+      </c>
+      <c r="R63" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| DTCH | Ditches or washes | Cunetas o lavaderos |  |</v>
+      </c>
+      <c r="S63" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| DTCH | Ditches or washes | Cunetas o lavaderos |  | |</v>
+      </c>
+      <c r="T63" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| DTCH | Ditches or washes | Cunetas o lavaderos |  | | |</v>
+      </c>
+      <c r="U63" s="5"/>
+      <c r="V63" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| DTCH | Ditches or washes | Cunetas o lavaderos |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="64" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B64" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="4"/>
+      <c r="L64" s="4"/>
+      <c r="M64" s="4"/>
+      <c r="N64" s="4"/>
+      <c r="O64" s="4"/>
+      <c r="P64" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| DUAL | Dual temperature systems |</v>
+      </c>
+      <c r="Q64" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| DUAL | Dual temperature systems | Sistemas de doble temperatura |</v>
+      </c>
+      <c r="R64" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| DUAL | Dual temperature systems | Sistemas de doble temperatura |  |</v>
+      </c>
+      <c r="S64" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| DUAL | Dual temperature systems | Sistemas de doble temperatura |  | |</v>
+      </c>
+      <c r="T64" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| DUAL | Dual temperature systems | Sistemas de doble temperatura |  | | |</v>
+      </c>
+      <c r="U64" s="5"/>
+      <c r="V64" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| DUAL | Dual temperature systems | Sistemas de doble temperatura |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B65" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="4"/>
+      <c r="L65" s="4"/>
+      <c r="M65" s="4"/>
+      <c r="N65" s="4"/>
+      <c r="O65" s="4"/>
+      <c r="P65" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| DUST | Dust and fume collection systems |</v>
+      </c>
+      <c r="Q65" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| DUST | Dust and fume collection systems | Sistemas de recolección de polvo y humos |</v>
+      </c>
+      <c r="R65" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| DUST | Dust and fume collection systems | Sistemas de recolección de polvo y humos |  |</v>
+      </c>
+      <c r="S65" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| DUST | Dust and fume collection systems | Sistemas de recolección de polvo y humos |  | |</v>
+      </c>
+      <c r="T65" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| DUST | Dust and fume collection systems | Sistemas de recolección de polvo y humos |  | | |</v>
+      </c>
+      <c r="U65" s="5"/>
+      <c r="V65" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| DUST | Dust and fume collection systems | Sistemas de recolección de polvo y humos |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B66" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="4"/>
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="4"/>
+      <c r="L66" s="4"/>
+      <c r="M66" s="4"/>
+      <c r="N66" s="4"/>
+      <c r="O66" s="4"/>
+      <c r="P66" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| ELEC | Electrical system, telecom plan |</v>
+      </c>
+      <c r="Q66" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| ELEC | Electrical system, telecom plan | Sistema eléctrico, plano de telecomunicaciones |</v>
+      </c>
+      <c r="R66" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| ELEC | Electrical system, telecom plan | Sistema eléctrico, plano de telecomunicaciones |  |</v>
+      </c>
+      <c r="S66" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| ELEC | Electrical system, telecom plan | Sistema eléctrico, plano de telecomunicaciones |  | |</v>
+      </c>
+      <c r="T66" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| ELEC | Electrical system, telecom plan | Sistema eléctrico, plano de telecomunicaciones |  | | |</v>
+      </c>
+      <c r="U66" s="5"/>
+      <c r="V66" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| ELEC | Electrical system, telecom plan | Sistema eléctrico, plano de telecomunicaciones |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B67" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="4"/>
+      <c r="L67" s="4"/>
+      <c r="M67" s="4"/>
+      <c r="N67" s="4"/>
+      <c r="O67" s="4"/>
+      <c r="P67" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| ELEV | Elevation |</v>
+      </c>
+      <c r="Q67" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| ELEV | Elevation | Elevación |</v>
+      </c>
+      <c r="R67" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| ELEV | Elevation | Elevación |  |</v>
+      </c>
+      <c r="S67" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| ELEV | Elevation | Elevación |  | |</v>
+      </c>
+      <c r="T67" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>| ELEV | Elevation | Elevación |  | | |</v>
+      </c>
+      <c r="U67" s="5"/>
+      <c r="V67" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| ELEV | Elevation | Elevación |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B68" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="4"/>
+      <c r="L68" s="4"/>
+      <c r="M68" s="4"/>
+      <c r="N68" s="4"/>
+      <c r="O68" s="4"/>
+      <c r="P68" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| ELHT | Electric heat |</v>
+      </c>
+      <c r="Q68" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| ELHT | Electric heat | Calefacción eléctrica |</v>
+      </c>
+      <c r="R68" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| ELHT | Electric heat | Calefacción eléctrica |  |</v>
+      </c>
+      <c r="S68" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| ELHT | Electric heat | Calefacción eléctrica |  | |</v>
+      </c>
+      <c r="T68" s="5" t="str">
+        <f t="shared" ref="T68:T103" si="10">_xlfn.CONCAT("| ",B68," | ",C68," | ",D68," | ",E68," |",F68," |",G68," |")</f>
+        <v>| ELHT | Electric heat | Calefacción eléctrica |  | | |</v>
+      </c>
+      <c r="U68" s="5"/>
+      <c r="V68" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| ELHT | Electric heat | Calefacción eléctrica |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B69" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="4"/>
+      <c r="L69" s="4"/>
+      <c r="M69" s="4"/>
+      <c r="N69" s="4"/>
+      <c r="O69" s="4"/>
+      <c r="P69" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| EMCS | Energy monitoring control system |</v>
+      </c>
+      <c r="Q69" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| EMCS | Energy monitoring control system | Sistema de control de monitoreo de energía |</v>
+      </c>
+      <c r="R69" s="5" t="str">
+        <f t="shared" si="5"/>
+        <v>| EMCS | Energy monitoring control system | Sistema de control de monitoreo de energía |  |</v>
+      </c>
+      <c r="S69" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>| EMCS | Energy monitoring control system | Sistema de control de monitoreo de energía |  | |</v>
+      </c>
+      <c r="T69" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| EMCS | Energy monitoring control system | Sistema de control de monitoreo de energía |  | | |</v>
+      </c>
+      <c r="U69" s="5"/>
+      <c r="V69" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| EMCS | Energy monitoring control system | Sistema de control de monitoreo de energía |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B70" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
+      <c r="J70" s="4"/>
+      <c r="K70" s="4"/>
+      <c r="L70" s="4"/>
+      <c r="M70" s="4"/>
+      <c r="N70" s="4"/>
+      <c r="O70" s="4"/>
+      <c r="P70" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| ENER | Energy management systems |</v>
+      </c>
+      <c r="Q70" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| ENER | Energy management systems | Sistemas de gestión de energía |</v>
+      </c>
+      <c r="R70" s="5" t="str">
+        <f t="shared" ref="R70:R103" si="11">_xlfn.CONCAT("| ",B70," | ",C70," | ",D70," | ",E70," |")</f>
+        <v>| ENER | Energy management systems | Sistemas de gestión de energía |  |</v>
+      </c>
+      <c r="S70" s="5" t="str">
+        <f t="shared" ref="S70:S103" si="12">_xlfn.CONCAT("| ",B70," | ",C70," | ",D70," | ",E70," |",F70," |")</f>
+        <v>| ENER | Energy management systems | Sistemas de gestión de energía |  | |</v>
+      </c>
+      <c r="T70" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| ENER | Energy management systems | Sistemas de gestión de energía |  | | |</v>
+      </c>
+      <c r="U70" s="5"/>
+      <c r="V70" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| ENER | Energy management systems | Sistemas de gestión de energía |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B71" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="4"/>
+      <c r="L71" s="4"/>
+      <c r="M71" s="4"/>
+      <c r="N71" s="4"/>
+      <c r="O71" s="4"/>
+      <c r="P71" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| EQPM | Equipment |</v>
+      </c>
+      <c r="Q71" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| EQPM | Equipment | Equipo |</v>
+      </c>
+      <c r="R71" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>| EQPM | Equipment | Equipo |  |</v>
+      </c>
+      <c r="S71" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>| EQPM | Equipment | Equipo |  | |</v>
+      </c>
+      <c r="T71" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| EQPM | Equipment | Equipo |  | | |</v>
+      </c>
+      <c r="U71" s="5"/>
+      <c r="V71" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| EQPM | Equipment | Equipo |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B72" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="4"/>
+      <c r="M72" s="4"/>
+      <c r="N72" s="4"/>
+      <c r="O72" s="4"/>
+      <c r="P72" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| EROS | Erosion and sediment control |</v>
+      </c>
+      <c r="Q72" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| EROS | Erosion and sediment control | Control de erosión y sedimentos |</v>
+      </c>
+      <c r="R72" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>| EROS | Erosion and sediment control | Control de erosión y sedimentos |  |</v>
+      </c>
+      <c r="S72" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>| EROS | Erosion and sediment control | Control de erosión y sedimentos |  | |</v>
+      </c>
+      <c r="T72" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| EROS | Erosion and sediment control | Control de erosión y sedimentos |  | | |</v>
+      </c>
+      <c r="U72" s="5"/>
+      <c r="V72" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| EROS | Erosion and sediment control | Control de erosión y sedimentos |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B73" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+      <c r="G73" s="4"/>
+      <c r="H73" s="4"/>
+      <c r="I73" s="4"/>
+      <c r="J73" s="4"/>
+      <c r="K73" s="4"/>
+      <c r="L73" s="4"/>
+      <c r="M73" s="4"/>
+      <c r="N73" s="4"/>
+      <c r="O73" s="4"/>
+      <c r="P73" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| ESMT | Easements |</v>
+      </c>
+      <c r="Q73" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| ESMT | Easements | Servidumbres |</v>
+      </c>
+      <c r="R73" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>| ESMT | Easements | Servidumbres |  |</v>
+      </c>
+      <c r="S73" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>| ESMT | Easements | Servidumbres |  | |</v>
+      </c>
+      <c r="T73" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| ESMT | Easements | Servidumbres |  | | |</v>
+      </c>
+      <c r="U73" s="5"/>
+      <c r="V73" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| ESMT | Easements | Servidumbres |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B74" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4"/>
+      <c r="M74" s="4"/>
+      <c r="N74" s="4"/>
+      <c r="O74" s="4"/>
+      <c r="P74" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| EVAC | Evacuation plan |</v>
+      </c>
+      <c r="Q74" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| EVAC | Evacuation plan | Plan de evacuación |</v>
+      </c>
+      <c r="R74" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>| EVAC | Evacuation plan | Plan de evacuación |  |</v>
+      </c>
+      <c r="S74" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>| EVAC | Evacuation plan | Plan de evacuación |  | |</v>
+      </c>
+      <c r="T74" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| EVAC | Evacuation plan | Plan de evacuación |  | | |</v>
+      </c>
+      <c r="U74" s="5"/>
+      <c r="V74" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| EVAC | Evacuation plan | Plan de evacuación |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B75" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+      <c r="G75" s="4"/>
+      <c r="H75" s="4"/>
+      <c r="I75" s="4"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="4"/>
+      <c r="L75" s="4"/>
+      <c r="M75" s="4"/>
+      <c r="N75" s="4"/>
+      <c r="O75" s="4"/>
+      <c r="P75" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| EXHS | Exhaust system |</v>
+      </c>
+      <c r="Q75" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| EXHS | Exhaust system | Sistema de extracción |</v>
+      </c>
+      <c r="R75" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>| EXHS | Exhaust system | Sistema de extracción |  |</v>
+      </c>
+      <c r="S75" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>| EXHS | Exhaust system | Sistema de extracción |  | |</v>
+      </c>
+      <c r="T75" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| EXHS | Exhaust system | Sistema de extracción |  | | |</v>
+      </c>
+      <c r="U75" s="5"/>
+      <c r="V75" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| EXHS | Exhaust system | Sistema de extracción |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B76" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+      <c r="G76" s="4"/>
+      <c r="H76" s="4"/>
+      <c r="I76" s="4"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="4"/>
+      <c r="L76" s="4"/>
+      <c r="M76" s="4"/>
+      <c r="N76" s="4"/>
+      <c r="O76" s="4"/>
+      <c r="P76" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| FENC | Fences |</v>
+      </c>
+      <c r="Q76" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| FENC | Fences | Cercas |</v>
+      </c>
+      <c r="R76" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>| FENC | Fences | Cercas |  |</v>
+      </c>
+      <c r="S76" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>| FENC | Fences | Cercas |  | |</v>
+      </c>
+      <c r="T76" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| FENC | Fences | Cercas |  | | |</v>
+      </c>
+      <c r="U76" s="5"/>
+      <c r="V76" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| FENC | Fences | Cercas |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B77" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="4"/>
+      <c r="I77" s="4"/>
+      <c r="J77" s="4"/>
+      <c r="K77" s="4"/>
+      <c r="L77" s="4"/>
+      <c r="M77" s="4"/>
+      <c r="N77" s="4"/>
+      <c r="O77" s="4"/>
+      <c r="P77" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| FIRE | Fire protection |</v>
+      </c>
+      <c r="Q77" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| FIRE | Fire protection | Protección contra incendios |</v>
+      </c>
+      <c r="R77" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>| FIRE | Fire protection | Protección contra incendios |  |</v>
+      </c>
+      <c r="S77" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>| FIRE | Fire protection | Protección contra incendios |  | |</v>
+      </c>
+      <c r="T77" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| FIRE | Fire protection | Protección contra incendios |  | | |</v>
+      </c>
+      <c r="U77" s="5"/>
+      <c r="V77" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| FIRE | Fire protection | Protección contra incendios |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="78" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B78" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="4"/>
+      <c r="I78" s="4"/>
+      <c r="J78" s="4"/>
+      <c r="K78" s="4"/>
+      <c r="L78" s="4"/>
+      <c r="M78" s="4"/>
+      <c r="N78" s="4"/>
+      <c r="O78" s="4"/>
+      <c r="P78" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| FLHA | Flood hazard area |</v>
+      </c>
+      <c r="Q78" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| FLHA | Flood hazard area | Zona con riesgo de inundación |</v>
+      </c>
+      <c r="R78" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>| FLHA | Flood hazard area | Zona con riesgo de inundación |  |</v>
+      </c>
+      <c r="S78" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>| FLHA | Flood hazard area | Zona con riesgo de inundación |  | |</v>
+      </c>
+      <c r="T78" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| FLHA | Flood hazard area | Zona con riesgo de inundación |  | | |</v>
+      </c>
+      <c r="U78" s="5"/>
+      <c r="V78" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| FLHA | Flood hazard area | Zona con riesgo de inundación |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B79" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+      <c r="I79" s="4"/>
+      <c r="J79" s="4"/>
+      <c r="K79" s="4"/>
+      <c r="L79" s="4"/>
+      <c r="M79" s="4"/>
+      <c r="N79" s="4"/>
+      <c r="O79" s="4"/>
+      <c r="P79" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| FLOR | Floor |</v>
+      </c>
+      <c r="Q79" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| FLOR | Floor | Piso |</v>
+      </c>
+      <c r="R79" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>| FLOR | Floor | Piso |  |</v>
+      </c>
+      <c r="S79" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>| FLOR | Floor | Piso |  | |</v>
+      </c>
+      <c r="T79" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| FLOR | Floor | Piso |  | | |</v>
+      </c>
+      <c r="U79" s="5"/>
+      <c r="V79" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| FLOR | Floor | Piso |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="80" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B80" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+      <c r="G80" s="4"/>
+      <c r="H80" s="4"/>
+      <c r="I80" s="4"/>
+      <c r="J80" s="4"/>
+      <c r="K80" s="4"/>
+      <c r="L80" s="4"/>
+      <c r="M80" s="4"/>
+      <c r="N80" s="4"/>
+      <c r="O80" s="4"/>
+      <c r="P80" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| FNDN | Foundation |</v>
+      </c>
+      <c r="Q80" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| FNDN | Foundation | Cimentación |</v>
+      </c>
+      <c r="R80" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>| FNDN | Foundation | Cimentación |  |</v>
+      </c>
+      <c r="S80" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>| FNDN | Foundation | Cimentación |  | |</v>
+      </c>
+      <c r="T80" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| FNDN | Foundation | Cimentación |  | | |</v>
+      </c>
+      <c r="U80" s="5"/>
+      <c r="V80" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| FNDN | Foundation | Cimentación |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="81" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B81" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
+      <c r="G81" s="4"/>
+      <c r="H81" s="4"/>
+      <c r="I81" s="4"/>
+      <c r="J81" s="4"/>
+      <c r="K81" s="4"/>
+      <c r="L81" s="4"/>
+      <c r="M81" s="4"/>
+      <c r="N81" s="4"/>
+      <c r="O81" s="4"/>
+      <c r="P81" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| FNSH | Finishes |</v>
+      </c>
+      <c r="Q81" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| FNSH | Finishes | Acabados |</v>
+      </c>
+      <c r="R81" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>| FNSH | Finishes | Acabados |  |</v>
+      </c>
+      <c r="S81" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>| FNSH | Finishes | Acabados |  | |</v>
+      </c>
+      <c r="T81" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| FNSH | Finishes | Acabados |  | | |</v>
+      </c>
+      <c r="U81" s="5"/>
+      <c r="V81" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| FNSH | Finishes | Acabados |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="82" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B82" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4"/>
+      <c r="I82" s="4"/>
+      <c r="J82" s="4"/>
+      <c r="K82" s="4"/>
+      <c r="L82" s="4"/>
+      <c r="M82" s="4"/>
+      <c r="N82" s="4"/>
+      <c r="O82" s="4"/>
+      <c r="P82" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| FRAM | Braced frame or moment frame |</v>
+      </c>
+      <c r="Q82" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| FRAM | Braced frame or moment frame | Marco arriostrado o marco de momento |</v>
+      </c>
+      <c r="R82" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>| FRAM | Braced frame or moment frame | Marco arriostrado o marco de momento |  |</v>
+      </c>
+      <c r="S82" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>| FRAM | Braced frame or moment frame | Marco arriostrado o marco de momento |  | |</v>
+      </c>
+      <c r="T82" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| FRAM | Braced frame or moment frame | Marco arriostrado o marco de momento |  | | |</v>
+      </c>
+      <c r="U82" s="5"/>
+      <c r="V82" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| FRAM | Braced frame or moment frame | Marco arriostrado o marco de momento |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="83" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B83" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+      <c r="G83" s="4"/>
+      <c r="H83" s="4"/>
+      <c r="I83" s="4"/>
+      <c r="J83" s="4"/>
+      <c r="K83" s="4"/>
+      <c r="L83" s="4"/>
+      <c r="M83" s="4"/>
+      <c r="N83" s="4"/>
+      <c r="O83" s="4"/>
+      <c r="P83" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| FSTN | Fasteners and connections |</v>
+      </c>
+      <c r="Q83" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| FSTN | Fasteners and connections | Sujeciones y conexiones |</v>
+      </c>
+      <c r="R83" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>| FSTN | Fasteners and connections | Sujeciones y conexiones |  |</v>
+      </c>
+      <c r="S83" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>| FSTN | Fasteners and connections | Sujeciones y conexiones |  | |</v>
+      </c>
+      <c r="T83" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| FSTN | Fasteners and connections | Sujeciones y conexiones |  | | |</v>
+      </c>
+      <c r="U83" s="5"/>
+      <c r="V83" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| FSTN | Fasteners and connections | Sujeciones y conexiones |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="84" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B84" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="4"/>
+      <c r="H84" s="4"/>
+      <c r="I84" s="4"/>
+      <c r="J84" s="4"/>
+      <c r="K84" s="4"/>
+      <c r="L84" s="4"/>
+      <c r="M84" s="4"/>
+      <c r="N84" s="4"/>
+      <c r="O84" s="4"/>
+      <c r="P84" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| FUEL | Fuel systems |</v>
+      </c>
+      <c r="Q84" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| FUEL | Fuel systems | Sistemas de combustible |</v>
+      </c>
+      <c r="R84" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>| FUEL | Fuel systems | Sistemas de combustible |  |</v>
+      </c>
+      <c r="S84" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>| FUEL | Fuel systems | Sistemas de combustible |  | |</v>
+      </c>
+      <c r="T84" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| FUEL | Fuel systems | Sistemas de combustible |  | | |</v>
+      </c>
+      <c r="U84" s="5"/>
+      <c r="V84" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| FUEL | Fuel systems | Sistemas de combustible |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="85" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B85" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+      <c r="G85" s="4"/>
+      <c r="H85" s="4"/>
+      <c r="I85" s="4"/>
+      <c r="J85" s="4"/>
+      <c r="K85" s="4"/>
+      <c r="L85" s="4"/>
+      <c r="M85" s="4"/>
+      <c r="N85" s="4"/>
+      <c r="O85" s="4"/>
+      <c r="P85" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| FUME | Fume hood |</v>
+      </c>
+      <c r="Q85" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| FUME | Fume hood | Campana de extracción de gases |</v>
+      </c>
+      <c r="R85" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>| FUME | Fume hood | Campana de extracción de gases |  |</v>
+      </c>
+      <c r="S85" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>| FUME | Fume hood | Campana de extracción de gases |  | |</v>
+      </c>
+      <c r="T85" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| FUME | Fume hood | Campana de extracción de gases |  | | |</v>
+      </c>
+      <c r="U85" s="5"/>
+      <c r="V85" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| FUME | Fume hood | Campana de extracción de gases |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="86" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B86" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+      <c r="G86" s="4"/>
+      <c r="H86" s="4"/>
+      <c r="I86" s="4"/>
+      <c r="J86" s="4"/>
+      <c r="K86" s="4"/>
+      <c r="L86" s="4"/>
+      <c r="M86" s="4"/>
+      <c r="N86" s="4"/>
+      <c r="O86" s="4"/>
+      <c r="P86" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| FURN | Furnishings |</v>
+      </c>
+      <c r="Q86" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| FURN | Furnishings | Mobiliario |</v>
+      </c>
+      <c r="R86" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>| FURN | Furnishings | Mobiliario |  |</v>
+      </c>
+      <c r="S86" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>| FURN | Furnishings | Mobiliario |  | |</v>
+      </c>
+      <c r="T86" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| FURN | Furnishings | Mobiliario |  | | |</v>
+      </c>
+      <c r="U86" s="5"/>
+      <c r="V86" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| FURN | Furnishings | Mobiliario |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="87" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B87" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="E87" s="4"/>
+      <c r="F87" s="4"/>
+      <c r="G87" s="4"/>
+      <c r="H87" s="4"/>
+      <c r="I87" s="4"/>
+      <c r="J87" s="4"/>
+      <c r="K87" s="4"/>
+      <c r="L87" s="4"/>
+      <c r="M87" s="4"/>
+      <c r="N87" s="4"/>
+      <c r="O87" s="4"/>
+      <c r="P87" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| GAS~ | Gas |</v>
+      </c>
+      <c r="Q87" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| GAS~ | Gas | Gas |</v>
+      </c>
+      <c r="R87" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>| GAS~ | Gas | Gas |  |</v>
+      </c>
+      <c r="S87" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>| GAS~ | Gas | Gas |  | |</v>
+      </c>
+      <c r="T87" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| GAS~ | Gas | Gas |  | | |</v>
+      </c>
+      <c r="U87" s="5"/>
+      <c r="V87" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| GAS~ | Gas | Gas |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="88" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B88" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="E88" s="4"/>
+      <c r="F88" s="4"/>
+      <c r="G88" s="4"/>
+      <c r="H88" s="4"/>
+      <c r="I88" s="4"/>
+      <c r="J88" s="4"/>
+      <c r="K88" s="4"/>
+      <c r="L88" s="4"/>
+      <c r="M88" s="4"/>
+      <c r="N88" s="4"/>
+      <c r="O88" s="4"/>
+      <c r="P88" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| GATE | Gate |</v>
+      </c>
+      <c r="Q88" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| GATE | Gate | Portón |</v>
+      </c>
+      <c r="R88" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>| GATE | Gate | Portón |  |</v>
+      </c>
+      <c r="S88" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>| GATE | Gate | Portón |  | |</v>
+      </c>
+      <c r="T88" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| GATE | Gate | Portón |  | | |</v>
+      </c>
+      <c r="U88" s="5"/>
+      <c r="V88" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| GATE | Gate | Portón |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="89" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B89" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4"/>
+      <c r="G89" s="4"/>
+      <c r="H89" s="4"/>
+      <c r="I89" s="4"/>
+      <c r="J89" s="4"/>
+      <c r="K89" s="4"/>
+      <c r="L89" s="4"/>
+      <c r="M89" s="4"/>
+      <c r="N89" s="4"/>
+      <c r="O89" s="4"/>
+      <c r="P89" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| GLAZ | Glazing |</v>
+      </c>
+      <c r="Q89" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| GLAZ | Glazing | Acristalamiento |</v>
+      </c>
+      <c r="R89" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>| GLAZ | Glazing | Acristalamiento |  |</v>
+      </c>
+      <c r="S89" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>| GLAZ | Glazing | Acristalamiento |  | |</v>
+      </c>
+      <c r="T89" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| GLAZ | Glazing | Acristalamiento |  | | |</v>
+      </c>
+      <c r="U89" s="5"/>
+      <c r="V89" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| GLAZ | Glazing | Acristalamiento |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="90" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B90" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="E90" s="4"/>
+      <c r="F90" s="4"/>
+      <c r="G90" s="4"/>
+      <c r="H90" s="4"/>
+      <c r="I90" s="4"/>
+      <c r="J90" s="4"/>
+      <c r="K90" s="4"/>
+      <c r="L90" s="4"/>
+      <c r="M90" s="4"/>
+      <c r="N90" s="4"/>
+      <c r="O90" s="4"/>
+      <c r="P90" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| GLYC | Glycol systems |</v>
+      </c>
+      <c r="Q90" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| GLYC | Glycol systems | Sistemas de glicol |</v>
+      </c>
+      <c r="R90" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>| GLYC | Glycol systems | Sistemas de glicol |  |</v>
+      </c>
+      <c r="S90" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>| GLYC | Glycol systems | Sistemas de glicol |  | |</v>
+      </c>
+      <c r="T90" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| GLYC | Glycol systems | Sistemas de glicol |  | | |</v>
+      </c>
+      <c r="U90" s="5"/>
+      <c r="V90" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| GLYC | Glycol systems | Sistemas de glicol |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="91" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B91" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="E91" s="4"/>
+      <c r="F91" s="4"/>
+      <c r="G91" s="4"/>
+      <c r="H91" s="4"/>
+      <c r="I91" s="4"/>
+      <c r="J91" s="4"/>
+      <c r="K91" s="4"/>
+      <c r="L91" s="4"/>
+      <c r="M91" s="4"/>
+      <c r="N91" s="4"/>
+      <c r="O91" s="4"/>
+      <c r="P91" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| GRID | Grids |</v>
+      </c>
+      <c r="Q91" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| GRID | Grids | Rejillas |</v>
+      </c>
+      <c r="R91" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>| GRID | Grids | Rejillas |  |</v>
+      </c>
+      <c r="S91" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>| GRID | Grids | Rejillas |  | |</v>
+      </c>
+      <c r="T91" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| GRID | Grids | Rejillas |  | | |</v>
+      </c>
+      <c r="U91" s="5"/>
+      <c r="V91" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| GRID | Grids | Rejillas |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="92" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B92" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="E92" s="4"/>
+      <c r="F92" s="4"/>
+      <c r="G92" s="4"/>
+      <c r="H92" s="4"/>
+      <c r="I92" s="4"/>
+      <c r="J92" s="4"/>
+      <c r="K92" s="4"/>
+      <c r="L92" s="4"/>
+      <c r="M92" s="4"/>
+      <c r="N92" s="4"/>
+      <c r="O92" s="4"/>
+      <c r="P92" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| GRLN | Grade line |</v>
+      </c>
+      <c r="Q92" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| GRLN | Grade line | Línea de rasante |</v>
+      </c>
+      <c r="R92" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>| GRLN | Grade line | Línea de rasante |  |</v>
+      </c>
+      <c r="S92" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>| GRLN | Grade line | Línea de rasante |  | |</v>
+      </c>
+      <c r="T92" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| GRLN | Grade line | Línea de rasante |  | | |</v>
+      </c>
+      <c r="U92" s="5"/>
+      <c r="V92" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| GRLN | Grade line | Línea de rasante |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="93" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B93" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="E93" s="4"/>
+      <c r="F93" s="4"/>
+      <c r="G93" s="4"/>
+      <c r="H93" s="4"/>
+      <c r="I93" s="4"/>
+      <c r="J93" s="4"/>
+      <c r="K93" s="4"/>
+      <c r="L93" s="4"/>
+      <c r="M93" s="4"/>
+      <c r="N93" s="4"/>
+      <c r="O93" s="4"/>
+      <c r="P93" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| GRND | Ground system |</v>
+      </c>
+      <c r="Q93" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| GRND | Ground system | Sistema de puesta a tierra |</v>
+      </c>
+      <c r="R93" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>| GRND | Ground system | Sistema de puesta a tierra |  |</v>
+      </c>
+      <c r="S93" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>| GRND | Ground system | Sistema de puesta a tierra |  | |</v>
+      </c>
+      <c r="T93" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| GRND | Ground system | Sistema de puesta a tierra |  | | |</v>
+      </c>
+      <c r="U93" s="5"/>
+      <c r="V93" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| GRND | Ground system | Sistema de puesta a tierra |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="94" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B94" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="E94" s="4"/>
+      <c r="F94" s="4"/>
+      <c r="G94" s="4"/>
+      <c r="H94" s="4"/>
+      <c r="I94" s="4"/>
+      <c r="J94" s="4"/>
+      <c r="K94" s="4"/>
+      <c r="L94" s="4"/>
+      <c r="M94" s="4"/>
+      <c r="N94" s="4"/>
+      <c r="O94" s="4"/>
+      <c r="P94" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| HALN | Halon |</v>
+      </c>
+      <c r="Q94" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| HALN | Halon | Halón |</v>
+      </c>
+      <c r="R94" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>| HALN | Halon | Halón |  |</v>
+      </c>
+      <c r="S94" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>| HALN | Halon | Halón |  | |</v>
+      </c>
+      <c r="T94" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| HALN | Halon | Halón |  | | |</v>
+      </c>
+      <c r="U94" s="5"/>
+      <c r="V94" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| HALN | Halon | Halón |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="95" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B95" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="E95" s="4"/>
+      <c r="F95" s="4"/>
+      <c r="G95" s="4"/>
+      <c r="H95" s="4"/>
+      <c r="I95" s="4"/>
+      <c r="J95" s="4"/>
+      <c r="K95" s="4"/>
+      <c r="L95" s="4"/>
+      <c r="M95" s="4"/>
+      <c r="N95" s="4"/>
+      <c r="O95" s="4"/>
+      <c r="P95" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| HVAC | HVAC systems |</v>
+      </c>
+      <c r="Q95" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| HVAC | HVAC systems | Sistemas de climatización (HVAC) |</v>
+      </c>
+      <c r="R95" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>| HVAC | HVAC systems | Sistemas de climatización (HVAC) |  |</v>
+      </c>
+      <c r="S95" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>| HVAC | HVAC systems | Sistemas de climatización (HVAC) |  | |</v>
+      </c>
+      <c r="T95" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| HVAC | HVAC systems | Sistemas de climatización (HVAC) |  | | |</v>
+      </c>
+      <c r="U95" s="5"/>
+      <c r="V95" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| HVAC | HVAC systems | Sistemas de climatización (HVAC) |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="96" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B96" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4"/>
+      <c r="G96" s="4"/>
+      <c r="H96" s="4"/>
+      <c r="I96" s="4"/>
+      <c r="J96" s="4"/>
+      <c r="K96" s="4"/>
+      <c r="L96" s="4"/>
+      <c r="M96" s="4"/>
+      <c r="N96" s="4"/>
+      <c r="O96" s="4"/>
+      <c r="P96" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| HWTR | Hot water heating system |</v>
+      </c>
+      <c r="Q96" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| HWTR | Hot water heating system | Sistema de calentamiento de agua caliente |</v>
+      </c>
+      <c r="R96" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>| HWTR | Hot water heating system | Sistema de calentamiento de agua caliente |  |</v>
+      </c>
+      <c r="S96" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>| HWTR | Hot water heating system | Sistema de calentamiento de agua caliente |  | |</v>
+      </c>
+      <c r="T96" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| HWTR | Hot water heating system | Sistema de calentamiento de agua caliente |  | | |</v>
+      </c>
+      <c r="U96" s="5"/>
+      <c r="V96" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| HWTR | Hot water heating system | Sistema de calentamiento de agua caliente |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="97" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B97" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="E97" s="4"/>
+      <c r="F97" s="4"/>
+      <c r="G97" s="4"/>
+      <c r="H97" s="4"/>
+      <c r="I97" s="4"/>
+      <c r="J97" s="4"/>
+      <c r="K97" s="4"/>
+      <c r="L97" s="4"/>
+      <c r="M97" s="4"/>
+      <c r="N97" s="4"/>
+      <c r="O97" s="4"/>
+      <c r="P97" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| HYDR | Hydraulic structure |</v>
+      </c>
+      <c r="Q97" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| HYDR | Hydraulic structure | Estructura hidráulica |</v>
+      </c>
+      <c r="R97" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>| HYDR | Hydraulic structure | Estructura hidráulica |  |</v>
+      </c>
+      <c r="S97" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>| HYDR | Hydraulic structure | Estructura hidráulica |  | |</v>
+      </c>
+      <c r="T97" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| HYDR | Hydraulic structure | Estructura hidráulica |  | | |</v>
+      </c>
+      <c r="U97" s="5"/>
+      <c r="V97" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| HYDR | Hydraulic structure | Estructura hidráulica |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="98" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B98" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="E98" s="4"/>
+      <c r="F98" s="4"/>
+      <c r="G98" s="4"/>
+      <c r="H98" s="4"/>
+      <c r="I98" s="4"/>
+      <c r="J98" s="4"/>
+      <c r="K98" s="4"/>
+      <c r="L98" s="4"/>
+      <c r="M98" s="4"/>
+      <c r="N98" s="4"/>
+      <c r="O98" s="4"/>
+      <c r="P98" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| IGAS | Inert gas |</v>
+      </c>
+      <c r="Q98" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| IGAS | Inert gas | Gas inerte |</v>
+      </c>
+      <c r="R98" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>| IGAS | Inert gas | Gas inerte |  |</v>
+      </c>
+      <c r="S98" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>| IGAS | Inert gas | Gas inerte |  | |</v>
+      </c>
+      <c r="T98" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| IGAS | Inert gas | Gas inerte |  | | |</v>
+      </c>
+      <c r="U98" s="5"/>
+      <c r="V98" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| IGAS | Inert gas | Gas inerte |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="99" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B99" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4"/>
+      <c r="G99" s="4"/>
+      <c r="H99" s="4"/>
+      <c r="I99" s="4"/>
+      <c r="J99" s="4"/>
+      <c r="K99" s="4"/>
+      <c r="L99" s="4"/>
+      <c r="M99" s="4"/>
+      <c r="N99" s="4"/>
+      <c r="O99" s="4"/>
+      <c r="P99" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| INGR | Ingrants |</v>
+      </c>
+      <c r="Q99" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| INGR | Ingrants | Concesiones |</v>
+      </c>
+      <c r="R99" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>| INGR | Ingrants | Concesiones |  |</v>
+      </c>
+      <c r="S99" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>| INGR | Ingrants | Concesiones |  | |</v>
+      </c>
+      <c r="T99" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| INGR | Ingrants | Concesiones |  | | |</v>
+      </c>
+      <c r="U99" s="5"/>
+      <c r="V99" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| INGR | Ingrants | Concesiones |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="100" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B100" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="E100" s="4"/>
+      <c r="F100" s="4"/>
+      <c r="G100" s="4"/>
+      <c r="H100" s="4"/>
+      <c r="I100" s="4"/>
+      <c r="J100" s="4"/>
+      <c r="K100" s="4"/>
+      <c r="L100" s="4"/>
+      <c r="M100" s="4"/>
+      <c r="N100" s="4"/>
+      <c r="O100" s="4"/>
+      <c r="P100" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| INST | Instrumentation system |</v>
+      </c>
+      <c r="Q100" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| INST | Instrumentation system | Sistema de instrumentación |</v>
+      </c>
+      <c r="R100" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>| INST | Instrumentation system | Sistema de instrumentación |  |</v>
+      </c>
+      <c r="S100" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>| INST | Instrumentation system | Sistema de instrumentación |  | |</v>
+      </c>
+      <c r="T100" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| INST | Instrumentation system | Sistema de instrumentación |  | | |</v>
+      </c>
+      <c r="U100" s="5"/>
+      <c r="V100" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| INST | Instrumentation system | Sistema de instrumentación |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="101" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B101" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="E101" s="4"/>
+      <c r="F101" s="4"/>
+      <c r="G101" s="4"/>
+      <c r="H101" s="4"/>
+      <c r="I101" s="4"/>
+      <c r="J101" s="4"/>
+      <c r="K101" s="4"/>
+      <c r="L101" s="4"/>
+      <c r="M101" s="4"/>
+      <c r="N101" s="4"/>
+      <c r="O101" s="4"/>
+      <c r="P101" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| INTC | Intercom / PA systems |</v>
+      </c>
+      <c r="Q101" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| INTC | Intercom / PA systems | Intercomunicador/PA Sistemas |</v>
+      </c>
+      <c r="R101" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>| INTC | Intercom / PA systems | Intercomunicador/PA Sistemas |  |</v>
+      </c>
+      <c r="S101" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>| INTC | Intercom / PA systems | Intercomunicador/PA Sistemas |  | |</v>
+      </c>
+      <c r="T101" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| INTC | Intercom / PA systems | Intercomunicador/PA Sistemas |  | | |</v>
+      </c>
+      <c r="U101" s="5"/>
+      <c r="V101" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| INTC | Intercom / PA systems | Intercomunicador/PA Sistemas |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="102" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B102" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="E102" s="4"/>
+      <c r="F102" s="4"/>
+      <c r="G102" s="4"/>
+      <c r="H102" s="4"/>
+      <c r="I102" s="4"/>
+      <c r="J102" s="4"/>
+      <c r="K102" s="4"/>
+      <c r="L102" s="4"/>
+      <c r="M102" s="4"/>
+      <c r="N102" s="4"/>
+      <c r="O102" s="4"/>
+      <c r="P102" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| IRRG | Irrigation |</v>
+      </c>
+      <c r="Q102" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| IRRG | Irrigation | Riego |</v>
+      </c>
+      <c r="R102" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>| IRRG | Irrigation | Riego |  |</v>
+      </c>
+      <c r="S102" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>| IRRG | Irrigation | Riego |  | |</v>
+      </c>
+      <c r="T102" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| IRRG | Irrigation | Riego |  | | |</v>
+      </c>
+      <c r="U102" s="5"/>
+      <c r="V102" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| IRRG | Irrigation | Riego |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="103" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B103" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="E103" s="4"/>
+      <c r="F103" s="4"/>
+      <c r="G103" s="4"/>
+      <c r="H103" s="4"/>
+      <c r="I103" s="4"/>
+      <c r="J103" s="4"/>
+      <c r="K103" s="4"/>
+      <c r="L103" s="4"/>
+      <c r="M103" s="4"/>
+      <c r="N103" s="4"/>
+      <c r="O103" s="4"/>
+      <c r="P103" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>| JNTS | Joints |</v>
+      </c>
+      <c r="Q103" s="5" t="str">
+        <f t="shared" si="8"/>
+        <v>| JNTS | Joints | Juntas |</v>
+      </c>
+      <c r="R103" s="5" t="str">
+        <f t="shared" si="11"/>
+        <v>| JNTS | Joints | Juntas |  |</v>
+      </c>
+      <c r="S103" s="5" t="str">
+        <f t="shared" si="12"/>
+        <v>| JNTS | Joints | Juntas |  | |</v>
+      </c>
+      <c r="T103" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| JNTS | Joints | Juntas |  | | |</v>
+      </c>
+      <c r="U103" s="5"/>
+      <c r="V103" s="5" t="str">
+        <f t="shared" si="9"/>
+        <v>| JNTS | Joints | Juntas |  | | | | | | | | | |</v>
+      </c>
+    </row>
+    <row r="104" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B104" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="105" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B105" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="106" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B106" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="107" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B107" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="108" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B108" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="109" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B109" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="110" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B110" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="111" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B111" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="112" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+      <c r="B112" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="113" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B113" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="114" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B114" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="115" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B115" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B116" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="117" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B117" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B118" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="119" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B119" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="120" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B120" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="121" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B121" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="122" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B122" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="123" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B123" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="124" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B124" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="125" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B125" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="126" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B126" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="127" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B127" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="128" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B128" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="129" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B129" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="130" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B130" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B131" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="132" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B132" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="133" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B133" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="134" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B134" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="135" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B135" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="136" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B136" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="137" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B137" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="138" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B138" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="139" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B139" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="140" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B140" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="141" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B141" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="142" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B142" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="143" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B143" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="144" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B144" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B145" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="146" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B146" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B147" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B148" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B149" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="150" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B150" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B151" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B152" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B153" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B154" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B155" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B156" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B157" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="158" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B158" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B159" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B160" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="161" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B161" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="162" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B162" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="163" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B163" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="164" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B164" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="165" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B165" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="166" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B166" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="167" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B167" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="168" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B168" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="169" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B169" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="170" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B170" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="171" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B171" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="172" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B172" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="173" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B173" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="174" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B174" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="175" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B175" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="176" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B176" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="177" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B177" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="178" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B178" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="179" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B179" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="180" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B180" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="181" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B181" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="182" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B182" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="183" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B183" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="184" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B184" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="185" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B185" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="186" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B186" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="187" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B187" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="188" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B188" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="189" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B189" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="190" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B190" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="191" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B191" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="192" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B192" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="193" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B193" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="194" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B194" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>765</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{435D73F0-A81A-4218-A9EB-3B3DC641466C}">
   <dimension ref="B1:V103"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.4" x14ac:dyDescent="0.55000000000000004"/>
@@ -13349,7 +20792,7 @@
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="4" t="s">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>127</v>
@@ -13378,31 +20821,31 @@
       <c r="O3" s="4"/>
       <c r="P3" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B3," | ",C3," |")</f>
-        <v>| Designador | Descripción (en) |</v>
+        <v>| Estado | Descripción (en) |</v>
       </c>
       <c r="Q3" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," |")</f>
-        <v>| Designador | Descripción (en) | Descripción (es) |</v>
+        <v>| Estado | Descripción (en) | Descripción (es) |</v>
       </c>
       <c r="R3" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," |")</f>
-        <v>| Designador | Descripción (en) | Descripción (es) | A |</v>
+        <v>| Estado | Descripción (en) | Descripción (es) | A |</v>
       </c>
       <c r="S3" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," |",F3," |")</f>
-        <v>| Designador | Descripción (en) | Descripción (es) | A |B |</v>
+        <v>| Estado | Descripción (en) | Descripción (es) | A |B |</v>
       </c>
       <c r="T3" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," |",F3," |",G3," |")</f>
-        <v>| Designador | Descripción (en) | Descripción (es) | A |B |C |</v>
+        <v>| Estado | Descripción (en) | Descripción (es) | A |B |C |</v>
       </c>
       <c r="U3" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," | ",F3," | ",G3," | ",H3," |")</f>
-        <v>| Designador | Descripción (en) | Descripción (es) | A | B | C | D |</v>
+        <v>| Estado | Descripción (en) | Descripción (es) | A | B | C | D |</v>
       </c>
       <c r="V3" s="5" t="str">
         <f t="shared" ref="V3:V14" si="0">_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," |",F3," |",G3," |",H3," |",I3," |",J3," |",K3," |",L3," |",M3," |",N3," |")</f>
-        <v>| Designador | Descripción (en) | Descripción (es) | A |B |C |D | | | | | | |</v>
+        <v>| Estado | Descripción (en) | Descripción (es) | A |B |C |D | | | | | | |</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.55000000000000004">
@@ -13529,7 +20972,7 @@
         <v>| A | Abandoned | Abandonado | ✓ |✓ | | | | | | | | |</v>
       </c>
     </row>
-    <row r="6" spans="2:22" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="2:22" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="5" t="s">
         <v>14</v>
       </c>
@@ -13583,7 +21026,7 @@
         <v>| D | Existing to demolish | Existente para demoler | ✓ |✕ | | | | | | | | |</v>
       </c>
     </row>
-    <row r="7" spans="2:22" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="2:22" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="5" t="s">
         <v>54</v>
       </c>

--- a/file/temp/ExcelTableToMarkDownSample.xlsx
+++ b/file/temp/ExcelTableToMarkDownSample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\D_SSD2TB\R.DAPC\file\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8204DCFC-3FA7-4729-BA42-346F1217FD5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9846886-9F23-4908-903C-71AF614000DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="3" xr2:uid="{D94F812B-BC61-4A22-9692-634766FE0D40}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="991" uniqueCount="766">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="991" uniqueCount="767">
   <si>
     <t>Creación de tablas en formato .md</t>
   </si>
@@ -2344,6 +2344,9 @@
   </si>
   <si>
     <t>Vía fluvial</t>
+  </si>
+  <si>
+    <t>Grupo mayor</t>
   </si>
 </sst>
 </file>
@@ -15226,7 +15229,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B53ECC1-3B1D-4C8A-92C3-A53ACBB569A1}">
-  <dimension ref="B1:V194"/>
+  <dimension ref="B1:V215"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="2.7109375" style="1" customWidth="1"/>
@@ -15324,7 +15327,7 @@
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="4" t="s">
-        <v>119</v>
+        <v>766</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>127</v>
@@ -15353,31 +15356,31 @@
       <c r="O3" s="4"/>
       <c r="P3" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B3," | ",C3," |")</f>
-        <v>| Designador | Descripción (en) |</v>
+        <v>| Grupo mayor | Descripción (en) |</v>
       </c>
       <c r="Q3" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," |")</f>
-        <v>| Designador | Descripción (en) | Descripción (es) |</v>
+        <v>| Grupo mayor | Descripción (en) | Descripción (es) |</v>
       </c>
       <c r="R3" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," |")</f>
-        <v>| Designador | Descripción (en) | Descripción (es) | A |</v>
+        <v>| Grupo mayor | Descripción (en) | Descripción (es) | A |</v>
       </c>
       <c r="S3" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," |",F3," |")</f>
-        <v>| Designador | Descripción (en) | Descripción (es) | A |B |</v>
+        <v>| Grupo mayor | Descripción (en) | Descripción (es) | A |B |</v>
       </c>
       <c r="T3" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," |",F3," |",G3," |")</f>
-        <v>| Designador | Descripción (en) | Descripción (es) | A |B |C |</v>
+        <v>| Grupo mayor | Descripción (en) | Descripción (es) | A |B |C |</v>
       </c>
       <c r="U3" s="5" t="str">
         <f>_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," | ",F3," | ",G3," | ",H3," |")</f>
-        <v>| Designador | Descripción (en) | Descripción (es) | A | B | C | D |</v>
+        <v>| Grupo mayor | Descripción (en) | Descripción (es) | A | B | C | D |</v>
       </c>
       <c r="V3" s="5" t="str">
         <f t="shared" ref="V3:V14" si="0">_xlfn.CONCAT("| ",B3," | ",C3," | ",D3," | ",E3," |",F3," |",G3," |",H3," |",I3," |",J3," |",K3," |",L3," |",M3," |",N3," |")</f>
-        <v>| Designador | Descripción (en) | Descripción (es) | A |B |C |D | | | | | | |</v>
+        <v>| Grupo mayor | Descripción (en) | Descripción (es) | A |B |C |D | | | | | | |</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.55000000000000004">
@@ -15480,7 +15483,7 @@
         <v>| ACCS | Access |</v>
       </c>
       <c r="Q5" s="5" t="str">
-        <f t="shared" ref="Q5:Q38" si="3">_xlfn.CONCAT("| ",B5," | ",C5," | ",D5," |")</f>
+        <f t="shared" ref="Q5:Q68" si="3">_xlfn.CONCAT("| ",B5," | ",C5," | ",D5," |")</f>
         <v>| ACCS | Access | Acceso |</v>
       </c>
       <c r="R5" s="5" t="str">
@@ -15558,7 +15561,7 @@
         <v>| ACID | Acid waste systems | Sistemas de residuos ácidos | ✓ |✕ | | | | | | | | |</v>
       </c>
     </row>
-    <row r="7" spans="2:22" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="2:22" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="5" t="s">
         <v>207</v>
       </c>
@@ -16759,7 +16762,10 @@
       <c r="N39" s="5"/>
       <c r="O39" s="4"/>
       <c r="P39" s="5"/>
-      <c r="Q39" s="5"/>
+      <c r="Q39" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| CLOK | Clock system | Sistema de relojería |</v>
+      </c>
       <c r="R39" s="5"/>
       <c r="S39" s="5"/>
       <c r="T39" s="5"/>
@@ -16788,7 +16794,10 @@
       <c r="N40" s="5"/>
       <c r="O40" s="4"/>
       <c r="P40" s="5"/>
-      <c r="Q40" s="5"/>
+      <c r="Q40" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| CMPA | Compressed / processed air systems | Sistemas de aire comprimido/procesado |</v>
+      </c>
       <c r="R40" s="5"/>
       <c r="S40" s="5"/>
       <c r="T40" s="5"/>
@@ -16817,7 +16826,10 @@
       <c r="N41" s="5"/>
       <c r="O41" s="4"/>
       <c r="P41" s="5"/>
-      <c r="Q41" s="5"/>
+      <c r="Q41" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| CMPR | Computer | Ordenador |</v>
+      </c>
       <c r="R41" s="5"/>
       <c r="S41" s="5"/>
       <c r="T41" s="5"/>
@@ -16846,7 +16858,10 @@
       <c r="N42" s="4"/>
       <c r="O42" s="4"/>
       <c r="P42" s="5"/>
-      <c r="Q42" s="5"/>
+      <c r="Q42" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| CNDW | Condenser water systems | Sistemas de agua del condensador |</v>
+      </c>
       <c r="R42" s="5"/>
       <c r="S42" s="5"/>
       <c r="T42" s="5"/>
@@ -16875,7 +16890,10 @@
       <c r="N43" s="4"/>
       <c r="O43" s="4"/>
       <c r="P43" s="5"/>
-      <c r="Q43" s="5"/>
+      <c r="Q43" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| CO2S | CO2 system | Sistema de CO2 |</v>
+      </c>
       <c r="R43" s="5"/>
       <c r="S43" s="5"/>
       <c r="T43" s="5"/>
@@ -16904,7 +16922,10 @@
       <c r="N44" s="4"/>
       <c r="O44" s="4"/>
       <c r="P44" s="5"/>
-      <c r="Q44" s="5"/>
+      <c r="Q44" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| CODE | Code compliance plan | Plan de cumplimiento normativo |</v>
+      </c>
       <c r="R44" s="5"/>
       <c r="S44" s="5"/>
       <c r="T44" s="5"/>
@@ -16937,7 +16958,7 @@
         <v>| COLS | Columns |</v>
       </c>
       <c r="Q45" s="5" t="str">
-        <f t="shared" ref="Q45:Q103" si="8">_xlfn.CONCAT("| ",B45," | ",C45," | ",D45," |")</f>
+        <f t="shared" si="3"/>
         <v>| COLS | Columns | Columnas |</v>
       </c>
       <c r="R45" s="5" t="str">
@@ -16954,7 +16975,7 @@
       </c>
       <c r="U45" s="5"/>
       <c r="V45" s="5" t="str">
-        <f t="shared" ref="V45:V103" si="9">_xlfn.CONCAT("| ",B45," | ",C45," | ",D45," | ",E45," |",F45," |",G45," |",H45," |",I45," |",J45," |",K45," |",L45," |",M45," |",N45," |")</f>
+        <f t="shared" ref="V45:V103" si="8">_xlfn.CONCAT("| ",B45," | ",C45," | ",D45," | ",E45," |",F45," |",G45," |",H45," |",I45," |",J45," |",K45," |",L45," |",M45," |",N45," |")</f>
         <v>| COLS | Columns | Columnas |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -16984,7 +17005,7 @@
         <v>| COMM | Communications |</v>
       </c>
       <c r="Q46" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>| COMM | Communications | Comunicaciones |</v>
       </c>
       <c r="R46" s="5" t="str">
@@ -17001,7 +17022,7 @@
       </c>
       <c r="U46" s="5"/>
       <c r="V46" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| COMM | Communications | Comunicaciones |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17031,7 +17052,7 @@
         <v>| CONT | Controls and instrumentation |</v>
       </c>
       <c r="Q47" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>| CONT | Controls and instrumentation | Controles e instrumentación |</v>
       </c>
       <c r="R47" s="5" t="str">
@@ -17048,7 +17069,7 @@
       </c>
       <c r="U47" s="5"/>
       <c r="V47" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| CONT | Controls and instrumentation | Controles e instrumentación |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17078,7 +17099,7 @@
         <v>| CONV | Conveying systems |</v>
       </c>
       <c r="Q48" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>| CONV | Conveying systems | Sistemas de transporte |</v>
       </c>
       <c r="R48" s="5" t="str">
@@ -17095,7 +17116,7 @@
       </c>
       <c r="U48" s="5"/>
       <c r="V48" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| CONV | Conveying systems | Sistemas de transporte |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17125,7 +17146,7 @@
         <v>| CRPT | Carpet / carpet tiles |</v>
       </c>
       <c r="Q49" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>| CRPT | Carpet / carpet tiles | Alfombra/losetas de moqueta |</v>
       </c>
       <c r="R49" s="5" t="str">
@@ -17142,7 +17163,7 @@
       </c>
       <c r="U49" s="5"/>
       <c r="V49" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| CRPT | Carpet / carpet tiles | Alfombra/losetas de moqueta |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17172,7 +17193,7 @@
         <v>| CSWK | Casework |</v>
       </c>
       <c r="Q50" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>| CSWK | Casework | Carpintería |</v>
       </c>
       <c r="R50" s="5" t="str">
@@ -17189,7 +17210,7 @@
       </c>
       <c r="U50" s="5"/>
       <c r="V50" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| CSWK | Casework | Carpintería |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17219,7 +17240,7 @@
         <v>| CTRL | Control points |</v>
       </c>
       <c r="Q51" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>| CTRL | Control points | Puntos de control |</v>
       </c>
       <c r="R51" s="5" t="str">
@@ -17236,7 +17257,7 @@
       </c>
       <c r="U51" s="5"/>
       <c r="V51" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| CTRL | Control points | Puntos de control |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17266,7 +17287,7 @@
         <v>| CWTR | Chilled water systems |</v>
       </c>
       <c r="Q52" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>| CWTR | Chilled water systems | Sistemas de agua refrigerada |</v>
       </c>
       <c r="R52" s="5" t="str">
@@ -17283,7 +17304,7 @@
       </c>
       <c r="U52" s="5"/>
       <c r="V52" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| CWTR | Chilled water systems | Sistemas de agua refrigerada |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17313,7 +17334,7 @@
         <v>| DATA | Data / LAN system |</v>
       </c>
       <c r="Q53" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>| DATA | Data / LAN system | Datos/LAN Sistema |</v>
       </c>
       <c r="R53" s="5" t="str">
@@ -17330,7 +17351,7 @@
       </c>
       <c r="U53" s="5"/>
       <c r="V53" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| DATA | Data / LAN system | Datos/LAN Sistema |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17360,7 +17381,7 @@
         <v>| DECK | Deck |</v>
       </c>
       <c r="Q54" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>| DECK | Deck | Cubierta |</v>
       </c>
       <c r="R54" s="5" t="str">
@@ -17377,7 +17398,7 @@
       </c>
       <c r="U54" s="5"/>
       <c r="V54" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| DECK | Deck | Cubierta |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17407,7 +17428,7 @@
         <v>| DETL | Detail |</v>
       </c>
       <c r="Q55" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>| DETL | Detail | Detalle |</v>
       </c>
       <c r="R55" s="5" t="str">
@@ -17424,7 +17445,7 @@
       </c>
       <c r="U55" s="5"/>
       <c r="V55" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| DETL | Detail | Detalle |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17454,7 +17475,7 @@
         <v>| DFLD | Drain fields |</v>
       </c>
       <c r="Q56" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>| DFLD | Drain fields | Campos de drenaje |</v>
       </c>
       <c r="R56" s="5" t="str">
@@ -17471,7 +17492,7 @@
       </c>
       <c r="U56" s="5"/>
       <c r="V56" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| DFLD | Drain fields | Campos de drenaje |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17501,7 +17522,7 @@
         <v>| DIAG | Diagrams |</v>
       </c>
       <c r="Q57" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>| DIAG | Diagrams | Diagramas |</v>
       </c>
       <c r="R57" s="5" t="str">
@@ -17518,7 +17539,7 @@
       </c>
       <c r="U57" s="5"/>
       <c r="V57" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| DIAG | Diagrams | Diagramas |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17548,7 +17569,7 @@
         <v>| DICT | Dictation system |</v>
       </c>
       <c r="Q58" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>| DICT | Dictation system | Sistema de dictado |</v>
       </c>
       <c r="R58" s="5" t="str">
@@ -17565,7 +17586,7 @@
       </c>
       <c r="U58" s="5"/>
       <c r="V58" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| DICT | Dictation system | Sistema de dictado |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17595,7 +17616,7 @@
         <v>| DOMW | Domestic water systems |</v>
       </c>
       <c r="Q59" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>| DOMW | Domestic water systems | Sistemas de agua potable |</v>
       </c>
       <c r="R59" s="5" t="str">
@@ -17612,7 +17633,7 @@
       </c>
       <c r="U59" s="5"/>
       <c r="V59" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| DOMW | Domestic water systems | Sistemas de agua potable |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17642,7 +17663,7 @@
         <v>| DOOR | Doors |</v>
       </c>
       <c r="Q60" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>| DOOR | Doors | Puertas |</v>
       </c>
       <c r="R60" s="5" t="str">
@@ -17659,7 +17680,7 @@
       </c>
       <c r="U60" s="5"/>
       <c r="V60" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| DOOR | Doors | Puertas |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17689,7 +17710,7 @@
         <v>| DRAN | Drains |</v>
       </c>
       <c r="Q61" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>| DRAN | Drains | Desagües |</v>
       </c>
       <c r="R61" s="5" t="str">
@@ -17706,7 +17727,7 @@
       </c>
       <c r="U61" s="5"/>
       <c r="V61" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| DRAN | Drains | Desagües |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17736,7 +17757,7 @@
         <v>| DRIV | Driveways |</v>
       </c>
       <c r="Q62" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>| DRIV | Driveways | Entradas de vehículos |</v>
       </c>
       <c r="R62" s="5" t="str">
@@ -17753,7 +17774,7 @@
       </c>
       <c r="U62" s="5"/>
       <c r="V62" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| DRIV | Driveways | Entradas de vehículos |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17783,7 +17804,7 @@
         <v>| DTCH | Ditches or washes |</v>
       </c>
       <c r="Q63" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>| DTCH | Ditches or washes | Cunetas o lavaderos |</v>
       </c>
       <c r="R63" s="5" t="str">
@@ -17800,7 +17821,7 @@
       </c>
       <c r="U63" s="5"/>
       <c r="V63" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| DTCH | Ditches or washes | Cunetas o lavaderos |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17830,7 +17851,7 @@
         <v>| DUAL | Dual temperature systems |</v>
       </c>
       <c r="Q64" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>| DUAL | Dual temperature systems | Sistemas de doble temperatura |</v>
       </c>
       <c r="R64" s="5" t="str">
@@ -17847,11 +17868,11 @@
       </c>
       <c r="U64" s="5"/>
       <c r="V64" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| DUAL | Dual temperature systems | Sistemas de doble temperatura |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="2:22" ht="30.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B65" s="4" t="s">
         <v>381</v>
       </c>
@@ -17877,7 +17898,7 @@
         <v>| DUST | Dust and fume collection systems |</v>
       </c>
       <c r="Q65" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>| DUST | Dust and fume collection systems | Sistemas de recolección de polvo y humos |</v>
       </c>
       <c r="R65" s="5" t="str">
@@ -17894,11 +17915,11 @@
       </c>
       <c r="U65" s="5"/>
       <c r="V65" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| DUST | Dust and fume collection systems | Sistemas de recolección de polvo y humos |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="2:22" ht="30.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B66" s="4" t="s">
         <v>384</v>
       </c>
@@ -17924,7 +17945,7 @@
         <v>| ELEC | Electrical system, telecom plan |</v>
       </c>
       <c r="Q66" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>| ELEC | Electrical system, telecom plan | Sistema eléctrico, plano de telecomunicaciones |</v>
       </c>
       <c r="R66" s="5" t="str">
@@ -17941,7 +17962,7 @@
       </c>
       <c r="U66" s="5"/>
       <c r="V66" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| ELEC | Electrical system, telecom plan | Sistema eléctrico, plano de telecomunicaciones |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17971,7 +17992,7 @@
         <v>| ELEV | Elevation |</v>
       </c>
       <c r="Q67" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>| ELEV | Elevation | Elevación |</v>
       </c>
       <c r="R67" s="5" t="str">
@@ -17988,7 +18009,7 @@
       </c>
       <c r="U67" s="5"/>
       <c r="V67" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| ELEV | Elevation | Elevación |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -18018,7 +18039,7 @@
         <v>| ELHT | Electric heat |</v>
       </c>
       <c r="Q68" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>| ELHT | Electric heat | Calefacción eléctrica |</v>
       </c>
       <c r="R68" s="5" t="str">
@@ -18030,16 +18051,16 @@
         <v>| ELHT | Electric heat | Calefacción eléctrica |  | |</v>
       </c>
       <c r="T68" s="5" t="str">
-        <f t="shared" ref="T68:T103" si="10">_xlfn.CONCAT("| ",B68," | ",C68," | ",D68," | ",E68," |",F68," |",G68," |")</f>
+        <f t="shared" ref="T68:T103" si="9">_xlfn.CONCAT("| ",B68," | ",C68," | ",D68," | ",E68," |",F68," |",G68," |")</f>
         <v>| ELHT | Electric heat | Calefacción eléctrica |  | | |</v>
       </c>
       <c r="U68" s="5"/>
       <c r="V68" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| ELHT | Electric heat | Calefacción eléctrica |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="2:22" ht="30.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B69" s="4" t="s">
         <v>393</v>
       </c>
@@ -18065,7 +18086,7 @@
         <v>| EMCS | Energy monitoring control system |</v>
       </c>
       <c r="Q69" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="Q69:Q132" si="10">_xlfn.CONCAT("| ",B69," | ",C69," | ",D69," |")</f>
         <v>| EMCS | Energy monitoring control system | Sistema de control de monitoreo de energía |</v>
       </c>
       <c r="R69" s="5" t="str">
@@ -18077,12 +18098,12 @@
         <v>| EMCS | Energy monitoring control system | Sistema de control de monitoreo de energía |  | |</v>
       </c>
       <c r="T69" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>| EMCS | Energy monitoring control system | Sistema de control de monitoreo de energía |  | | |</v>
       </c>
       <c r="U69" s="5"/>
       <c r="V69" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| EMCS | Energy monitoring control system | Sistema de control de monitoreo de energía |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -18112,7 +18133,7 @@
         <v>| ENER | Energy management systems |</v>
       </c>
       <c r="Q70" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>| ENER | Energy management systems | Sistemas de gestión de energía |</v>
       </c>
       <c r="R70" s="5" t="str">
@@ -18124,12 +18145,12 @@
         <v>| ENER | Energy management systems | Sistemas de gestión de energía |  | |</v>
       </c>
       <c r="T70" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>| ENER | Energy management systems | Sistemas de gestión de energía |  | | |</v>
       </c>
       <c r="U70" s="5"/>
       <c r="V70" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| ENER | Energy management systems | Sistemas de gestión de energía |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -18159,7 +18180,7 @@
         <v>| EQPM | Equipment |</v>
       </c>
       <c r="Q71" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>| EQPM | Equipment | Equipo |</v>
       </c>
       <c r="R71" s="5" t="str">
@@ -18171,12 +18192,12 @@
         <v>| EQPM | Equipment | Equipo |  | |</v>
       </c>
       <c r="T71" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>| EQPM | Equipment | Equipo |  | | |</v>
       </c>
       <c r="U71" s="5"/>
       <c r="V71" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| EQPM | Equipment | Equipo |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -18206,7 +18227,7 @@
         <v>| EROS | Erosion and sediment control |</v>
       </c>
       <c r="Q72" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>| EROS | Erosion and sediment control | Control de erosión y sedimentos |</v>
       </c>
       <c r="R72" s="5" t="str">
@@ -18218,12 +18239,12 @@
         <v>| EROS | Erosion and sediment control | Control de erosión y sedimentos |  | |</v>
       </c>
       <c r="T72" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>| EROS | Erosion and sediment control | Control de erosión y sedimentos |  | | |</v>
       </c>
       <c r="U72" s="5"/>
       <c r="V72" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| EROS | Erosion and sediment control | Control de erosión y sedimentos |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -18253,7 +18274,7 @@
         <v>| ESMT | Easements |</v>
       </c>
       <c r="Q73" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>| ESMT | Easements | Servidumbres |</v>
       </c>
       <c r="R73" s="5" t="str">
@@ -18265,12 +18286,12 @@
         <v>| ESMT | Easements | Servidumbres |  | |</v>
       </c>
       <c r="T73" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>| ESMT | Easements | Servidumbres |  | | |</v>
       </c>
       <c r="U73" s="5"/>
       <c r="V73" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| ESMT | Easements | Servidumbres |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -18300,7 +18321,7 @@
         <v>| EVAC | Evacuation plan |</v>
       </c>
       <c r="Q74" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>| EVAC | Evacuation plan | Plan de evacuación |</v>
       </c>
       <c r="R74" s="5" t="str">
@@ -18312,12 +18333,12 @@
         <v>| EVAC | Evacuation plan | Plan de evacuación |  | |</v>
       </c>
       <c r="T74" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>| EVAC | Evacuation plan | Plan de evacuación |  | | |</v>
       </c>
       <c r="U74" s="5"/>
       <c r="V74" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| EVAC | Evacuation plan | Plan de evacuación |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -18347,7 +18368,7 @@
         <v>| EXHS | Exhaust system |</v>
       </c>
       <c r="Q75" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>| EXHS | Exhaust system | Sistema de extracción |</v>
       </c>
       <c r="R75" s="5" t="str">
@@ -18359,12 +18380,12 @@
         <v>| EXHS | Exhaust system | Sistema de extracción |  | |</v>
       </c>
       <c r="T75" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>| EXHS | Exhaust system | Sistema de extracción |  | | |</v>
       </c>
       <c r="U75" s="5"/>
       <c r="V75" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| EXHS | Exhaust system | Sistema de extracción |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -18394,7 +18415,7 @@
         <v>| FENC | Fences |</v>
       </c>
       <c r="Q76" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>| FENC | Fences | Cercas |</v>
       </c>
       <c r="R76" s="5" t="str">
@@ -18406,12 +18427,12 @@
         <v>| FENC | Fences | Cercas |  | |</v>
       </c>
       <c r="T76" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>| FENC | Fences | Cercas |  | | |</v>
       </c>
       <c r="U76" s="5"/>
       <c r="V76" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| FENC | Fences | Cercas |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -18441,7 +18462,7 @@
         <v>| FIRE | Fire protection |</v>
       </c>
       <c r="Q77" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>| FIRE | Fire protection | Protección contra incendios |</v>
       </c>
       <c r="R77" s="5" t="str">
@@ -18453,12 +18474,12 @@
         <v>| FIRE | Fire protection | Protección contra incendios |  | |</v>
       </c>
       <c r="T77" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>| FIRE | Fire protection | Protección contra incendios |  | | |</v>
       </c>
       <c r="U77" s="5"/>
       <c r="V77" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| FIRE | Fire protection | Protección contra incendios |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -18488,7 +18509,7 @@
         <v>| FLHA | Flood hazard area |</v>
       </c>
       <c r="Q78" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>| FLHA | Flood hazard area | Zona con riesgo de inundación |</v>
       </c>
       <c r="R78" s="5" t="str">
@@ -18500,12 +18521,12 @@
         <v>| FLHA | Flood hazard area | Zona con riesgo de inundación |  | |</v>
       </c>
       <c r="T78" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>| FLHA | Flood hazard area | Zona con riesgo de inundación |  | | |</v>
       </c>
       <c r="U78" s="5"/>
       <c r="V78" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| FLHA | Flood hazard area | Zona con riesgo de inundación |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -18535,7 +18556,7 @@
         <v>| FLOR | Floor |</v>
       </c>
       <c r="Q79" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>| FLOR | Floor | Piso |</v>
       </c>
       <c r="R79" s="5" t="str">
@@ -18547,12 +18568,12 @@
         <v>| FLOR | Floor | Piso |  | |</v>
       </c>
       <c r="T79" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>| FLOR | Floor | Piso |  | | |</v>
       </c>
       <c r="U79" s="5"/>
       <c r="V79" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| FLOR | Floor | Piso |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -18582,7 +18603,7 @@
         <v>| FNDN | Foundation |</v>
       </c>
       <c r="Q80" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>| FNDN | Foundation | Cimentación |</v>
       </c>
       <c r="R80" s="5" t="str">
@@ -18594,12 +18615,12 @@
         <v>| FNDN | Foundation | Cimentación |  | |</v>
       </c>
       <c r="T80" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>| FNDN | Foundation | Cimentación |  | | |</v>
       </c>
       <c r="U80" s="5"/>
       <c r="V80" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| FNDN | Foundation | Cimentación |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -18629,7 +18650,7 @@
         <v>| FNSH | Finishes |</v>
       </c>
       <c r="Q81" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>| FNSH | Finishes | Acabados |</v>
       </c>
       <c r="R81" s="5" t="str">
@@ -18641,16 +18662,16 @@
         <v>| FNSH | Finishes | Acabados |  | |</v>
       </c>
       <c r="T81" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>| FNSH | Finishes | Acabados |  | | |</v>
       </c>
       <c r="U81" s="5"/>
       <c r="V81" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| FNSH | Finishes | Acabados |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="82" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="2:22" ht="30.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B82" s="4" t="s">
         <v>430</v>
       </c>
@@ -18676,7 +18697,7 @@
         <v>| FRAM | Braced frame or moment frame |</v>
       </c>
       <c r="Q82" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>| FRAM | Braced frame or moment frame | Marco arriostrado o marco de momento |</v>
       </c>
       <c r="R82" s="5" t="str">
@@ -18688,12 +18709,12 @@
         <v>| FRAM | Braced frame or moment frame | Marco arriostrado o marco de momento |  | |</v>
       </c>
       <c r="T82" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>| FRAM | Braced frame or moment frame | Marco arriostrado o marco de momento |  | | |</v>
       </c>
       <c r="U82" s="5"/>
       <c r="V82" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| FRAM | Braced frame or moment frame | Marco arriostrado o marco de momento |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -18723,7 +18744,7 @@
         <v>| FSTN | Fasteners and connections |</v>
       </c>
       <c r="Q83" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>| FSTN | Fasteners and connections | Sujeciones y conexiones |</v>
       </c>
       <c r="R83" s="5" t="str">
@@ -18735,12 +18756,12 @@
         <v>| FSTN | Fasteners and connections | Sujeciones y conexiones |  | |</v>
       </c>
       <c r="T83" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>| FSTN | Fasteners and connections | Sujeciones y conexiones |  | | |</v>
       </c>
       <c r="U83" s="5"/>
       <c r="V83" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| FSTN | Fasteners and connections | Sujeciones y conexiones |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -18770,7 +18791,7 @@
         <v>| FUEL | Fuel systems |</v>
       </c>
       <c r="Q84" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>| FUEL | Fuel systems | Sistemas de combustible |</v>
       </c>
       <c r="R84" s="5" t="str">
@@ -18782,12 +18803,12 @@
         <v>| FUEL | Fuel systems | Sistemas de combustible |  | |</v>
       </c>
       <c r="T84" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>| FUEL | Fuel systems | Sistemas de combustible |  | | |</v>
       </c>
       <c r="U84" s="5"/>
       <c r="V84" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| FUEL | Fuel systems | Sistemas de combustible |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -18817,7 +18838,7 @@
         <v>| FUME | Fume hood |</v>
       </c>
       <c r="Q85" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>| FUME | Fume hood | Campana de extracción de gases |</v>
       </c>
       <c r="R85" s="5" t="str">
@@ -18829,12 +18850,12 @@
         <v>| FUME | Fume hood | Campana de extracción de gases |  | |</v>
       </c>
       <c r="T85" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>| FUME | Fume hood | Campana de extracción de gases |  | | |</v>
       </c>
       <c r="U85" s="5"/>
       <c r="V85" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| FUME | Fume hood | Campana de extracción de gases |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -18864,7 +18885,7 @@
         <v>| FURN | Furnishings |</v>
       </c>
       <c r="Q86" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>| FURN | Furnishings | Mobiliario |</v>
       </c>
       <c r="R86" s="5" t="str">
@@ -18876,12 +18897,12 @@
         <v>| FURN | Furnishings | Mobiliario |  | |</v>
       </c>
       <c r="T86" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>| FURN | Furnishings | Mobiliario |  | | |</v>
       </c>
       <c r="U86" s="5"/>
       <c r="V86" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| FURN | Furnishings | Mobiliario |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -18911,7 +18932,7 @@
         <v>| GAS~ | Gas |</v>
       </c>
       <c r="Q87" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>| GAS~ | Gas | Gas |</v>
       </c>
       <c r="R87" s="5" t="str">
@@ -18923,12 +18944,12 @@
         <v>| GAS~ | Gas | Gas |  | |</v>
       </c>
       <c r="T87" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>| GAS~ | Gas | Gas |  | | |</v>
       </c>
       <c r="U87" s="5"/>
       <c r="V87" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| GAS~ | Gas | Gas |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -18958,7 +18979,7 @@
         <v>| GATE | Gate |</v>
       </c>
       <c r="Q88" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>| GATE | Gate | Portón |</v>
       </c>
       <c r="R88" s="5" t="str">
@@ -18970,12 +18991,12 @@
         <v>| GATE | Gate | Portón |  | |</v>
       </c>
       <c r="T88" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>| GATE | Gate | Portón |  | | |</v>
       </c>
       <c r="U88" s="5"/>
       <c r="V88" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| GATE | Gate | Portón |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -19005,7 +19026,7 @@
         <v>| GLAZ | Glazing |</v>
       </c>
       <c r="Q89" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>| GLAZ | Glazing | Acristalamiento |</v>
       </c>
       <c r="R89" s="5" t="str">
@@ -19017,12 +19038,12 @@
         <v>| GLAZ | Glazing | Acristalamiento |  | |</v>
       </c>
       <c r="T89" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>| GLAZ | Glazing | Acristalamiento |  | | |</v>
       </c>
       <c r="U89" s="5"/>
       <c r="V89" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| GLAZ | Glazing | Acristalamiento |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -19052,7 +19073,7 @@
         <v>| GLYC | Glycol systems |</v>
       </c>
       <c r="Q90" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>| GLYC | Glycol systems | Sistemas de glicol |</v>
       </c>
       <c r="R90" s="5" t="str">
@@ -19064,12 +19085,12 @@
         <v>| GLYC | Glycol systems | Sistemas de glicol |  | |</v>
       </c>
       <c r="T90" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>| GLYC | Glycol systems | Sistemas de glicol |  | | |</v>
       </c>
       <c r="U90" s="5"/>
       <c r="V90" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| GLYC | Glycol systems | Sistemas de glicol |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -19099,7 +19120,7 @@
         <v>| GRID | Grids |</v>
       </c>
       <c r="Q91" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>| GRID | Grids | Rejillas |</v>
       </c>
       <c r="R91" s="5" t="str">
@@ -19111,12 +19132,12 @@
         <v>| GRID | Grids | Rejillas |  | |</v>
       </c>
       <c r="T91" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>| GRID | Grids | Rejillas |  | | |</v>
       </c>
       <c r="U91" s="5"/>
       <c r="V91" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| GRID | Grids | Rejillas |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -19146,7 +19167,7 @@
         <v>| GRLN | Grade line |</v>
       </c>
       <c r="Q92" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>| GRLN | Grade line | Línea de rasante |</v>
       </c>
       <c r="R92" s="5" t="str">
@@ -19158,12 +19179,12 @@
         <v>| GRLN | Grade line | Línea de rasante |  | |</v>
       </c>
       <c r="T92" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>| GRLN | Grade line | Línea de rasante |  | | |</v>
       </c>
       <c r="U92" s="5"/>
       <c r="V92" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| GRLN | Grade line | Línea de rasante |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -19193,7 +19214,7 @@
         <v>| GRND | Ground system |</v>
       </c>
       <c r="Q93" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>| GRND | Ground system | Sistema de puesta a tierra |</v>
       </c>
       <c r="R93" s="5" t="str">
@@ -19205,12 +19226,12 @@
         <v>| GRND | Ground system | Sistema de puesta a tierra |  | |</v>
       </c>
       <c r="T93" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>| GRND | Ground system | Sistema de puesta a tierra |  | | |</v>
       </c>
       <c r="U93" s="5"/>
       <c r="V93" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| GRND | Ground system | Sistema de puesta a tierra |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -19240,7 +19261,7 @@
         <v>| HALN | Halon |</v>
       </c>
       <c r="Q94" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>| HALN | Halon | Halón |</v>
       </c>
       <c r="R94" s="5" t="str">
@@ -19252,12 +19273,12 @@
         <v>| HALN | Halon | Halón |  | |</v>
       </c>
       <c r="T94" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>| HALN | Halon | Halón |  | | |</v>
       </c>
       <c r="U94" s="5"/>
       <c r="V94" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| HALN | Halon | Halón |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -19287,7 +19308,7 @@
         <v>| HVAC | HVAC systems |</v>
       </c>
       <c r="Q95" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>| HVAC | HVAC systems | Sistemas de climatización (HVAC) |</v>
       </c>
       <c r="R95" s="5" t="str">
@@ -19299,16 +19320,16 @@
         <v>| HVAC | HVAC systems | Sistemas de climatización (HVAC) |  | |</v>
       </c>
       <c r="T95" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>| HVAC | HVAC systems | Sistemas de climatización (HVAC) |  | | |</v>
       </c>
       <c r="U95" s="5"/>
       <c r="V95" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| HVAC | HVAC systems | Sistemas de climatización (HVAC) |  | | | | | | | | | |</v>
       </c>
     </row>
-    <row r="96" spans="2:22" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="2:22" ht="30.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B96" s="4" t="s">
         <v>471</v>
       </c>
@@ -19334,7 +19355,7 @@
         <v>| HWTR | Hot water heating system |</v>
       </c>
       <c r="Q96" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>| HWTR | Hot water heating system | Sistema de calentamiento de agua caliente |</v>
       </c>
       <c r="R96" s="5" t="str">
@@ -19346,12 +19367,12 @@
         <v>| HWTR | Hot water heating system | Sistema de calentamiento de agua caliente |  | |</v>
       </c>
       <c r="T96" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>| HWTR | Hot water heating system | Sistema de calentamiento de agua caliente |  | | |</v>
       </c>
       <c r="U96" s="5"/>
       <c r="V96" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| HWTR | Hot water heating system | Sistema de calentamiento de agua caliente |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -19381,7 +19402,7 @@
         <v>| HYDR | Hydraulic structure |</v>
       </c>
       <c r="Q97" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>| HYDR | Hydraulic structure | Estructura hidráulica |</v>
       </c>
       <c r="R97" s="5" t="str">
@@ -19393,12 +19414,12 @@
         <v>| HYDR | Hydraulic structure | Estructura hidráulica |  | |</v>
       </c>
       <c r="T97" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>| HYDR | Hydraulic structure | Estructura hidráulica |  | | |</v>
       </c>
       <c r="U97" s="5"/>
       <c r="V97" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| HYDR | Hydraulic structure | Estructura hidráulica |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -19428,7 +19449,7 @@
         <v>| IGAS | Inert gas |</v>
       </c>
       <c r="Q98" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>| IGAS | Inert gas | Gas inerte |</v>
       </c>
       <c r="R98" s="5" t="str">
@@ -19440,12 +19461,12 @@
         <v>| IGAS | Inert gas | Gas inerte |  | |</v>
       </c>
       <c r="T98" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>| IGAS | Inert gas | Gas inerte |  | | |</v>
       </c>
       <c r="U98" s="5"/>
       <c r="V98" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| IGAS | Inert gas | Gas inerte |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -19475,7 +19496,7 @@
         <v>| INGR | Ingrants |</v>
       </c>
       <c r="Q99" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>| INGR | Ingrants | Concesiones |</v>
       </c>
       <c r="R99" s="5" t="str">
@@ -19487,12 +19508,12 @@
         <v>| INGR | Ingrants | Concesiones |  | |</v>
       </c>
       <c r="T99" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>| INGR | Ingrants | Concesiones |  | | |</v>
       </c>
       <c r="U99" s="5"/>
       <c r="V99" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| INGR | Ingrants | Concesiones |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -19522,7 +19543,7 @@
         <v>| INST | Instrumentation system |</v>
       </c>
       <c r="Q100" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>| INST | Instrumentation system | Sistema de instrumentación |</v>
       </c>
       <c r="R100" s="5" t="str">
@@ -19534,12 +19555,12 @@
         <v>| INST | Instrumentation system | Sistema de instrumentación |  | |</v>
       </c>
       <c r="T100" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>| INST | Instrumentation system | Sistema de instrumentación |  | | |</v>
       </c>
       <c r="U100" s="5"/>
       <c r="V100" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| INST | Instrumentation system | Sistema de instrumentación |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -19569,7 +19590,7 @@
         <v>| INTC | Intercom / PA systems |</v>
       </c>
       <c r="Q101" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>| INTC | Intercom / PA systems | Intercomunicador/PA Sistemas |</v>
       </c>
       <c r="R101" s="5" t="str">
@@ -19581,12 +19602,12 @@
         <v>| INTC | Intercom / PA systems | Intercomunicador/PA Sistemas |  | |</v>
       </c>
       <c r="T101" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>| INTC | Intercom / PA systems | Intercomunicador/PA Sistemas |  | | |</v>
       </c>
       <c r="U101" s="5"/>
       <c r="V101" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| INTC | Intercom / PA systems | Intercomunicador/PA Sistemas |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -19616,7 +19637,7 @@
         <v>| IRRG | Irrigation |</v>
       </c>
       <c r="Q102" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>| IRRG | Irrigation | Riego |</v>
       </c>
       <c r="R102" s="5" t="str">
@@ -19628,12 +19649,12 @@
         <v>| IRRG | Irrigation | Riego |  | |</v>
       </c>
       <c r="T102" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>| IRRG | Irrigation | Riego |  | | |</v>
       </c>
       <c r="U102" s="5"/>
       <c r="V102" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| IRRG | Irrigation | Riego |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -19663,7 +19684,7 @@
         <v>| JNTS | Joints |</v>
       </c>
       <c r="Q103" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>| JNTS | Joints | Juntas |</v>
       </c>
       <c r="R103" s="5" t="str">
@@ -19675,12 +19696,12 @@
         <v>| JNTS | Joints | Juntas |  | |</v>
       </c>
       <c r="T103" s="5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>| JNTS | Joints | Juntas |  | | |</v>
       </c>
       <c r="U103" s="5"/>
       <c r="V103" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>| JNTS | Joints | Juntas |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -19694,6 +19715,10 @@
       <c r="D104" s="1" t="s">
         <v>497</v>
       </c>
+      <c r="Q104" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| JOIS | Joists | Viguetas |</v>
+      </c>
     </row>
     <row r="105" spans="2:22" x14ac:dyDescent="0.55000000000000004">
       <c r="B105" s="1" t="s">
@@ -19705,6 +19730,10 @@
       <c r="D105" s="1" t="s">
         <v>500</v>
       </c>
+      <c r="Q105" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| LAND | Land | Terreno |</v>
+      </c>
     </row>
     <row r="106" spans="2:22" x14ac:dyDescent="0.55000000000000004">
       <c r="B106" s="1" t="s">
@@ -19716,6 +19745,10 @@
       <c r="D106" s="1" t="s">
         <v>503</v>
       </c>
+      <c r="Q106" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| LEGN | Legend, symbols keys | Leyenda, símbolos y claves |</v>
+      </c>
     </row>
     <row r="107" spans="2:22" x14ac:dyDescent="0.55000000000000004">
       <c r="B107" s="1" t="s">
@@ -19727,6 +19760,10 @@
       <c r="D107" s="1" t="s">
         <v>506</v>
       </c>
+      <c r="Q107" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| LEVE | Levee | Dique |</v>
+      </c>
     </row>
     <row r="108" spans="2:22" x14ac:dyDescent="0.55000000000000004">
       <c r="B108" s="1" t="s">
@@ -19738,6 +19775,10 @@
       <c r="D108" s="1" t="s">
         <v>509</v>
       </c>
+      <c r="Q108" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| LGAS | Laboratory gas systems | Sistemas de gases de laboratorio |</v>
+      </c>
     </row>
     <row r="109" spans="2:22" x14ac:dyDescent="0.55000000000000004">
       <c r="B109" s="1" t="s">
@@ -19749,6 +19790,10 @@
       <c r="D109" s="1" t="s">
         <v>512</v>
       </c>
+      <c r="Q109" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| LIQD | Liquid | Líquido |</v>
+      </c>
     </row>
     <row r="110" spans="2:22" x14ac:dyDescent="0.55000000000000004">
       <c r="B110" s="1" t="s">
@@ -19760,6 +19805,10 @@
       <c r="D110" s="1" t="s">
         <v>515</v>
       </c>
+      <c r="Q110" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| LITE | Lighting | Iluminación |</v>
+      </c>
     </row>
     <row r="111" spans="2:22" x14ac:dyDescent="0.55000000000000004">
       <c r="B111" s="1" t="s">
@@ -19771,6 +19820,10 @@
       <c r="D111" s="1" t="s">
         <v>518</v>
       </c>
+      <c r="Q111" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| LNTL | Lintels | Dinteles |</v>
+      </c>
     </row>
     <row r="112" spans="2:22" x14ac:dyDescent="0.55000000000000004">
       <c r="B112" s="1" t="s">
@@ -19782,8 +19835,12 @@
       <c r="D112" s="1" t="s">
         <v>521</v>
       </c>
-    </row>
-    <row r="113" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q112" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| LOCN | Limits of construction | Límites de construcción |</v>
+      </c>
+    </row>
+    <row r="113" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B113" s="1" t="s">
         <v>522</v>
       </c>
@@ -19793,8 +19850,12 @@
       <c r="D113" s="1" t="s">
         <v>524</v>
       </c>
-    </row>
-    <row r="114" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q113" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| LTNG | Lightning protection system | Sistema de protección contra rayos |</v>
+      </c>
+    </row>
+    <row r="114" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B114" s="1" t="s">
         <v>525</v>
       </c>
@@ -19804,8 +19865,12 @@
       <c r="D114" s="1" t="s">
         <v>527</v>
       </c>
-    </row>
-    <row r="115" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q114" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| MACH | Machine shop | Taller de maquinaria |</v>
+      </c>
+    </row>
+    <row r="115" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B115" s="1" t="s">
         <v>528</v>
       </c>
@@ -19815,8 +19880,12 @@
       <c r="D115" s="1" t="s">
         <v>530</v>
       </c>
-    </row>
-    <row r="116" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q115" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| MAJQ | Major equipment | Equipo principal |</v>
+      </c>
+    </row>
+    <row r="116" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B116" s="1" t="s">
         <v>531</v>
       </c>
@@ -19826,8 +19895,12 @@
       <c r="D116" s="1" t="s">
         <v>533</v>
       </c>
-    </row>
-    <row r="117" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q116" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| MDGS | Medical gas systems | Sistemas de gases medicinales |</v>
+      </c>
+    </row>
+    <row r="117" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B117" s="1" t="s">
         <v>534</v>
       </c>
@@ -19837,8 +19910,12 @@
       <c r="D117" s="1" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="118" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q117" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| MILL | Millwork | Carpintería |</v>
+      </c>
+    </row>
+    <row r="118" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B118" s="1" t="s">
         <v>536</v>
       </c>
@@ -19848,8 +19925,12 @@
       <c r="D118" s="1" t="s">
         <v>538</v>
       </c>
-    </row>
-    <row r="119" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q118" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| MINQ | Minor equipment | Equipo menor |</v>
+      </c>
+    </row>
+    <row r="119" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B119" s="1" t="s">
         <v>539</v>
       </c>
@@ -19859,8 +19940,12 @@
       <c r="D119" s="1" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="120" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q119" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| MKUP | Make-up air systems | Sistemas de aire de reposición |</v>
+      </c>
+    </row>
+    <row r="120" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B120" s="1" t="s">
         <v>542</v>
       </c>
@@ -19870,8 +19955,12 @@
       <c r="D120" s="1" t="s">
         <v>544</v>
       </c>
-    </row>
-    <row r="121" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q120" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| MNTG | Mounting system | Sistema de montaje |</v>
+      </c>
+    </row>
+    <row r="121" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B121" s="1" t="s">
         <v>545</v>
       </c>
@@ -19881,8 +19970,12 @@
       <c r="D121" s="1" t="s">
         <v>547</v>
       </c>
-    </row>
-    <row r="122" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q121" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| MPIP | Miscellaneous piping systems | Sistemas de tuberías misceláneos |</v>
+      </c>
+    </row>
+    <row r="122" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B122" s="1" t="s">
         <v>548</v>
       </c>
@@ -19892,8 +19985,12 @@
       <c r="D122" s="1" t="s">
         <v>550</v>
       </c>
-    </row>
-    <row r="123" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q122" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| NGAS | Natural gas systems | Sistemas de gas natural |</v>
+      </c>
+    </row>
+    <row r="123" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B123" s="1" t="s">
         <v>551</v>
       </c>
@@ -19903,8 +20000,12 @@
       <c r="D123" s="1" t="s">
         <v>553</v>
       </c>
-    </row>
-    <row r="124" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q123" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| NODE | Node | Nodo |</v>
+      </c>
+    </row>
+    <row r="124" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B124" s="1" t="s">
         <v>554</v>
       </c>
@@ -19914,8 +20015,12 @@
       <c r="D124" s="1" t="s">
         <v>556</v>
       </c>
-    </row>
-    <row r="125" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q124" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| NURS | Nurse call system | Sistema de llamada a enfermeras |</v>
+      </c>
+    </row>
+    <row r="125" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B125" s="1" t="s">
         <v>557</v>
       </c>
@@ -19925,8 +20030,12 @@
       <c r="D125" s="1" t="s">
         <v>559</v>
       </c>
-    </row>
-    <row r="126" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q125" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| OBST | Obstructions | Obstrucciones |</v>
+      </c>
+    </row>
+    <row r="126" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B126" s="1" t="s">
         <v>560</v>
       </c>
@@ -19936,8 +20045,12 @@
       <c r="D126" s="1" t="s">
         <v>562</v>
       </c>
-    </row>
-    <row r="127" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q126" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| OIL~ | Oil | Petróleo |</v>
+      </c>
+    </row>
+    <row r="127" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B127" s="1" t="s">
         <v>563</v>
       </c>
@@ -19947,8 +20060,12 @@
       <c r="D127" s="1" t="s">
         <v>565</v>
       </c>
-    </row>
-    <row r="128" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q127" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| OTGR | Outgrants | Conducciones de salida |</v>
+      </c>
+    </row>
+    <row r="128" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B128" s="1" t="s">
         <v>566</v>
       </c>
@@ -19958,8 +20075,12 @@
       <c r="D128" s="1" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="129" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q128" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| PADS | Pads | Almohadillas |</v>
+      </c>
+    </row>
+    <row r="129" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B129" s="1" t="s">
         <v>569</v>
       </c>
@@ -19969,8 +20090,12 @@
       <c r="D129" s="1" t="s">
         <v>571</v>
       </c>
-    </row>
-    <row r="130" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q129" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| PERC | Perc testing | Prueba de percolación |</v>
+      </c>
+    </row>
+    <row r="130" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B130" s="1" t="s">
         <v>572</v>
       </c>
@@ -19980,8 +20105,12 @@
       <c r="D130" s="1" t="s">
         <v>574</v>
       </c>
-    </row>
-    <row r="131" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q130" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| PGNG | Paging system | Sistema de buscapersonas |</v>
+      </c>
+    </row>
+    <row r="131" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B131" s="1" t="s">
         <v>575</v>
       </c>
@@ -19991,8 +20120,12 @@
       <c r="D131" s="1" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="132" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q131" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| PHON | Telephone system | Sistema telefónico |</v>
+      </c>
+    </row>
+    <row r="132" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B132" s="1" t="s">
         <v>578</v>
       </c>
@@ -20002,8 +20135,12 @@
       <c r="D132" s="1" t="s">
         <v>580</v>
       </c>
-    </row>
-    <row r="133" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q132" s="5" t="str">
+        <f t="shared" si="10"/>
+        <v>| PIPE | Piping | Tuberías |</v>
+      </c>
+    </row>
+    <row r="133" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B133" s="1" t="s">
         <v>581</v>
       </c>
@@ -20013,8 +20150,12 @@
       <c r="D133" s="1" t="s">
         <v>583</v>
       </c>
-    </row>
-    <row r="134" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q133" s="5" t="str">
+        <f t="shared" ref="Q133:Q196" si="13">_xlfn.CONCAT("| ",B133," | ",C133," | ",D133," |")</f>
+        <v>| PLAN | Key Plan (Floor Plan) | Plano clave (Plano de planta) |</v>
+      </c>
+    </row>
+    <row r="134" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B134" s="1" t="s">
         <v>584</v>
       </c>
@@ -20024,8 +20165,12 @@
       <c r="D134" s="1" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="135" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q134" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| PLAT | Platform | Andén |</v>
+      </c>
+    </row>
+    <row r="135" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B135" s="1" t="s">
         <v>587</v>
       </c>
@@ -20035,8 +20180,12 @@
       <c r="D135" s="1" t="s">
         <v>589</v>
       </c>
-    </row>
-    <row r="136" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q135" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| PLNT | Plant and landscape material | Planta y material de jardinería |</v>
+      </c>
+    </row>
+    <row r="136" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B136" s="1" t="s">
         <v>590</v>
       </c>
@@ -20046,8 +20195,12 @@
       <c r="D136" s="1" t="s">
         <v>592</v>
       </c>
-    </row>
-    <row r="137" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q136" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| POND | Ponds | Estanques |</v>
+      </c>
+    </row>
+    <row r="137" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B137" s="1" t="s">
         <v>593</v>
       </c>
@@ -20057,8 +20210,12 @@
       <c r="D137" s="1" t="s">
         <v>595</v>
       </c>
-    </row>
-    <row r="138" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q137" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| POWR | Power | Energía |</v>
+      </c>
+    </row>
+    <row r="138" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B138" s="1" t="s">
         <v>596</v>
       </c>
@@ -20068,8 +20225,12 @@
       <c r="D138" s="1" t="s">
         <v>598</v>
       </c>
-    </row>
-    <row r="139" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q138" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| PRKG | Parking lots | Estacionamientos |</v>
+      </c>
+    </row>
+    <row r="139" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B139" s="1" t="s">
         <v>599</v>
       </c>
@@ -20079,8 +20240,12 @@
       <c r="D139" s="1" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="140" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q139" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| PROC | Process systems | Sistemas de proceso |</v>
+      </c>
+    </row>
+    <row r="140" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B140" s="1" t="s">
         <v>602</v>
       </c>
@@ -20090,8 +20255,12 @@
       <c r="D140" s="1" t="s">
         <v>604</v>
       </c>
-    </row>
-    <row r="141" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q140" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| PROJ | Projector system | Sistema de proyectores |</v>
+      </c>
+    </row>
+    <row r="141" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B141" s="1" t="s">
         <v>605</v>
       </c>
@@ -20101,8 +20270,12 @@
       <c r="D141" s="1" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="142" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q141" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| PROP | Property | Propiedad |</v>
+      </c>
+    </row>
+    <row r="142" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B142" s="1" t="s">
         <v>608</v>
       </c>
@@ -20112,8 +20285,12 @@
       <c r="D142" s="1" t="s">
         <v>610</v>
       </c>
-    </row>
-    <row r="143" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q142" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| PROT | Fire protection system | Sistema de protección contra incendios |</v>
+      </c>
+    </row>
+    <row r="143" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B143" s="1" t="s">
         <v>611</v>
       </c>
@@ -20123,8 +20300,12 @@
       <c r="D143" s="1" t="s">
         <v>613</v>
       </c>
-    </row>
-    <row r="144" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q143" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| PRTN | Partitions | Tabiques |</v>
+      </c>
+    </row>
+    <row r="144" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B144" s="1" t="s">
         <v>614</v>
       </c>
@@ -20134,8 +20315,12 @@
       <c r="D144" s="1" t="s">
         <v>616</v>
       </c>
-    </row>
-    <row r="145" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q144" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| PVMD | Photovoltaic modules | Módulos fotovoltaicos |</v>
+      </c>
+    </row>
+    <row r="145" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B145" s="1" t="s">
         <v>617</v>
       </c>
@@ -20145,8 +20330,12 @@
       <c r="D145" s="1" t="s">
         <v>619</v>
       </c>
-    </row>
-    <row r="146" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q145" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| PVMT | Pavement | Pavimento |</v>
+      </c>
+    </row>
+    <row r="146" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B146" s="1" t="s">
         <v>620</v>
       </c>
@@ -20156,8 +20345,12 @@
       <c r="D146" s="1" t="s">
         <v>622</v>
       </c>
-    </row>
-    <row r="147" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q146" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| RAIL | Railroad | Ferrocarril |</v>
+      </c>
+    </row>
+    <row r="147" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B147" s="1" t="s">
         <v>623</v>
       </c>
@@ -20167,8 +20360,12 @@
       <c r="D147" s="1" t="s">
         <v>625</v>
       </c>
-    </row>
-    <row r="148" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q147" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| RAIR | Relief air systems | Sistemas de aire de alivio |</v>
+      </c>
+    </row>
+    <row r="148" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B148" s="1" t="s">
         <v>626</v>
       </c>
@@ -20178,8 +20375,12 @@
       <c r="D148" s="1" t="s">
         <v>628</v>
       </c>
-    </row>
-    <row r="149" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q148" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| RCOV | Energy recovery systems | Sistemas de recuperación de energía |</v>
+      </c>
+    </row>
+    <row r="149" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B149" s="1" t="s">
         <v>629</v>
       </c>
@@ -20189,8 +20390,12 @@
       <c r="D149" s="1" t="s">
         <v>631</v>
       </c>
-    </row>
-    <row r="150" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q149" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| REFG | Refrigeration systems | Sistemas de refrigeración |</v>
+      </c>
+    </row>
+    <row r="150" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B150" s="1" t="s">
         <v>632</v>
       </c>
@@ -20200,8 +20405,12 @@
       <c r="D150" s="1" t="s">
         <v>634</v>
       </c>
-    </row>
-    <row r="151" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q150" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| RIGG | Rigging / automation systems | Aparejos/automatización Sistemas |</v>
+      </c>
+    </row>
+    <row r="151" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B151" s="1" t="s">
         <v>635</v>
       </c>
@@ -20211,8 +20420,12 @@
       <c r="D151" s="1" t="s">
         <v>637</v>
       </c>
-    </row>
-    <row r="152" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q151" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| RIVR | River | Río |</v>
+      </c>
+    </row>
+    <row r="152" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B152" s="1" t="s">
         <v>638</v>
       </c>
@@ -20222,8 +20435,12 @@
       <c r="D152" s="1" t="s">
         <v>640</v>
       </c>
-    </row>
-    <row r="153" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q152" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| ROAD | Roadways | Carreteras |</v>
+      </c>
+    </row>
+    <row r="153" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B153" s="1" t="s">
         <v>641</v>
       </c>
@@ -20233,8 +20450,12 @@
       <c r="D153" s="1" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="154" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q153" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| ROOF | Roof | Techo |</v>
+      </c>
+    </row>
+    <row r="154" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B154" s="1" t="s">
         <v>643</v>
       </c>
@@ -20244,8 +20465,12 @@
       <c r="D154" s="1" t="s">
         <v>645</v>
       </c>
-    </row>
-    <row r="155" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q154" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| RRAP | Riprap | Escalones |</v>
+      </c>
+    </row>
+    <row r="155" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B155" s="1" t="s">
         <v>646</v>
       </c>
@@ -20255,8 +20480,12 @@
       <c r="D155" s="1" t="s">
         <v>648</v>
       </c>
-    </row>
-    <row r="156" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q155" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| RUNW | Runway | Pista |</v>
+      </c>
+    </row>
+    <row r="156" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B156" s="1" t="s">
         <v>649</v>
       </c>
@@ -20266,8 +20495,12 @@
       <c r="D156" s="1" t="s">
         <v>651</v>
       </c>
-    </row>
-    <row r="157" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q156" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| RWAY | Right-of-way | Derecho de paso |</v>
+      </c>
+    </row>
+    <row r="157" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B157" s="1" t="s">
         <v>652</v>
       </c>
@@ -20277,8 +20510,12 @@
       <c r="D157" s="1" t="s">
         <v>654</v>
       </c>
-    </row>
-    <row r="158" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q157" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| SECT | Section | Sección |</v>
+      </c>
+    </row>
+    <row r="158" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B158" s="1" t="s">
         <v>655</v>
       </c>
@@ -20288,8 +20525,12 @@
       <c r="D158" s="1" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="159" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q158" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| SERT | Security system | Sistema de seguridad |</v>
+      </c>
+    </row>
+    <row r="159" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B159" s="1" t="s">
         <v>658</v>
       </c>
@@ -20299,8 +20540,12 @@
       <c r="D159" s="1" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="160" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q159" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| SGHT | Sight distance | Distancia visual |</v>
+      </c>
+    </row>
+    <row r="160" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B160" s="1" t="s">
         <v>661</v>
       </c>
@@ -20310,8 +20555,12 @@
       <c r="D160" s="1" t="s">
         <v>663</v>
       </c>
-    </row>
-    <row r="161" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q160" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| SIGN | Sign | Señal |</v>
+      </c>
+    </row>
+    <row r="161" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B161" s="1" t="s">
         <v>664</v>
       </c>
@@ -20321,8 +20570,12 @@
       <c r="D161" s="1" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="162" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q161" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| SITE | Site features | Características del sitio |</v>
+      </c>
+    </row>
+    <row r="162" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B162" s="1" t="s">
         <v>667</v>
       </c>
@@ -20332,8 +20585,12 @@
       <c r="D162" s="1" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="163" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q162" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| SLAB | Slab | Losa |</v>
+      </c>
+    </row>
+    <row r="163" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B163" s="1" t="s">
         <v>670</v>
       </c>
@@ -20343,8 +20600,12 @@
       <c r="D163" s="1" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="164" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q163" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| SLUR | Slurry | Lodo |</v>
+      </c>
+    </row>
+    <row r="164" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B164" s="1" t="s">
         <v>673</v>
       </c>
@@ -20354,8 +20615,12 @@
       <c r="D164" s="1" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="165" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q164" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| SMOK | Smoke extraction systems | Sistemas de extracción de humos |</v>
+      </c>
+    </row>
+    <row r="165" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B165" s="1" t="s">
         <v>676</v>
       </c>
@@ -20365,8 +20630,12 @@
       <c r="D165" s="1" t="s">
         <v>678</v>
       </c>
-    </row>
-    <row r="166" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q165" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| SOIL | Soils | Suelos |</v>
+      </c>
+    </row>
+    <row r="166" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B166" s="1" t="s">
         <v>679</v>
       </c>
@@ -20376,8 +20645,12 @@
       <c r="D166" s="1" t="s">
         <v>681</v>
       </c>
-    </row>
-    <row r="167" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q166" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| SOUN | Sound system | Sistema de sonido |</v>
+      </c>
+    </row>
+    <row r="167" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B167" s="1" t="s">
         <v>682</v>
       </c>
@@ -20387,8 +20660,12 @@
       <c r="D167" s="1" t="s">
         <v>684</v>
       </c>
-    </row>
-    <row r="168" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q167" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| SPCL | Special systems | Sistemas especiales |</v>
+      </c>
+    </row>
+    <row r="168" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B168" s="1" t="s">
         <v>685</v>
       </c>
@@ -20398,8 +20675,12 @@
       <c r="D168" s="1" t="s">
         <v>687</v>
       </c>
-    </row>
-    <row r="169" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q168" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| SPFX | Entertainment special effects system | Sistema de efectos especiales para entretenimiento |</v>
+      </c>
+    </row>
+    <row r="169" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B169" s="1" t="s">
         <v>688</v>
       </c>
@@ -20409,8 +20690,12 @@
       <c r="D169" s="1" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="170" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q169" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| SPKL | Sprinkler | Rociadores |</v>
+      </c>
+    </row>
+    <row r="170" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B170" s="1" t="s">
         <v>691</v>
       </c>
@@ -20420,8 +20705,12 @@
       <c r="D170" s="1" t="s">
         <v>693</v>
       </c>
-    </row>
-    <row r="171" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q170" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| SSWR | Sanitary sewer | Alcantarillado sanitario |</v>
+      </c>
+    </row>
+    <row r="171" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B171" s="1" t="s">
         <v>694</v>
       </c>
@@ -20431,8 +20720,12 @@
       <c r="D171" s="1" t="s">
         <v>696</v>
       </c>
-    </row>
-    <row r="172" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q171" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| STEM | Steam system | Sistema de vapor |</v>
+      </c>
+    </row>
+    <row r="172" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B172" s="1" t="s">
         <v>697</v>
       </c>
@@ -20442,8 +20735,12 @@
       <c r="D172" s="1" t="s">
         <v>699</v>
       </c>
-    </row>
-    <row r="173" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q172" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| STIF | Stiffener | Refuerzo |</v>
+      </c>
+    </row>
+    <row r="173" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B173" s="1" t="s">
         <v>700</v>
       </c>
@@ -20453,8 +20750,12 @@
       <c r="D173" s="1" t="s">
         <v>702</v>
       </c>
-    </row>
-    <row r="174" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q173" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| STRM | Storm sewer | Alcantarillado pluvial |</v>
+      </c>
+    </row>
+    <row r="174" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B174" s="1" t="s">
         <v>703</v>
       </c>
@@ -20464,8 +20765,12 @@
       <c r="D174" s="1" t="s">
         <v>705</v>
       </c>
-    </row>
-    <row r="175" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q174" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| STRS | Stairs | Escaleras |</v>
+      </c>
+    </row>
+    <row r="175" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B175" s="1" t="s">
         <v>706</v>
       </c>
@@ -20475,8 +20780,12 @@
       <c r="D175" s="1" t="s">
         <v>708</v>
       </c>
-    </row>
-    <row r="176" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q175" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| SURV | Survey | Topografía |</v>
+      </c>
+    </row>
+    <row r="176" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B176" s="1" t="s">
         <v>709</v>
       </c>
@@ -20486,8 +20795,12 @@
       <c r="D176" s="1" t="s">
         <v>711</v>
       </c>
-    </row>
-    <row r="177" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q176" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| SWLK | Sidewalks | Aceras |</v>
+      </c>
+    </row>
+    <row r="177" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B177" s="1" t="s">
         <v>712</v>
       </c>
@@ -20497,8 +20810,12 @@
       <c r="D177" s="1" t="s">
         <v>714</v>
       </c>
-    </row>
-    <row r="178" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q177" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| TEST | Test equipment | Equipo de prueba |</v>
+      </c>
+    </row>
+    <row r="178" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B178" s="1" t="s">
         <v>715</v>
       </c>
@@ -20508,8 +20825,12 @@
       <c r="D178" s="1" t="s">
         <v>717</v>
       </c>
-    </row>
-    <row r="179" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q178" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| TILE | Tile | Tejas |</v>
+      </c>
+    </row>
+    <row r="179" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B179" s="1" t="s">
         <v>718</v>
       </c>
@@ -20519,8 +20840,12 @@
       <c r="D179" s="1" t="s">
         <v>720</v>
       </c>
-    </row>
-    <row r="180" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q179" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| TINN | Triangulated irregular network | Red irregular triangular |</v>
+      </c>
+    </row>
+    <row r="180" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B180" s="1" t="s">
         <v>721</v>
       </c>
@@ -20530,8 +20855,12 @@
       <c r="D180" s="1" t="s">
         <v>723</v>
       </c>
-    </row>
-    <row r="181" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q180" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| TOPO | Topographic feature | Característica topográfica |</v>
+      </c>
+    </row>
+    <row r="181" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B181" s="1" t="s">
         <v>724</v>
       </c>
@@ -20541,8 +20870,12 @@
       <c r="D181" s="1" t="s">
         <v>726</v>
       </c>
-    </row>
-    <row r="182" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q181" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| TRAL | Trails or paths | Senderos o caminos |</v>
+      </c>
+    </row>
+    <row r="182" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B182" s="1" t="s">
         <v>727</v>
       </c>
@@ -20552,8 +20885,12 @@
       <c r="D182" s="1" t="s">
         <v>729</v>
       </c>
-    </row>
-    <row r="183" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q182" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| TRAN | Transmission system | Sistema de transmisión |</v>
+      </c>
+    </row>
+    <row r="183" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B183" s="1" t="s">
         <v>730</v>
       </c>
@@ -20563,8 +20900,12 @@
       <c r="D183" s="1" t="s">
         <v>732</v>
       </c>
-    </row>
-    <row r="184" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q183" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| TRUS | Trusses | Cerchas |</v>
+      </c>
+    </row>
+    <row r="184" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B184" s="1" t="s">
         <v>733</v>
       </c>
@@ -20574,8 +20915,12 @@
       <c r="D184" s="1" t="s">
         <v>735</v>
       </c>
-    </row>
-    <row r="185" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q184" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| TVAN | Television antenna system | Sistema de antena de televisión |</v>
+      </c>
+    </row>
+    <row r="185" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B185" s="1" t="s">
         <v>736</v>
       </c>
@@ -20585,8 +20930,12 @@
       <c r="D185" s="1" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="186" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q185" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| TVVS | Television and video system | Sistema de televisión y video |</v>
+      </c>
+    </row>
+    <row r="186" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B186" s="1" t="s">
         <v>739</v>
       </c>
@@ -20596,8 +20945,12 @@
       <c r="D186" s="1" t="s">
         <v>741</v>
       </c>
-    </row>
-    <row r="187" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q186" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| UNID | Unidentified site objects | Objetos no identificados del sitio |</v>
+      </c>
+    </row>
+    <row r="187" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B187" s="1" t="s">
         <v>742</v>
       </c>
@@ -20607,8 +20960,12 @@
       <c r="D187" s="1" t="s">
         <v>744</v>
       </c>
-    </row>
-    <row r="188" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q187" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| UTIL | Utilities | Servicios públicos |</v>
+      </c>
+    </row>
+    <row r="188" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B188" s="1" t="s">
         <v>745</v>
       </c>
@@ -20618,8 +20975,12 @@
       <c r="D188" s="1" t="s">
         <v>747</v>
       </c>
-    </row>
-    <row r="189" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q188" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| VACU | Vacuum | Aspiradora |</v>
+      </c>
+    </row>
+    <row r="189" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B189" s="1" t="s">
         <v>748</v>
       </c>
@@ -20629,8 +20990,12 @@
       <c r="D189" s="1" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="190" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q189" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| VIDO | Entertainment projection systems | Sistemas de proyección de entretenimiento |</v>
+      </c>
+    </row>
+    <row r="190" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B190" s="1" t="s">
         <v>751</v>
       </c>
@@ -20640,8 +21005,12 @@
       <c r="D190" s="1" t="s">
         <v>753</v>
       </c>
-    </row>
-    <row r="191" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q190" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| WALL | Walls | Muros |</v>
+      </c>
+    </row>
+    <row r="191" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B191" s="1" t="s">
         <v>754</v>
       </c>
@@ -20651,8 +21020,12 @@
       <c r="D191" s="1" t="s">
         <v>756</v>
       </c>
-    </row>
-    <row r="192" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q191" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| WATR | Water supply | Suministro de agua |</v>
+      </c>
+    </row>
+    <row r="192" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B192" s="1" t="s">
         <v>757</v>
       </c>
@@ -20662,8 +21035,12 @@
       <c r="D192" s="1" t="s">
         <v>759</v>
       </c>
-    </row>
-    <row r="193" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q192" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| WETL | Wetlands | Humedales |</v>
+      </c>
+    </row>
+    <row r="193" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B193" s="1" t="s">
         <v>760</v>
       </c>
@@ -20673,8 +21050,12 @@
       <c r="D193" s="1" t="s">
         <v>762</v>
       </c>
-    </row>
-    <row r="194" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q193" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| WIND | Wind powered | Energía eólica |</v>
+      </c>
+    </row>
+    <row r="194" spans="2:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B194" s="1" t="s">
         <v>763</v>
       </c>
@@ -20683,6 +21064,136 @@
       </c>
       <c r="D194" s="1" t="s">
         <v>765</v>
+      </c>
+      <c r="Q194" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>| WWAY | Waterway | Vía fluvial |</v>
+      </c>
+    </row>
+    <row r="195" spans="2:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q195" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>|  |  |  |</v>
+      </c>
+    </row>
+    <row r="196" spans="2:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q196" s="5" t="str">
+        <f t="shared" si="13"/>
+        <v>|  |  |  |</v>
+      </c>
+    </row>
+    <row r="197" spans="2:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q197" s="5" t="str">
+        <f t="shared" ref="Q197:Q215" si="14">_xlfn.CONCAT("| ",B197," | ",C197," | ",D197," |")</f>
+        <v>|  |  |  |</v>
+      </c>
+    </row>
+    <row r="198" spans="2:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q198" s="5" t="str">
+        <f t="shared" si="14"/>
+        <v>|  |  |  |</v>
+      </c>
+    </row>
+    <row r="199" spans="2:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q199" s="5" t="str">
+        <f t="shared" si="14"/>
+        <v>|  |  |  |</v>
+      </c>
+    </row>
+    <row r="200" spans="2:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q200" s="5" t="str">
+        <f t="shared" si="14"/>
+        <v>|  |  |  |</v>
+      </c>
+    </row>
+    <row r="201" spans="2:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q201" s="5" t="str">
+        <f t="shared" si="14"/>
+        <v>|  |  |  |</v>
+      </c>
+    </row>
+    <row r="202" spans="2:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q202" s="5" t="str">
+        <f t="shared" si="14"/>
+        <v>|  |  |  |</v>
+      </c>
+    </row>
+    <row r="203" spans="2:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q203" s="5" t="str">
+        <f t="shared" si="14"/>
+        <v>|  |  |  |</v>
+      </c>
+    </row>
+    <row r="204" spans="2:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q204" s="5" t="str">
+        <f t="shared" si="14"/>
+        <v>|  |  |  |</v>
+      </c>
+    </row>
+    <row r="205" spans="2:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q205" s="5" t="str">
+        <f t="shared" si="14"/>
+        <v>|  |  |  |</v>
+      </c>
+    </row>
+    <row r="206" spans="2:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q206" s="5" t="str">
+        <f t="shared" si="14"/>
+        <v>|  |  |  |</v>
+      </c>
+    </row>
+    <row r="207" spans="2:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q207" s="5" t="str">
+        <f t="shared" si="14"/>
+        <v>|  |  |  |</v>
+      </c>
+    </row>
+    <row r="208" spans="2:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q208" s="5" t="str">
+        <f t="shared" si="14"/>
+        <v>|  |  |  |</v>
+      </c>
+    </row>
+    <row r="209" spans="17:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q209" s="5" t="str">
+        <f t="shared" si="14"/>
+        <v>|  |  |  |</v>
+      </c>
+    </row>
+    <row r="210" spans="17:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q210" s="5" t="str">
+        <f t="shared" si="14"/>
+        <v>|  |  |  |</v>
+      </c>
+    </row>
+    <row r="211" spans="17:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q211" s="5" t="str">
+        <f t="shared" si="14"/>
+        <v>|  |  |  |</v>
+      </c>
+    </row>
+    <row r="212" spans="17:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q212" s="5" t="str">
+        <f t="shared" si="14"/>
+        <v>|  |  |  |</v>
+      </c>
+    </row>
+    <row r="213" spans="17:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q213" s="5" t="str">
+        <f t="shared" si="14"/>
+        <v>|  |  |  |</v>
+      </c>
+    </row>
+    <row r="214" spans="17:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q214" s="5" t="str">
+        <f t="shared" si="14"/>
+        <v>|  |  |  |</v>
+      </c>
+    </row>
+    <row r="215" spans="17:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q215" s="5" t="str">
+        <f t="shared" si="14"/>
+        <v>|  |  |  |</v>
       </c>
     </row>
   </sheetData>

--- a/file/temp/ExcelTableToMarkDownSample.xlsx
+++ b/file/temp/ExcelTableToMarkDownSample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\D_SSD2TB\R.DAPC\file\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB54205-E7CF-4344-B881-D8FF61F340BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CF8673B-C55C-4575-9502-674C6A0B4F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="6" xr2:uid="{D94F812B-BC61-4A22-9692-634766FE0D40}"/>
   </bookViews>

--- a/file/temp/ExcelTableToMarkDownSample.xlsx
+++ b/file/temp/ExcelTableToMarkDownSample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\D_SSD2TB\R.DAPC\file\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CF8673B-C55C-4575-9502-674C6A0B4F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADDC1E28-14F5-4AAC-93AF-0A6F82B0D84E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="6" xr2:uid="{D94F812B-BC61-4A22-9692-634766FE0D40}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{D94F812B-BC61-4A22-9692-634766FE0D40}"/>
   </bookViews>
   <sheets>
     <sheet name="Sample" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2176" uniqueCount="1761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2257" uniqueCount="1823">
   <si>
     <t>Creación de tablas en formato .md</t>
   </si>
@@ -5333,6 +5333,192 @@
   </si>
   <si>
     <t>Vía fluvial: amarre</t>
+  </si>
+  <si>
+    <t>SB</t>
+  </si>
+  <si>
+    <t>Structural Substructure</t>
+  </si>
+  <si>
+    <t>SD</t>
+  </si>
+  <si>
+    <t>Structural Demolition</t>
+  </si>
+  <si>
+    <t>SF</t>
+  </si>
+  <si>
+    <t>Structural Framing</t>
+  </si>
+  <si>
+    <t>SJ</t>
+  </si>
+  <si>
+    <t>SK</t>
+  </si>
+  <si>
+    <t>SS</t>
+  </si>
+  <si>
+    <t>Structural Site</t>
+  </si>
+  <si>
+    <t>VA</t>
+  </si>
+  <si>
+    <t>Survey / Mapping Aerial</t>
+  </si>
+  <si>
+    <t>VC</t>
+  </si>
+  <si>
+    <t>Survey / Mapping Computated Points</t>
+  </si>
+  <si>
+    <t>VF</t>
+  </si>
+  <si>
+    <t>Survey / Mapping Field</t>
+  </si>
+  <si>
+    <t>VI</t>
+  </si>
+  <si>
+    <t>Survey / Mapping Digital</t>
+  </si>
+  <si>
+    <t>VJ</t>
+  </si>
+  <si>
+    <t>VK</t>
+  </si>
+  <si>
+    <t>VN</t>
+  </si>
+  <si>
+    <t>Survey / Mapping Node Points</t>
+  </si>
+  <si>
+    <t>VS</t>
+  </si>
+  <si>
+    <t>Survey / Mapping Staked Points</t>
+  </si>
+  <si>
+    <t>VU</t>
+  </si>
+  <si>
+    <t>Survey / Mapping Combined Utilities</t>
+  </si>
+  <si>
+    <t>WC</t>
+  </si>
+  <si>
+    <t>Distributed Energy Civil</t>
+  </si>
+  <si>
+    <t>WD</t>
+  </si>
+  <si>
+    <t>Distributed Energy Demolition</t>
+  </si>
+  <si>
+    <t>WI</t>
+  </si>
+  <si>
+    <t>Distributed Energy Interconnection</t>
+  </si>
+  <si>
+    <t>WJ</t>
+  </si>
+  <si>
+    <t>WK</t>
+  </si>
+  <si>
+    <t>WP</t>
+  </si>
+  <si>
+    <t>Distributed Energy Power</t>
+  </si>
+  <si>
+    <t>WS</t>
+  </si>
+  <si>
+    <t>Distributed Energy Structural</t>
+  </si>
+  <si>
+    <t>WT</t>
+  </si>
+  <si>
+    <t>Distributed Energy Telecommunications</t>
+  </si>
+  <si>
+    <t>WY</t>
+  </si>
+  <si>
+    <t>Distributed Energy Auxiliary Systems</t>
+  </si>
+  <si>
+    <t>Estructural</t>
+  </si>
+  <si>
+    <t>Subestructura estructural</t>
+  </si>
+  <si>
+    <t>Demolición estructural</t>
+  </si>
+  <si>
+    <t>Estructura estructural</t>
+  </si>
+  <si>
+    <t>Sitio estructural</t>
+  </si>
+  <si>
+    <t>Levantamiento/Cartografía</t>
+  </si>
+  <si>
+    <t>Levantamiento/Cartografía aérea</t>
+  </si>
+  <si>
+    <t>Levantamiento/Cartografía de puntos calculados</t>
+  </si>
+  <si>
+    <t>Levantamiento/Cartografía de campo</t>
+  </si>
+  <si>
+    <t>Levantamiento/Cartografía digital</t>
+  </si>
+  <si>
+    <t>Levantamiento/Cartografía de puntos nodales</t>
+  </si>
+  <si>
+    <t>Levantamiento/Cartografía de puntos replanteados</t>
+  </si>
+  <si>
+    <t>Levantamiento/Cartografía de servicios públicos combinados</t>
+  </si>
+  <si>
+    <t>Energía distribuida civil</t>
+  </si>
+  <si>
+    <t>Demolición de energía distribuida</t>
+  </si>
+  <si>
+    <t>Interconexión de energía distribuida</t>
+  </si>
+  <si>
+    <t>Energía distribuida eléctrica</t>
+  </si>
+  <si>
+    <t>Energía distribuida estructural</t>
+  </si>
+  <si>
+    <t>Telecomunicaciones de energía distribuida</t>
+  </si>
+  <si>
+    <t>Sistemas auxiliares de energía distribuida</t>
   </si>
 </sst>
 </file>
@@ -14417,7 +14603,7 @@
         <v>| A | Architectural |</v>
       </c>
       <c r="Q5" s="5" t="str">
-        <f t="shared" ref="Q5:Q38" si="3">_xlfn.CONCAT("| ",B5," | ",C5," | ",D5," |")</f>
+        <f t="shared" ref="Q5:Q46" si="3">_xlfn.CONCAT("| ",B5," | ",C5," | ",D5," |")</f>
         <v>| A | Architectural | Arquitectura |</v>
       </c>
       <c r="R5" s="5" t="str">
@@ -15547,9 +15733,15 @@
       <c r="V34" s="5"/>
     </row>
     <row r="35" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
+      <c r="B35" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>1803</v>
+      </c>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
@@ -15564,7 +15756,7 @@
       <c r="P35" s="5"/>
       <c r="Q35" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>|  |  |  |</v>
+        <v>| S | Structural | Estructural |</v>
       </c>
       <c r="R35" s="5"/>
       <c r="S35" s="5"/>
@@ -15573,9 +15765,15 @@
       <c r="V35" s="5"/>
     </row>
     <row r="36" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
+      <c r="B36" s="4" t="s">
+        <v>1761</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>1762</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>1804</v>
+      </c>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
@@ -15590,7 +15788,7 @@
       <c r="P36" s="5"/>
       <c r="Q36" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>|  |  |  |</v>
+        <v>| SB | Structural Substructure | Subestructura estructural |</v>
       </c>
       <c r="R36" s="5"/>
       <c r="S36" s="5"/>
@@ -15599,9 +15797,15 @@
       <c r="V36" s="5"/>
     </row>
     <row r="37" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B37" s="5"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
+      <c r="B37" s="5" t="s">
+        <v>1763</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>1764</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>1805</v>
+      </c>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
@@ -15616,7 +15820,7 @@
       <c r="P37" s="5"/>
       <c r="Q37" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>|  |  |  |</v>
+        <v>| SD | Structural Demolition | Demolición estructural |</v>
       </c>
       <c r="R37" s="5"/>
       <c r="S37" s="5"/>
@@ -15625,9 +15829,15 @@
       <c r="V37" s="5"/>
     </row>
     <row r="38" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="4"/>
+      <c r="B38" s="5" t="s">
+        <v>1765</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>1766</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>1806</v>
+      </c>
       <c r="E38" s="5"/>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
@@ -15642,7 +15852,7 @@
       <c r="P38" s="5"/>
       <c r="Q38" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>|  |  |  |</v>
+        <v>| SF | Structural Framing | Estructura estructural |</v>
       </c>
       <c r="R38" s="5"/>
       <c r="S38" s="5"/>
@@ -15651,9 +15861,15 @@
       <c r="V38" s="5"/>
     </row>
     <row r="39" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
+      <c r="B39" s="4" t="s">
+        <v>1767</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>125</v>
+      </c>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
@@ -15666,7 +15882,10 @@
       <c r="N39" s="5"/>
       <c r="O39" s="4"/>
       <c r="P39" s="5"/>
-      <c r="Q39" s="5"/>
+      <c r="Q39" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| SJ | User Defined | Definido por el usuario |</v>
+      </c>
       <c r="R39" s="5"/>
       <c r="S39" s="5"/>
       <c r="T39" s="5"/>
@@ -15674,9 +15893,15 @@
       <c r="V39" s="5"/>
     </row>
     <row r="40" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
+      <c r="B40" s="4" t="s">
+        <v>1768</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>125</v>
+      </c>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
       <c r="G40" s="4"/>
@@ -15689,7 +15914,10 @@
       <c r="N40" s="5"/>
       <c r="O40" s="4"/>
       <c r="P40" s="5"/>
-      <c r="Q40" s="5"/>
+      <c r="Q40" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| SK | User Defined | Definido por el usuario |</v>
+      </c>
       <c r="R40" s="5"/>
       <c r="S40" s="5"/>
       <c r="T40" s="5"/>
@@ -15697,9 +15925,15 @@
       <c r="V40" s="5"/>
     </row>
     <row r="41" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
+      <c r="B41" s="4" t="s">
+        <v>1769</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>1770</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>1807</v>
+      </c>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
@@ -15712,7 +15946,10 @@
       <c r="N41" s="5"/>
       <c r="O41" s="4"/>
       <c r="P41" s="5"/>
-      <c r="Q41" s="5"/>
+      <c r="Q41" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| SS | Structural Site | Sitio estructural |</v>
+      </c>
       <c r="R41" s="5"/>
       <c r="S41" s="5"/>
       <c r="T41" s="5"/>
@@ -15720,9 +15957,15 @@
       <c r="V41" s="5"/>
     </row>
     <row r="42" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
+      <c r="B42" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>1808</v>
+      </c>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
@@ -15735,7 +15978,10 @@
       <c r="N42" s="4"/>
       <c r="O42" s="4"/>
       <c r="P42" s="5"/>
-      <c r="Q42" s="5"/>
+      <c r="Q42" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| V | Survey / Mapping | Levantamiento/Cartografía |</v>
+      </c>
       <c r="R42" s="5"/>
       <c r="S42" s="5"/>
       <c r="T42" s="5"/>
@@ -15743,9 +15989,15 @@
       <c r="V42" s="5"/>
     </row>
     <row r="43" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
+      <c r="B43" s="4" t="s">
+        <v>1771</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>1772</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>1809</v>
+      </c>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
@@ -15758,7 +16010,10 @@
       <c r="N43" s="4"/>
       <c r="O43" s="4"/>
       <c r="P43" s="5"/>
-      <c r="Q43" s="5"/>
+      <c r="Q43" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| VA | Survey / Mapping Aerial | Levantamiento/Cartografía aérea |</v>
+      </c>
       <c r="R43" s="5"/>
       <c r="S43" s="5"/>
       <c r="T43" s="5"/>
@@ -15766,9 +16021,15 @@
       <c r="V43" s="5"/>
     </row>
     <row r="44" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
+      <c r="B44" s="4" t="s">
+        <v>1773</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>1774</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>1810</v>
+      </c>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
@@ -15781,7 +16042,10 @@
       <c r="N44" s="4"/>
       <c r="O44" s="4"/>
       <c r="P44" s="5"/>
-      <c r="Q44" s="5"/>
+      <c r="Q44" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>| VC | Survey / Mapping Computated Points | Levantamiento/Cartografía de puntos calculados |</v>
+      </c>
       <c r="R44" s="5"/>
       <c r="S44" s="5"/>
       <c r="T44" s="5"/>
@@ -15789,9 +16053,15 @@
       <c r="V44" s="5"/>
     </row>
     <row r="45" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
+      <c r="B45" s="4" t="s">
+        <v>1775</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>1776</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>1811</v>
+      </c>
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
@@ -15805,34 +16075,40 @@
       <c r="O45" s="4"/>
       <c r="P45" s="5" t="str">
         <f t="shared" ref="P45:P103" si="7">_xlfn.CONCAT("| ",B45," | ",C45," |")</f>
-        <v>|  |  |</v>
+        <v>| VF | Survey / Mapping Field |</v>
       </c>
       <c r="Q45" s="5" t="str">
-        <f t="shared" ref="Q45:Q103" si="8">_xlfn.CONCAT("| ",B45," | ",C45," | ",D45," |")</f>
-        <v>|  |  |  |</v>
+        <f t="shared" si="3"/>
+        <v>| VF | Survey / Mapping Field | Levantamiento/Cartografía de campo |</v>
       </c>
       <c r="R45" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>|  |  |  |  |</v>
+        <v>| VF | Survey / Mapping Field | Levantamiento/Cartografía de campo |  |</v>
       </c>
       <c r="S45" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>|  |  |  |  | |</v>
+        <v>| VF | Survey / Mapping Field | Levantamiento/Cartografía de campo |  | |</v>
       </c>
       <c r="T45" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>|  |  |  |  | | |</v>
+        <v>| VF | Survey / Mapping Field | Levantamiento/Cartografía de campo |  | | |</v>
       </c>
       <c r="U45" s="5"/>
       <c r="V45" s="5" t="str">
-        <f t="shared" ref="V45:V103" si="9">_xlfn.CONCAT("| ",B45," | ",C45," | ",D45," | ",E45," |",F45," |",G45," |",H45," |",I45," |",J45," |",K45," |",L45," |",M45," |",N45," |")</f>
-        <v>|  |  |  |  | | | | | | | | | |</v>
+        <f t="shared" ref="V45:V103" si="8">_xlfn.CONCAT("| ",B45," | ",C45," | ",D45," | ",E45," |",F45," |",G45," |",H45," |",I45," |",J45," |",K45," |",L45," |",M45," |",N45," |")</f>
+        <v>| VF | Survey / Mapping Field | Levantamiento/Cartografía de campo |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="46" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
+      <c r="B46" s="4" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>1778</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>1812</v>
+      </c>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
@@ -15846,34 +16122,40 @@
       <c r="O46" s="4"/>
       <c r="P46" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>|  |  |</v>
+        <v>| VI | Survey / Mapping Digital |</v>
       </c>
       <c r="Q46" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>|  |  |  |</v>
+        <f t="shared" si="3"/>
+        <v>| VI | Survey / Mapping Digital | Levantamiento/Cartografía digital |</v>
       </c>
       <c r="R46" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>|  |  |  |  |</v>
+        <v>| VI | Survey / Mapping Digital | Levantamiento/Cartografía digital |  |</v>
       </c>
       <c r="S46" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>|  |  |  |  | |</v>
+        <v>| VI | Survey / Mapping Digital | Levantamiento/Cartografía digital |  | |</v>
       </c>
       <c r="T46" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>|  |  |  |  | | |</v>
+        <v>| VI | Survey / Mapping Digital | Levantamiento/Cartografía digital |  | | |</v>
       </c>
       <c r="U46" s="5"/>
       <c r="V46" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>|  |  |  |  | | | | | | | | | |</v>
+        <f t="shared" si="8"/>
+        <v>| VI | Survey / Mapping Digital | Levantamiento/Cartografía digital |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="47" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
+      <c r="B47" s="4" t="s">
+        <v>1779</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>125</v>
+      </c>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
@@ -15887,34 +16169,40 @@
       <c r="O47" s="4"/>
       <c r="P47" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>|  |  |</v>
+        <v>| VJ | User Defined |</v>
       </c>
       <c r="Q47" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>|  |  |  |</v>
+        <f t="shared" ref="Q45:Q103" si="9">_xlfn.CONCAT("| ",B47," | ",C47," | ",D47," |")</f>
+        <v>| VJ | User Defined | Definido por el usuario |</v>
       </c>
       <c r="R47" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>|  |  |  |  |</v>
+        <v>| VJ | User Defined | Definido por el usuario |  |</v>
       </c>
       <c r="S47" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>|  |  |  |  | |</v>
+        <v>| VJ | User Defined | Definido por el usuario |  | |</v>
       </c>
       <c r="T47" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>|  |  |  |  | | |</v>
+        <v>| VJ | User Defined | Definido por el usuario |  | | |</v>
       </c>
       <c r="U47" s="5"/>
       <c r="V47" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>|  |  |  |  | | | | | | | | | |</v>
+        <f t="shared" si="8"/>
+        <v>| VJ | User Defined | Definido por el usuario |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="48" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
+      <c r="B48" s="4" t="s">
+        <v>1780</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>125</v>
+      </c>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
@@ -15928,34 +16216,40 @@
       <c r="O48" s="4"/>
       <c r="P48" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>|  |  |</v>
+        <v>| VK | User Defined |</v>
       </c>
       <c r="Q48" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>|  |  |  |</v>
+        <f t="shared" si="9"/>
+        <v>| VK | User Defined | Definido por el usuario |</v>
       </c>
       <c r="R48" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>|  |  |  |  |</v>
+        <v>| VK | User Defined | Definido por el usuario |  |</v>
       </c>
       <c r="S48" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>|  |  |  |  | |</v>
+        <v>| VK | User Defined | Definido por el usuario |  | |</v>
       </c>
       <c r="T48" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>|  |  |  |  | | |</v>
+        <v>| VK | User Defined | Definido por el usuario |  | | |</v>
       </c>
       <c r="U48" s="5"/>
       <c r="V48" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>|  |  |  |  | | | | | | | | | |</v>
+        <f t="shared" si="8"/>
+        <v>| VK | User Defined | Definido por el usuario |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="49" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
+      <c r="B49" s="4" t="s">
+        <v>1781</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>1782</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>1813</v>
+      </c>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
@@ -15969,34 +16263,40 @@
       <c r="O49" s="4"/>
       <c r="P49" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>|  |  |</v>
+        <v>| VN | Survey / Mapping Node Points |</v>
       </c>
       <c r="Q49" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>|  |  |  |</v>
+        <f t="shared" si="9"/>
+        <v>| VN | Survey / Mapping Node Points | Levantamiento/Cartografía de puntos nodales |</v>
       </c>
       <c r="R49" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>|  |  |  |  |</v>
+        <v>| VN | Survey / Mapping Node Points | Levantamiento/Cartografía de puntos nodales |  |</v>
       </c>
       <c r="S49" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>|  |  |  |  | |</v>
+        <v>| VN | Survey / Mapping Node Points | Levantamiento/Cartografía de puntos nodales |  | |</v>
       </c>
       <c r="T49" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>|  |  |  |  | | |</v>
+        <v>| VN | Survey / Mapping Node Points | Levantamiento/Cartografía de puntos nodales |  | | |</v>
       </c>
       <c r="U49" s="5"/>
       <c r="V49" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>|  |  |  |  | | | | | | | | | |</v>
+        <f t="shared" si="8"/>
+        <v>| VN | Survey / Mapping Node Points | Levantamiento/Cartografía de puntos nodales |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="50" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
+      <c r="B50" s="4" t="s">
+        <v>1783</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>1784</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>1814</v>
+      </c>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
@@ -16010,34 +16310,40 @@
       <c r="O50" s="4"/>
       <c r="P50" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>|  |  |</v>
+        <v>| VS | Survey / Mapping Staked Points |</v>
       </c>
       <c r="Q50" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>|  |  |  |</v>
+        <f t="shared" si="9"/>
+        <v>| VS | Survey / Mapping Staked Points | Levantamiento/Cartografía de puntos replanteados |</v>
       </c>
       <c r="R50" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>|  |  |  |  |</v>
+        <v>| VS | Survey / Mapping Staked Points | Levantamiento/Cartografía de puntos replanteados |  |</v>
       </c>
       <c r="S50" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>|  |  |  |  | |</v>
+        <v>| VS | Survey / Mapping Staked Points | Levantamiento/Cartografía de puntos replanteados |  | |</v>
       </c>
       <c r="T50" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>|  |  |  |  | | |</v>
+        <v>| VS | Survey / Mapping Staked Points | Levantamiento/Cartografía de puntos replanteados |  | | |</v>
       </c>
       <c r="U50" s="5"/>
       <c r="V50" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>|  |  |  |  | | | | | | | | | |</v>
+        <f t="shared" si="8"/>
+        <v>| VS | Survey / Mapping Staked Points | Levantamiento/Cartografía de puntos replanteados |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="51" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
+      <c r="B51" s="4" t="s">
+        <v>1785</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>1786</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>1815</v>
+      </c>
       <c r="E51" s="4"/>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
@@ -16051,34 +16357,40 @@
       <c r="O51" s="4"/>
       <c r="P51" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>|  |  |</v>
+        <v>| VU | Survey / Mapping Combined Utilities |</v>
       </c>
       <c r="Q51" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>|  |  |  |</v>
+        <f t="shared" si="9"/>
+        <v>| VU | Survey / Mapping Combined Utilities | Levantamiento/Cartografía de servicios públicos combinados |</v>
       </c>
       <c r="R51" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>|  |  |  |  |</v>
+        <v>| VU | Survey / Mapping Combined Utilities | Levantamiento/Cartografía de servicios públicos combinados |  |</v>
       </c>
       <c r="S51" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>|  |  |  |  | |</v>
+        <v>| VU | Survey / Mapping Combined Utilities | Levantamiento/Cartografía de servicios públicos combinados |  | |</v>
       </c>
       <c r="T51" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>|  |  |  |  | | |</v>
+        <v>| VU | Survey / Mapping Combined Utilities | Levantamiento/Cartografía de servicios públicos combinados |  | | |</v>
       </c>
       <c r="U51" s="5"/>
       <c r="V51" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>|  |  |  |  | | | | | | | | | |</v>
+        <f t="shared" si="8"/>
+        <v>| VU | Survey / Mapping Combined Utilities | Levantamiento/Cartografía de servicios públicos combinados |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="52" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
+      <c r="B52" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>97</v>
+      </c>
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
@@ -16092,34 +16404,40 @@
       <c r="O52" s="4"/>
       <c r="P52" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>|  |  |</v>
+        <v>| W | Distributed Energy |</v>
       </c>
       <c r="Q52" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>|  |  |  |</v>
+        <f t="shared" si="9"/>
+        <v>| W | Distributed Energy | Energía distribuida |</v>
       </c>
       <c r="R52" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>|  |  |  |  |</v>
+        <v>| W | Distributed Energy | Energía distribuida |  |</v>
       </c>
       <c r="S52" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>|  |  |  |  | |</v>
+        <v>| W | Distributed Energy | Energía distribuida |  | |</v>
       </c>
       <c r="T52" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>|  |  |  |  | | |</v>
+        <v>| W | Distributed Energy | Energía distribuida |  | | |</v>
       </c>
       <c r="U52" s="5"/>
       <c r="V52" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>|  |  |  |  | | | | | | | | | |</v>
+        <f t="shared" si="8"/>
+        <v>| W | Distributed Energy | Energía distribuida |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="53" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
+      <c r="B53" s="4" t="s">
+        <v>1787</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>1788</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>1816</v>
+      </c>
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
@@ -16133,34 +16451,40 @@
       <c r="O53" s="4"/>
       <c r="P53" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>|  |  |</v>
+        <v>| WC | Distributed Energy Civil |</v>
       </c>
       <c r="Q53" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>|  |  |  |</v>
+        <f t="shared" si="9"/>
+        <v>| WC | Distributed Energy Civil | Energía distribuida civil |</v>
       </c>
       <c r="R53" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>|  |  |  |  |</v>
+        <v>| WC | Distributed Energy Civil | Energía distribuida civil |  |</v>
       </c>
       <c r="S53" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>|  |  |  |  | |</v>
+        <v>| WC | Distributed Energy Civil | Energía distribuida civil |  | |</v>
       </c>
       <c r="T53" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>|  |  |  |  | | |</v>
+        <v>| WC | Distributed Energy Civil | Energía distribuida civil |  | | |</v>
       </c>
       <c r="U53" s="5"/>
       <c r="V53" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>|  |  |  |  | | | | | | | | | |</v>
+        <f t="shared" si="8"/>
+        <v>| WC | Distributed Energy Civil | Energía distribuida civil |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="54" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
+      <c r="B54" s="4" t="s">
+        <v>1789</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>1790</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>1817</v>
+      </c>
       <c r="E54" s="4"/>
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
@@ -16174,34 +16498,40 @@
       <c r="O54" s="4"/>
       <c r="P54" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>|  |  |</v>
+        <v>| WD | Distributed Energy Demolition |</v>
       </c>
       <c r="Q54" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>|  |  |  |</v>
+        <f t="shared" si="9"/>
+        <v>| WD | Distributed Energy Demolition | Demolición de energía distribuida |</v>
       </c>
       <c r="R54" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>|  |  |  |  |</v>
+        <v>| WD | Distributed Energy Demolition | Demolición de energía distribuida |  |</v>
       </c>
       <c r="S54" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>|  |  |  |  | |</v>
+        <v>| WD | Distributed Energy Demolition | Demolición de energía distribuida |  | |</v>
       </c>
       <c r="T54" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>|  |  |  |  | | |</v>
+        <v>| WD | Distributed Energy Demolition | Demolición de energía distribuida |  | | |</v>
       </c>
       <c r="U54" s="5"/>
       <c r="V54" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>|  |  |  |  | | | | | | | | | |</v>
+        <f t="shared" si="8"/>
+        <v>| WD | Distributed Energy Demolition | Demolición de energía distribuida |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="55" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="4"/>
+      <c r="B55" s="4" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>1792</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>1818</v>
+      </c>
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
@@ -16215,34 +16545,40 @@
       <c r="O55" s="4"/>
       <c r="P55" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>|  |  |</v>
+        <v>| WI | Distributed Energy Interconnection |</v>
       </c>
       <c r="Q55" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>|  |  |  |</v>
+        <f t="shared" si="9"/>
+        <v>| WI | Distributed Energy Interconnection | Interconexión de energía distribuida |</v>
       </c>
       <c r="R55" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>|  |  |  |  |</v>
+        <v>| WI | Distributed Energy Interconnection | Interconexión de energía distribuida |  |</v>
       </c>
       <c r="S55" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>|  |  |  |  | |</v>
+        <v>| WI | Distributed Energy Interconnection | Interconexión de energía distribuida |  | |</v>
       </c>
       <c r="T55" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>|  |  |  |  | | |</v>
+        <v>| WI | Distributed Energy Interconnection | Interconexión de energía distribuida |  | | |</v>
       </c>
       <c r="U55" s="5"/>
       <c r="V55" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>|  |  |  |  | | | | | | | | | |</v>
+        <f t="shared" si="8"/>
+        <v>| WI | Distributed Energy Interconnection | Interconexión de energía distribuida |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="56" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
+      <c r="B56" s="4" t="s">
+        <v>1793</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>125</v>
+      </c>
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
@@ -16256,34 +16592,40 @@
       <c r="O56" s="4"/>
       <c r="P56" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>|  |  |</v>
+        <v>| WJ | User Defined |</v>
       </c>
       <c r="Q56" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>|  |  |  |</v>
+        <f t="shared" si="9"/>
+        <v>| WJ | User Defined | Definido por el usuario |</v>
       </c>
       <c r="R56" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>|  |  |  |  |</v>
+        <v>| WJ | User Defined | Definido por el usuario |  |</v>
       </c>
       <c r="S56" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>|  |  |  |  | |</v>
+        <v>| WJ | User Defined | Definido por el usuario |  | |</v>
       </c>
       <c r="T56" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>|  |  |  |  | | |</v>
+        <v>| WJ | User Defined | Definido por el usuario |  | | |</v>
       </c>
       <c r="U56" s="5"/>
       <c r="V56" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>|  |  |  |  | | | | | | | | | |</v>
+        <f t="shared" si="8"/>
+        <v>| WJ | User Defined | Definido por el usuario |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="57" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="4"/>
+      <c r="B57" s="4" t="s">
+        <v>1794</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>125</v>
+      </c>
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
@@ -16297,34 +16639,40 @@
       <c r="O57" s="4"/>
       <c r="P57" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>|  |  |</v>
+        <v>| WK | User Defined |</v>
       </c>
       <c r="Q57" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>|  |  |  |</v>
+        <f t="shared" si="9"/>
+        <v>| WK | User Defined | Definido por el usuario |</v>
       </c>
       <c r="R57" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>|  |  |  |  |</v>
+        <v>| WK | User Defined | Definido por el usuario |  |</v>
       </c>
       <c r="S57" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>|  |  |  |  | |</v>
+        <v>| WK | User Defined | Definido por el usuario |  | |</v>
       </c>
       <c r="T57" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>|  |  |  |  | | |</v>
+        <v>| WK | User Defined | Definido por el usuario |  | | |</v>
       </c>
       <c r="U57" s="5"/>
       <c r="V57" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>|  |  |  |  | | | | | | | | | |</v>
+        <f t="shared" si="8"/>
+        <v>| WK | User Defined | Definido por el usuario |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="58" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="4"/>
+      <c r="B58" s="4" t="s">
+        <v>1795</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>1796</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>1819</v>
+      </c>
       <c r="E58" s="4"/>
       <c r="F58" s="4"/>
       <c r="G58" s="4"/>
@@ -16338,34 +16686,40 @@
       <c r="O58" s="4"/>
       <c r="P58" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>|  |  |</v>
+        <v>| WP | Distributed Energy Power |</v>
       </c>
       <c r="Q58" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>|  |  |  |</v>
+        <f t="shared" si="9"/>
+        <v>| WP | Distributed Energy Power | Energía distribuida eléctrica |</v>
       </c>
       <c r="R58" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>|  |  |  |  |</v>
+        <v>| WP | Distributed Energy Power | Energía distribuida eléctrica |  |</v>
       </c>
       <c r="S58" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>|  |  |  |  | |</v>
+        <v>| WP | Distributed Energy Power | Energía distribuida eléctrica |  | |</v>
       </c>
       <c r="T58" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>|  |  |  |  | | |</v>
+        <v>| WP | Distributed Energy Power | Energía distribuida eléctrica |  | | |</v>
       </c>
       <c r="U58" s="5"/>
       <c r="V58" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>|  |  |  |  | | | | | | | | | |</v>
+        <f t="shared" si="8"/>
+        <v>| WP | Distributed Energy Power | Energía distribuida eléctrica |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="59" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="4"/>
+      <c r="B59" s="4" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>1798</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>1820</v>
+      </c>
       <c r="E59" s="4"/>
       <c r="F59" s="4"/>
       <c r="G59" s="4"/>
@@ -16379,34 +16733,40 @@
       <c r="O59" s="4"/>
       <c r="P59" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>|  |  |</v>
+        <v>| WS | Distributed Energy Structural |</v>
       </c>
       <c r="Q59" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>|  |  |  |</v>
+        <f t="shared" si="9"/>
+        <v>| WS | Distributed Energy Structural | Energía distribuida estructural |</v>
       </c>
       <c r="R59" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>|  |  |  |  |</v>
+        <v>| WS | Distributed Energy Structural | Energía distribuida estructural |  |</v>
       </c>
       <c r="S59" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>|  |  |  |  | |</v>
+        <v>| WS | Distributed Energy Structural | Energía distribuida estructural |  | |</v>
       </c>
       <c r="T59" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>|  |  |  |  | | |</v>
+        <v>| WS | Distributed Energy Structural | Energía distribuida estructural |  | | |</v>
       </c>
       <c r="U59" s="5"/>
       <c r="V59" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>|  |  |  |  | | | | | | | | | |</v>
+        <f t="shared" si="8"/>
+        <v>| WS | Distributed Energy Structural | Energía distribuida estructural |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="60" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="4"/>
+      <c r="B60" s="4" t="s">
+        <v>1799</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>1800</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>1821</v>
+      </c>
       <c r="E60" s="4"/>
       <c r="F60" s="4"/>
       <c r="G60" s="4"/>
@@ -16420,34 +16780,40 @@
       <c r="O60" s="4"/>
       <c r="P60" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>|  |  |</v>
+        <v>| WT | Distributed Energy Telecommunications |</v>
       </c>
       <c r="Q60" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>|  |  |  |</v>
+        <f t="shared" si="9"/>
+        <v>| WT | Distributed Energy Telecommunications | Telecomunicaciones de energía distribuida |</v>
       </c>
       <c r="R60" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>|  |  |  |  |</v>
+        <v>| WT | Distributed Energy Telecommunications | Telecomunicaciones de energía distribuida |  |</v>
       </c>
       <c r="S60" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>|  |  |  |  | |</v>
+        <v>| WT | Distributed Energy Telecommunications | Telecomunicaciones de energía distribuida |  | |</v>
       </c>
       <c r="T60" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>|  |  |  |  | | |</v>
+        <v>| WT | Distributed Energy Telecommunications | Telecomunicaciones de energía distribuida |  | | |</v>
       </c>
       <c r="U60" s="5"/>
       <c r="V60" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>|  |  |  |  | | | | | | | | | |</v>
+        <f t="shared" si="8"/>
+        <v>| WT | Distributed Energy Telecommunications | Telecomunicaciones de energía distribuida |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="61" spans="2:22" x14ac:dyDescent="0.55000000000000004">
-      <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="4"/>
+      <c r="B61" s="4" t="s">
+        <v>1801</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>1802</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>1822</v>
+      </c>
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
       <c r="G61" s="4"/>
@@ -16461,28 +16827,28 @@
       <c r="O61" s="4"/>
       <c r="P61" s="5" t="str">
         <f t="shared" si="7"/>
-        <v>|  |  |</v>
+        <v>| WY | Distributed Energy Auxiliary Systems |</v>
       </c>
       <c r="Q61" s="5" t="str">
-        <f t="shared" si="8"/>
-        <v>|  |  |  |</v>
+        <f t="shared" si="9"/>
+        <v>| WY | Distributed Energy Auxiliary Systems | Sistemas auxiliares de energía distribuida |</v>
       </c>
       <c r="R61" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>|  |  |  |  |</v>
+        <v>| WY | Distributed Energy Auxiliary Systems | Sistemas auxiliares de energía distribuida |  |</v>
       </c>
       <c r="S61" s="5" t="str">
         <f t="shared" si="6"/>
-        <v>|  |  |  |  | |</v>
+        <v>| WY | Distributed Energy Auxiliary Systems | Sistemas auxiliares de energía distribuida |  | |</v>
       </c>
       <c r="T61" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>|  |  |  |  | | |</v>
+        <v>| WY | Distributed Energy Auxiliary Systems | Sistemas auxiliares de energía distribuida |  | | |</v>
       </c>
       <c r="U61" s="5"/>
       <c r="V61" s="5" t="str">
-        <f t="shared" si="9"/>
-        <v>|  |  |  |  | | | | | | | | | |</v>
+        <f t="shared" si="8"/>
+        <v>| WY | Distributed Energy Auxiliary Systems | Sistemas auxiliares de energía distribuida |  | | | | | | | | | |</v>
       </c>
     </row>
     <row r="62" spans="2:22" x14ac:dyDescent="0.55000000000000004">
@@ -16505,7 +16871,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q62" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R62" s="5" t="str">
@@ -16522,7 +16888,7 @@
       </c>
       <c r="U62" s="5"/>
       <c r="V62" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -16546,7 +16912,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q63" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R63" s="5" t="str">
@@ -16563,7 +16929,7 @@
       </c>
       <c r="U63" s="5"/>
       <c r="V63" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -16587,7 +16953,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q64" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R64" s="5" t="str">
@@ -16604,7 +16970,7 @@
       </c>
       <c r="U64" s="5"/>
       <c r="V64" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -16628,7 +16994,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q65" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R65" s="5" t="str">
@@ -16645,7 +17011,7 @@
       </c>
       <c r="U65" s="5"/>
       <c r="V65" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -16669,7 +17035,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q66" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R66" s="5" t="str">
@@ -16686,7 +17052,7 @@
       </c>
       <c r="U66" s="5"/>
       <c r="V66" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -16710,7 +17076,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q67" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R67" s="5" t="str">
@@ -16727,7 +17093,7 @@
       </c>
       <c r="U67" s="5"/>
       <c r="V67" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -16751,7 +17117,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q68" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R68" s="5" t="str">
@@ -16768,7 +17134,7 @@
       </c>
       <c r="U68" s="5"/>
       <c r="V68" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -16792,7 +17158,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q69" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R69" s="5" t="str">
@@ -16809,7 +17175,7 @@
       </c>
       <c r="U69" s="5"/>
       <c r="V69" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -16833,7 +17199,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q70" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R70" s="5" t="str">
@@ -16850,7 +17216,7 @@
       </c>
       <c r="U70" s="5"/>
       <c r="V70" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -16874,7 +17240,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q71" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R71" s="5" t="str">
@@ -16891,7 +17257,7 @@
       </c>
       <c r="U71" s="5"/>
       <c r="V71" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -16915,7 +17281,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q72" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R72" s="5" t="str">
@@ -16932,7 +17298,7 @@
       </c>
       <c r="U72" s="5"/>
       <c r="V72" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -16956,7 +17322,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q73" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R73" s="5" t="str">
@@ -16973,7 +17339,7 @@
       </c>
       <c r="U73" s="5"/>
       <c r="V73" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -16997,7 +17363,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q74" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R74" s="5" t="str">
@@ -17014,7 +17380,7 @@
       </c>
       <c r="U74" s="5"/>
       <c r="V74" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17038,7 +17404,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q75" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R75" s="5" t="str">
@@ -17055,7 +17421,7 @@
       </c>
       <c r="U75" s="5"/>
       <c r="V75" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17079,7 +17445,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q76" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R76" s="5" t="str">
@@ -17096,7 +17462,7 @@
       </c>
       <c r="U76" s="5"/>
       <c r="V76" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17120,7 +17486,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q77" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R77" s="5" t="str">
@@ -17137,7 +17503,7 @@
       </c>
       <c r="U77" s="5"/>
       <c r="V77" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17161,7 +17527,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q78" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R78" s="5" t="str">
@@ -17178,7 +17544,7 @@
       </c>
       <c r="U78" s="5"/>
       <c r="V78" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17202,7 +17568,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q79" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R79" s="5" t="str">
@@ -17219,7 +17585,7 @@
       </c>
       <c r="U79" s="5"/>
       <c r="V79" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17243,7 +17609,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q80" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R80" s="5" t="str">
@@ -17260,7 +17626,7 @@
       </c>
       <c r="U80" s="5"/>
       <c r="V80" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17284,7 +17650,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q81" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R81" s="5" t="str">
@@ -17301,7 +17667,7 @@
       </c>
       <c r="U81" s="5"/>
       <c r="V81" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17325,7 +17691,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q82" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R82" s="5" t="str">
@@ -17342,7 +17708,7 @@
       </c>
       <c r="U82" s="5"/>
       <c r="V82" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17366,7 +17732,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q83" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R83" s="5" t="str">
@@ -17383,7 +17749,7 @@
       </c>
       <c r="U83" s="5"/>
       <c r="V83" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17407,7 +17773,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q84" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R84" s="5" t="str">
@@ -17424,7 +17790,7 @@
       </c>
       <c r="U84" s="5"/>
       <c r="V84" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17448,7 +17814,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q85" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R85" s="5" t="str">
@@ -17465,7 +17831,7 @@
       </c>
       <c r="U85" s="5"/>
       <c r="V85" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17489,7 +17855,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q86" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R86" s="5" t="str">
@@ -17506,7 +17872,7 @@
       </c>
       <c r="U86" s="5"/>
       <c r="V86" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17530,7 +17896,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q87" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R87" s="5" t="str">
@@ -17547,7 +17913,7 @@
       </c>
       <c r="U87" s="5"/>
       <c r="V87" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17571,7 +17937,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q88" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R88" s="5" t="str">
@@ -17588,7 +17954,7 @@
       </c>
       <c r="U88" s="5"/>
       <c r="V88" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17612,7 +17978,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q89" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R89" s="5" t="str">
@@ -17629,7 +17995,7 @@
       </c>
       <c r="U89" s="5"/>
       <c r="V89" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17653,7 +18019,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q90" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R90" s="5" t="str">
@@ -17670,7 +18036,7 @@
       </c>
       <c r="U90" s="5"/>
       <c r="V90" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17694,7 +18060,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q91" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R91" s="5" t="str">
@@ -17711,7 +18077,7 @@
       </c>
       <c r="U91" s="5"/>
       <c r="V91" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17735,7 +18101,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q92" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R92" s="5" t="str">
@@ -17752,7 +18118,7 @@
       </c>
       <c r="U92" s="5"/>
       <c r="V92" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17776,7 +18142,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q93" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R93" s="5" t="str">
@@ -17793,7 +18159,7 @@
       </c>
       <c r="U93" s="5"/>
       <c r="V93" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17817,7 +18183,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q94" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R94" s="5" t="str">
@@ -17834,7 +18200,7 @@
       </c>
       <c r="U94" s="5"/>
       <c r="V94" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17858,7 +18224,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q95" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R95" s="5" t="str">
@@ -17875,7 +18241,7 @@
       </c>
       <c r="U95" s="5"/>
       <c r="V95" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17899,7 +18265,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q96" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R96" s="5" t="str">
@@ -17916,7 +18282,7 @@
       </c>
       <c r="U96" s="5"/>
       <c r="V96" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17940,7 +18306,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q97" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R97" s="5" t="str">
@@ -17957,7 +18323,7 @@
       </c>
       <c r="U97" s="5"/>
       <c r="V97" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -17981,7 +18347,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q98" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R98" s="5" t="str">
@@ -17998,7 +18364,7 @@
       </c>
       <c r="U98" s="5"/>
       <c r="V98" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -18022,7 +18388,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q99" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R99" s="5" t="str">
@@ -18039,7 +18405,7 @@
       </c>
       <c r="U99" s="5"/>
       <c r="V99" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -18063,7 +18429,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q100" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R100" s="5" t="str">
@@ -18080,7 +18446,7 @@
       </c>
       <c r="U100" s="5"/>
       <c r="V100" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -18104,7 +18470,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q101" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R101" s="5" t="str">
@@ -18121,7 +18487,7 @@
       </c>
       <c r="U101" s="5"/>
       <c r="V101" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -18145,7 +18511,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q102" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R102" s="5" t="str">
@@ -18162,7 +18528,7 @@
       </c>
       <c r="U102" s="5"/>
       <c r="V102" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
@@ -18186,7 +18552,7 @@
         <v>|  |  |</v>
       </c>
       <c r="Q103" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>|  |  |  |</v>
       </c>
       <c r="R103" s="5" t="str">
@@ -18203,7 +18569,7 @@
       </c>
       <c r="U103" s="5"/>
       <c r="V103" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>|  |  |  |  | | | | | | | | | |</v>
       </c>
     </row>
